--- a/output/Data and Chart Outputs/philippines_power_market.xlsx
+++ b/output/Data and Chart Outputs/philippines_power_market.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Units" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart - Prices" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily demand" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily prices" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Units" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Chart" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Chart - Prices" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Daily demand" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Daily prices" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -146,13 +146,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -176,22 +176,22 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="2A78D6"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$E$2:$E$91</f>
+              <f>'Chart'!$E$2:$E$92</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$91</f>
+              <f>'Chart'!$B$2:$B$92</f>
             </numRef>
           </val>
         </ser>
@@ -204,22 +204,22 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="EB6834"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$E$2:$E$91</f>
+              <f>'Chart'!$E$2:$E$92</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$91</f>
+              <f>'Chart'!$C$2:$C$92</f>
             </numRef>
           </val>
         </ser>
@@ -232,22 +232,22 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="1BAF7A"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$E$2:$E$91</f>
+              <f>'Chart'!$E$2:$E$92</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$91</f>
+              <f>'Chart'!$D$2:$D$92</f>
             </numRef>
           </val>
         </ser>
@@ -266,8 +266,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-2700000" vert="horz"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -293,8 +293,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -311,7 +311,7 @@
         <crossAx val="10"/>
       </valAx>
       <spPr>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -325,7 +325,7 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -334,13 +334,13 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -364,7 +364,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22225">
+            <a:ln w="22225">
               <a:solidFill>
                 <a:srgbClr val="2A78D6"/>
               </a:solidFill>
@@ -374,19 +374,19 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - Prices'!$E$2:$E$91</f>
+              <f>'Chart - Prices'!$E$2:$E$92</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Prices'!$B$2:$B$91</f>
+              <f>'Chart - Prices'!$B$2:$B$92</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -400,7 +400,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22225">
+            <a:ln w="22225">
               <a:solidFill>
                 <a:srgbClr val="EB6834"/>
               </a:solidFill>
@@ -410,19 +410,19 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - Prices'!$E$2:$E$91</f>
+              <f>'Chart - Prices'!$E$2:$E$92</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Prices'!$C$2:$C$91</f>
+              <f>'Chart - Prices'!$C$2:$C$92</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -436,7 +436,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22225">
+            <a:ln w="22225">
               <a:solidFill>
                 <a:srgbClr val="1BAF7A"/>
               </a:solidFill>
@@ -446,19 +446,19 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - Prices'!$E$2:$E$91</f>
+              <f>'Chart - Prices'!$E$2:$E$92</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Prices'!$D$2:$D$91</f>
+              <f>'Chart - Prices'!$D$2:$D$92</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -478,8 +478,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-2700000" vert="horz"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -505,8 +505,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -523,7 +523,7 @@
         <crossAx val="10"/>
       </valAx>
       <spPr>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -537,7 +537,7 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -546,7 +546,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>5</col>
@@ -561,9 +561,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -573,7 +573,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>5</col>
@@ -588,9 +588,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -911,7 +911,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Daily demand: per region (Luzon, Visayas, Mindanao) from the 5-minute real-time dispatch (RTD) regional summaries, energy commodity: demand_avg / demand_peak = average and maximum market requirement (MW); demand_MWh, generation_MWh, losses_MWh = mean MW x 24. Philippines_* = the three regions summed per interval. Intervals = 5-minute intervals in the day (288 = complete).</t>
+          <t>Daily demand: per region (Luzon, Visayas, Mindanao) from the 5-minute real-time dispatch (RTD) regional summaries, energy commodity: demand_avg / demand_peak = average and maximum market requirement (MW); demand_MWh, generation_MWh, losses_MWh = mean MW x 24. Philippines_* = the three regions summed per interval. Intervals = 5-minute intervals in the day (287 = complete: the files carry 287 per day; under 280 is re-read).</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Demand from 2026-07-05 to 2026-10-02; prices from 2026-07-05 to 2026-10-02. IEMOP lists about 90 days of files; older days are kept from previous runs. Grid-connected WESM regions (Mindanao joined WESM in 2023); off-grid islands are not included.</t>
+          <t>Demand from 2026-07-05 to 2026-10-03; prices from 2026-07-05 to 2026-10-03. IEMOP lists about 90 days of files; older days are kept from previous runs. Grid-connected WESM regions (Mindanao joined WESM in 2023); off-grid islands are not included.</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E91"/>
+  <dimension ref="A1:E92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2274,6 +2274,20 @@
       </c>
       <c r="D91" t="n">
         <v>2103.8</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B92" t="n">
+        <v>10172.5</v>
+      </c>
+      <c r="C92" t="n">
+        <v>2038.8</v>
+      </c>
+      <c r="D92" t="n">
+        <v>2023.1</v>
       </c>
     </row>
   </sheetData>
@@ -2288,7 +2302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E91"/>
+  <dimension ref="A1:E92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2345,13 +2359,13 @@
         <v>46209</v>
       </c>
       <c r="B3" t="n">
-        <v>9648.309999999999</v>
+        <v>9674.01</v>
       </c>
       <c r="C3" t="n">
-        <v>16760.89</v>
+        <v>15156.17</v>
       </c>
       <c r="D3" t="n">
-        <v>13824.38</v>
+        <v>14460.04</v>
       </c>
     </row>
     <row r="4">
@@ -2359,13 +2373,13 @@
         <v>46210</v>
       </c>
       <c r="B4" t="n">
-        <v>15956.01</v>
+        <v>15492.4</v>
       </c>
       <c r="C4" t="n">
-        <v>20025.79</v>
+        <v>17820.99</v>
       </c>
       <c r="D4" t="n">
-        <v>14833.9</v>
+        <v>15246.13</v>
       </c>
     </row>
     <row r="5">
@@ -2373,13 +2387,13 @@
         <v>46211</v>
       </c>
       <c r="B5" t="n">
-        <v>8685.23</v>
+        <v>10449.38</v>
       </c>
       <c r="C5" t="n">
-        <v>24777.43</v>
+        <v>13888.54</v>
       </c>
       <c r="D5" t="n">
-        <v>11143.05</v>
+        <v>14614.91</v>
       </c>
     </row>
     <row r="6">
@@ -2387,13 +2401,13 @@
         <v>46212</v>
       </c>
       <c r="B6" t="n">
-        <v>10505.78</v>
+        <v>10372.94</v>
       </c>
       <c r="C6" t="n">
-        <v>13619.49</v>
+        <v>11598.82</v>
       </c>
       <c r="D6" t="n">
-        <v>10865.44</v>
+        <v>10811.54</v>
       </c>
     </row>
     <row r="7">
@@ -2401,13 +2415,13 @@
         <v>46213</v>
       </c>
       <c r="B7" t="n">
-        <v>8399.889999999999</v>
+        <v>8512.870000000001</v>
       </c>
       <c r="C7" t="n">
-        <v>12085.15</v>
+        <v>11923.74</v>
       </c>
       <c r="D7" t="n">
-        <v>13467.62</v>
+        <v>10811.07</v>
       </c>
     </row>
     <row r="8">
@@ -2415,13 +2429,13 @@
         <v>46214</v>
       </c>
       <c r="B8" t="n">
-        <v>4438.67</v>
+        <v>4452.64</v>
       </c>
       <c r="C8" t="n">
-        <v>7450.6</v>
+        <v>7464.57</v>
       </c>
       <c r="D8" t="n">
-        <v>7692.64</v>
+        <v>7346.37</v>
       </c>
     </row>
     <row r="9">
@@ -2429,13 +2443,13 @@
         <v>46215</v>
       </c>
       <c r="B9" t="n">
-        <v>3792.52</v>
+        <v>2642.16</v>
       </c>
       <c r="C9" t="n">
-        <v>6886.49</v>
+        <v>6034.67</v>
       </c>
       <c r="D9" t="n">
-        <v>6810.65</v>
+        <v>5928.22</v>
       </c>
     </row>
     <row r="10">
@@ -2443,13 +2457,13 @@
         <v>46216</v>
       </c>
       <c r="B10" t="n">
-        <v>9187.74</v>
+        <v>9189.700000000001</v>
       </c>
       <c r="C10" t="n">
-        <v>17198.04</v>
+        <v>14279.83</v>
       </c>
       <c r="D10" t="n">
-        <v>13874.25</v>
+        <v>13475.05</v>
       </c>
     </row>
     <row r="11">
@@ -2457,13 +2471,13 @@
         <v>46217</v>
       </c>
       <c r="B11" t="n">
-        <v>8226.719999999999</v>
+        <v>8732.280000000001</v>
       </c>
       <c r="C11" t="n">
-        <v>19351.91</v>
+        <v>13763.51</v>
       </c>
       <c r="D11" t="n">
-        <v>17337.68</v>
+        <v>13415.44</v>
       </c>
     </row>
     <row r="12">
@@ -2471,13 +2485,13 @@
         <v>46218</v>
       </c>
       <c r="B12" t="n">
-        <v>6814.86</v>
+        <v>6750.34</v>
       </c>
       <c r="C12" t="n">
-        <v>20605.38</v>
+        <v>14389.92</v>
       </c>
       <c r="D12" t="n">
-        <v>24079.76</v>
+        <v>14360.79</v>
       </c>
     </row>
     <row r="13">
@@ -2485,13 +2499,13 @@
         <v>46219</v>
       </c>
       <c r="B13" t="n">
-        <v>7804.14</v>
+        <v>7864.06</v>
       </c>
       <c r="C13" t="n">
-        <v>16703.67</v>
+        <v>13883.19</v>
       </c>
       <c r="D13" t="n">
-        <v>13503.7</v>
+        <v>13279.45</v>
       </c>
     </row>
     <row r="14">
@@ -2499,13 +2513,13 @@
         <v>46220</v>
       </c>
       <c r="B14" t="n">
-        <v>8389.67</v>
+        <v>8464.02</v>
       </c>
       <c r="C14" t="n">
-        <v>12006.05</v>
+        <v>11423.06</v>
       </c>
       <c r="D14" t="n">
-        <v>11237.12</v>
+        <v>10344.33</v>
       </c>
     </row>
     <row r="15">
@@ -2513,13 +2527,13 @@
         <v>46221</v>
       </c>
       <c r="B15" t="n">
-        <v>5250.35</v>
+        <v>5117.03</v>
       </c>
       <c r="C15" t="n">
-        <v>10671.46</v>
+        <v>10347.97</v>
       </c>
       <c r="D15" t="n">
-        <v>10814.91</v>
+        <v>9862.98</v>
       </c>
     </row>
     <row r="16">
@@ -2527,13 +2541,13 @@
         <v>46222</v>
       </c>
       <c r="B16" t="n">
-        <v>4947.37</v>
+        <v>4970.86</v>
       </c>
       <c r="C16" t="n">
-        <v>7157.79</v>
+        <v>7220.62</v>
       </c>
       <c r="D16" t="n">
-        <v>7256.89</v>
+        <v>7237.53</v>
       </c>
     </row>
     <row r="17">
@@ -2541,13 +2555,13 @@
         <v>46223</v>
       </c>
       <c r="B17" t="n">
-        <v>6926.35</v>
+        <v>6890.82</v>
       </c>
       <c r="C17" t="n">
-        <v>14019.76</v>
+        <v>13865.49</v>
       </c>
       <c r="D17" t="n">
-        <v>14557.21</v>
+        <v>14544.17</v>
       </c>
     </row>
     <row r="18">
@@ -2555,13 +2569,13 @@
         <v>46224</v>
       </c>
       <c r="B18" t="n">
-        <v>6048.51</v>
+        <v>6083.68</v>
       </c>
       <c r="C18" t="n">
-        <v>10376.66</v>
+        <v>10411.83</v>
       </c>
       <c r="D18" t="n">
-        <v>10749.31</v>
+        <v>10562.24</v>
       </c>
     </row>
     <row r="19">
@@ -2569,13 +2583,13 @@
         <v>46225</v>
       </c>
       <c r="B19" t="n">
-        <v>8250.99</v>
+        <v>8257.85</v>
       </c>
       <c r="C19" t="n">
-        <v>12831.69</v>
+        <v>12154.8</v>
       </c>
       <c r="D19" t="n">
-        <v>11348.61</v>
+        <v>11589.02</v>
       </c>
     </row>
     <row r="20">
@@ -2583,13 +2597,13 @@
         <v>46226</v>
       </c>
       <c r="B20" t="n">
-        <v>6042.33</v>
+        <v>6056.21</v>
       </c>
       <c r="C20" t="n">
-        <v>10775.91</v>
+        <v>10789.8</v>
       </c>
       <c r="D20" t="n">
-        <v>9834.950000000001</v>
+        <v>9989.58</v>
       </c>
     </row>
     <row r="21">
@@ -2597,13 +2611,13 @@
         <v>46227</v>
       </c>
       <c r="B21" t="n">
-        <v>5338.66</v>
+        <v>4921.19</v>
       </c>
       <c r="C21" t="n">
-        <v>8577.41</v>
+        <v>8242.719999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>8312.16</v>
+        <v>8436.879999999999</v>
       </c>
     </row>
     <row r="22">
@@ -2611,13 +2625,13 @@
         <v>46228</v>
       </c>
       <c r="B22" t="n">
-        <v>4781.28</v>
+        <v>4805</v>
       </c>
       <c r="C22" t="n">
-        <v>8628.34</v>
+        <v>8652.07</v>
       </c>
       <c r="D22" t="n">
-        <v>8963.35</v>
+        <v>8386.870000000001</v>
       </c>
     </row>
     <row r="23">
@@ -2625,13 +2639,13 @@
         <v>46229</v>
       </c>
       <c r="B23" t="n">
-        <v>3886.3</v>
+        <v>3886.71</v>
       </c>
       <c r="C23" t="n">
-        <v>5239.44</v>
+        <v>5239.84</v>
       </c>
       <c r="D23" t="n">
-        <v>4629.28</v>
+        <v>4629.7</v>
       </c>
     </row>
     <row r="24">
@@ -2639,13 +2653,13 @@
         <v>46230</v>
       </c>
       <c r="B24" t="n">
-        <v>6399.86</v>
+        <v>6405.59</v>
       </c>
       <c r="C24" t="n">
-        <v>11449.27</v>
+        <v>11455</v>
       </c>
       <c r="D24" t="n">
-        <v>10422.27</v>
+        <v>10443.03</v>
       </c>
     </row>
     <row r="25">
@@ -2653,13 +2667,13 @@
         <v>46231</v>
       </c>
       <c r="B25" t="n">
-        <v>5885</v>
+        <v>5886.06</v>
       </c>
       <c r="C25" t="n">
-        <v>11580.55</v>
+        <v>11581.61</v>
       </c>
       <c r="D25" t="n">
-        <v>11666.25</v>
+        <v>11653.53</v>
       </c>
     </row>
     <row r="26">
@@ -2667,13 +2681,13 @@
         <v>46232</v>
       </c>
       <c r="B26" t="n">
-        <v>5148.51</v>
+        <v>5205.21</v>
       </c>
       <c r="C26" t="n">
-        <v>19762.43</v>
+        <v>14951.17</v>
       </c>
       <c r="D26" t="n">
-        <v>20746.04</v>
+        <v>16579.68</v>
       </c>
     </row>
     <row r="27">
@@ -2681,13 +2695,13 @@
         <v>46233</v>
       </c>
       <c r="B27" t="n">
-        <v>5544.86</v>
+        <v>5603.98</v>
       </c>
       <c r="C27" t="n">
-        <v>16950.35</v>
+        <v>10563.8</v>
       </c>
       <c r="D27" t="n">
-        <v>17111.49</v>
+        <v>11030.67</v>
       </c>
     </row>
     <row r="28">
@@ -2695,13 +2709,13 @@
         <v>46234</v>
       </c>
       <c r="B28" t="n">
-        <v>5783.4</v>
+        <v>5857.44</v>
       </c>
       <c r="C28" t="n">
-        <v>14104.07</v>
+        <v>10717.52</v>
       </c>
       <c r="D28" t="n">
-        <v>14688.65</v>
+        <v>11943.7</v>
       </c>
     </row>
     <row r="29">
@@ -2709,13 +2723,13 @@
         <v>46235</v>
       </c>
       <c r="B29" t="n">
-        <v>4598.28</v>
+        <v>4561.83</v>
       </c>
       <c r="C29" t="n">
-        <v>9378.17</v>
+        <v>9263.35</v>
       </c>
       <c r="D29" t="n">
-        <v>10417.72</v>
+        <v>9239.18</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -2731,10 +2745,10 @@
         <v>3796.44</v>
       </c>
       <c r="C30" t="n">
-        <v>12690.92</v>
+        <v>11969.25</v>
       </c>
       <c r="D30" t="n">
-        <v>10885.3</v>
+        <v>10845.88</v>
       </c>
     </row>
     <row r="31">
@@ -2742,13 +2756,13 @@
         <v>46237</v>
       </c>
       <c r="B31" t="n">
-        <v>4017.63</v>
+        <v>3787.23</v>
       </c>
       <c r="C31" t="n">
-        <v>25267.3</v>
+        <v>17100.04</v>
       </c>
       <c r="D31" t="n">
-        <v>22143.26</v>
+        <v>17908.14</v>
       </c>
     </row>
     <row r="32">
@@ -2756,13 +2770,13 @@
         <v>46238</v>
       </c>
       <c r="B32" t="n">
-        <v>3572.86</v>
+        <v>3535.25</v>
       </c>
       <c r="C32" t="n">
-        <v>79023.75</v>
+        <v>7882.29</v>
       </c>
       <c r="D32" t="n">
-        <v>52165.17</v>
+        <v>9861.610000000001</v>
       </c>
     </row>
     <row r="33">
@@ -2770,13 +2784,13 @@
         <v>46239</v>
       </c>
       <c r="B33" t="n">
-        <v>3504.75</v>
+        <v>2973.33</v>
       </c>
       <c r="C33" t="n">
-        <v>34533.15</v>
+        <v>10675.1</v>
       </c>
       <c r="D33" t="n">
-        <v>21345.89</v>
+        <v>11277.64</v>
       </c>
     </row>
     <row r="34">
@@ -2784,13 +2798,13 @@
         <v>46240</v>
       </c>
       <c r="B34" t="n">
-        <v>4570.63</v>
+        <v>3782.31</v>
       </c>
       <c r="C34" t="n">
-        <v>22139.92</v>
+        <v>16623.05</v>
       </c>
       <c r="D34" t="n">
-        <v>19537.48</v>
+        <v>18459.61</v>
       </c>
     </row>
     <row r="35">
@@ -2798,13 +2812,13 @@
         <v>46241</v>
       </c>
       <c r="B35" t="n">
-        <v>4651.96</v>
+        <v>4346.28</v>
       </c>
       <c r="C35" t="n">
-        <v>45907.29</v>
+        <v>8291.66</v>
       </c>
       <c r="D35" t="n">
-        <v>44308.6</v>
+        <v>9740.26</v>
       </c>
     </row>
     <row r="36">
@@ -2812,13 +2826,13 @@
         <v>46242</v>
       </c>
       <c r="B36" t="n">
-        <v>4805.88</v>
+        <v>4663.58</v>
       </c>
       <c r="C36" t="n">
-        <v>27860.31</v>
+        <v>10483</v>
       </c>
       <c r="D36" t="n">
-        <v>20013.61</v>
+        <v>11438.52</v>
       </c>
     </row>
     <row r="37">
@@ -2826,13 +2840,13 @@
         <v>46243</v>
       </c>
       <c r="B37" t="n">
-        <v>1959.87</v>
+        <v>1547.8</v>
       </c>
       <c r="C37" t="n">
-        <v>25227.6</v>
+        <v>14741.54</v>
       </c>
       <c r="D37" t="n">
-        <v>26635.01</v>
+        <v>16176.46</v>
       </c>
     </row>
     <row r="38">
@@ -2840,13 +2854,13 @@
         <v>46244</v>
       </c>
       <c r="B38" t="n">
-        <v>4981.25</v>
+        <v>4929.35</v>
       </c>
       <c r="C38" t="n">
-        <v>16254.63</v>
+        <v>11145.99</v>
       </c>
       <c r="D38" t="n">
-        <v>71627.39</v>
+        <v>12159.54</v>
       </c>
     </row>
     <row r="39">
@@ -2854,13 +2868,13 @@
         <v>46245</v>
       </c>
       <c r="B39" t="n">
-        <v>6102.37</v>
+        <v>7358.18</v>
       </c>
       <c r="C39" t="n">
-        <v>14253.26</v>
+        <v>11435.63</v>
       </c>
       <c r="D39" t="n">
-        <v>35825.91</v>
+        <v>11054.31</v>
       </c>
     </row>
     <row r="40">
@@ -2868,13 +2882,13 @@
         <v>46246</v>
       </c>
       <c r="B40" t="n">
-        <v>7018.91</v>
+        <v>11501.98</v>
       </c>
       <c r="C40" t="n">
-        <v>14112.64</v>
+        <v>14012.1</v>
       </c>
       <c r="D40" t="n">
-        <v>16739.9</v>
+        <v>15848.95</v>
       </c>
     </row>
     <row r="41">
@@ -2882,13 +2896,13 @@
         <v>46247</v>
       </c>
       <c r="B41" t="n">
-        <v>6447.6</v>
+        <v>6684.9</v>
       </c>
       <c r="C41" t="n">
-        <v>13353.34</v>
+        <v>12051.29</v>
       </c>
       <c r="D41" t="n">
-        <v>66349.28999999999</v>
+        <v>12404.99</v>
       </c>
     </row>
     <row r="42">
@@ -2896,13 +2910,13 @@
         <v>46248</v>
       </c>
       <c r="B42" t="n">
-        <v>5295.29</v>
+        <v>5263.8</v>
       </c>
       <c r="C42" t="n">
-        <v>21911.28</v>
+        <v>10940.16</v>
       </c>
       <c r="D42" t="n">
-        <v>26485.7</v>
+        <v>11076.78</v>
       </c>
     </row>
     <row r="43">
@@ -2910,13 +2924,13 @@
         <v>46249</v>
       </c>
       <c r="B43" t="n">
-        <v>4777.12</v>
+        <v>4857.89</v>
       </c>
       <c r="C43" t="n">
-        <v>14532.99</v>
+        <v>13485.61</v>
       </c>
       <c r="D43" t="n">
-        <v>23616.75</v>
+        <v>15791.65</v>
       </c>
     </row>
     <row r="44">
@@ -2924,13 +2938,13 @@
         <v>46250</v>
       </c>
       <c r="B44" t="n">
-        <v>3651.33</v>
+        <v>3048.5</v>
       </c>
       <c r="C44" t="n">
-        <v>51025.44</v>
+        <v>12190.58</v>
       </c>
       <c r="D44" t="n">
-        <v>48255.74</v>
+        <v>12622.72</v>
       </c>
     </row>
     <row r="45">
@@ -2938,13 +2952,13 @@
         <v>46251</v>
       </c>
       <c r="B45" t="n">
-        <v>3737.85</v>
+        <v>2960.13</v>
       </c>
       <c r="C45" t="n">
-        <v>14056.2</v>
+        <v>11313.86</v>
       </c>
       <c r="D45" t="n">
-        <v>38632.25</v>
+        <v>10931.23</v>
       </c>
     </row>
     <row r="46">
@@ -2952,13 +2966,13 @@
         <v>46252</v>
       </c>
       <c r="B46" t="n">
-        <v>4590.85</v>
+        <v>4502.67</v>
       </c>
       <c r="C46" t="n">
-        <v>14409.3</v>
+        <v>11769.83</v>
       </c>
       <c r="D46" t="n">
-        <v>14977.15</v>
+        <v>14083.82</v>
       </c>
     </row>
     <row r="47">
@@ -2966,13 +2980,13 @@
         <v>46253</v>
       </c>
       <c r="B47" t="n">
-        <v>4726.91</v>
+        <v>4582.48</v>
       </c>
       <c r="C47" t="n">
-        <v>68907.00999999999</v>
+        <v>13771.67</v>
       </c>
       <c r="D47" t="n">
-        <v>24509.83</v>
+        <v>14413.45</v>
       </c>
     </row>
     <row r="48">
@@ -2980,13 +2994,13 @@
         <v>46254</v>
       </c>
       <c r="B48" t="n">
-        <v>4616.53</v>
+        <v>5275.79</v>
       </c>
       <c r="C48" t="n">
-        <v>40078.1</v>
+        <v>9226.67</v>
       </c>
       <c r="D48" t="n">
-        <v>25955.98</v>
+        <v>9706.99</v>
       </c>
     </row>
     <row r="49">
@@ -2994,13 +3008,13 @@
         <v>46255</v>
       </c>
       <c r="B49" t="n">
-        <v>4546.29</v>
+        <v>4556.96</v>
       </c>
       <c r="C49" t="n">
-        <v>17481.12</v>
+        <v>14055.76</v>
       </c>
       <c r="D49" t="n">
-        <v>15531.78</v>
+        <v>13802.96</v>
       </c>
     </row>
     <row r="50">
@@ -3008,13 +3022,13 @@
         <v>46256</v>
       </c>
       <c r="B50" t="n">
-        <v>3566.44</v>
+        <v>3481.62</v>
       </c>
       <c r="C50" t="n">
-        <v>19381.75</v>
+        <v>13602.04</v>
       </c>
       <c r="D50" t="n">
-        <v>19443.56</v>
+        <v>15250.68</v>
       </c>
     </row>
     <row r="51">
@@ -3022,13 +3036,13 @@
         <v>46257</v>
       </c>
       <c r="B51" t="n">
-        <v>3217.07</v>
+        <v>3216.95</v>
       </c>
       <c r="C51" t="n">
-        <v>23820.62</v>
+        <v>9254.389999999999</v>
       </c>
       <c r="D51" t="n">
-        <v>22914</v>
+        <v>9933.52</v>
       </c>
     </row>
     <row r="52">
@@ -3036,13 +3050,13 @@
         <v>46258</v>
       </c>
       <c r="B52" t="n">
-        <v>6282.61</v>
+        <v>6217.28</v>
       </c>
       <c r="C52" t="n">
-        <v>21512.43</v>
+        <v>13592.9</v>
       </c>
       <c r="D52" t="n">
-        <v>81493.41</v>
+        <v>14273.03</v>
       </c>
     </row>
     <row r="53">
@@ -3050,13 +3064,13 @@
         <v>46259</v>
       </c>
       <c r="B53" t="n">
-        <v>6276.87</v>
+        <v>7128.3</v>
       </c>
       <c r="C53" t="n">
-        <v>14108.39</v>
+        <v>13399.38</v>
       </c>
       <c r="D53" t="n">
-        <v>11247.44</v>
+        <v>15772.83</v>
       </c>
     </row>
     <row r="54">
@@ -3599,6 +3613,20 @@
       </c>
       <c r="D91" t="n">
         <v>15518.65</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B92" t="n">
+        <v>6912.95</v>
+      </c>
+      <c r="C92" t="n">
+        <v>12747.33</v>
+      </c>
+      <c r="D92" t="n">
+        <v>12296.48</v>
       </c>
     </row>
   </sheetData>
@@ -3613,7 +3641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T91"/>
+  <dimension ref="A1:T92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9295,6 +9323,68 @@
         <v>358238.1</v>
       </c>
       <c r="T91" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B92" t="n">
+        <v>10172.5</v>
+      </c>
+      <c r="C92" t="n">
+        <v>11606.7</v>
+      </c>
+      <c r="D92" t="n">
+        <v>244139.3</v>
+      </c>
+      <c r="E92" t="n">
+        <v>249887.2</v>
+      </c>
+      <c r="F92" t="n">
+        <v>3875.4</v>
+      </c>
+      <c r="G92" t="n">
+        <v>2023.1</v>
+      </c>
+      <c r="H92" t="n">
+        <v>2433.8</v>
+      </c>
+      <c r="I92" t="n">
+        <v>48555.4</v>
+      </c>
+      <c r="J92" t="n">
+        <v>55230.3</v>
+      </c>
+      <c r="K92" t="n">
+        <v>1230.9</v>
+      </c>
+      <c r="L92" t="n">
+        <v>2038.8</v>
+      </c>
+      <c r="M92" t="n">
+        <v>2406.4</v>
+      </c>
+      <c r="N92" t="n">
+        <v>48931.6</v>
+      </c>
+      <c r="O92" t="n">
+        <v>46944.2</v>
+      </c>
+      <c r="P92" t="n">
+        <v>493.7</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>14236.9</v>
+      </c>
+      <c r="R92" t="n">
+        <v>16187</v>
+      </c>
+      <c r="S92" t="n">
+        <v>341685.1</v>
+      </c>
+      <c r="T92" t="n">
         <v>287</v>
       </c>
     </row>
@@ -9309,7 +9399,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I91"/>
+  <dimension ref="A1:I92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9393,25 +9483,25 @@
         <v>46209</v>
       </c>
       <c r="B3" t="n">
-        <v>9648.309999999999</v>
+        <v>9674.01</v>
       </c>
       <c r="C3" t="n">
-        <v>9859.110000000001</v>
+        <v>9814.93</v>
       </c>
       <c r="D3" t="n">
-        <v>13824.38</v>
+        <v>14460.04</v>
       </c>
       <c r="E3" t="n">
-        <v>15068.91</v>
+        <v>15656.8</v>
       </c>
       <c r="F3" t="n">
-        <v>16760.89</v>
+        <v>15156.17</v>
       </c>
       <c r="G3" t="n">
-        <v>17697.2</v>
+        <v>15976.2</v>
       </c>
       <c r="H3" t="n">
-        <v>11535.18</v>
+        <v>11407.62</v>
       </c>
       <c r="I3" t="n">
         <v>288</v>
@@ -9422,25 +9512,25 @@
         <v>46210</v>
       </c>
       <c r="B4" t="n">
-        <v>15956.01</v>
+        <v>15492.4</v>
       </c>
       <c r="C4" t="n">
-        <v>16143.7</v>
+        <v>15571.02</v>
       </c>
       <c r="D4" t="n">
-        <v>14833.9</v>
+        <v>15246.13</v>
       </c>
       <c r="E4" t="n">
-        <v>15684.03</v>
+        <v>16023.57</v>
       </c>
       <c r="F4" t="n">
-        <v>20025.79</v>
+        <v>17820.99</v>
       </c>
       <c r="G4" t="n">
-        <v>20093.53</v>
+        <v>18091.28</v>
       </c>
       <c r="H4" t="n">
-        <v>16519.4</v>
+        <v>15928.17</v>
       </c>
       <c r="I4" t="n">
         <v>288</v>
@@ -9451,25 +9541,25 @@
         <v>46211</v>
       </c>
       <c r="B5" t="n">
-        <v>8685.23</v>
+        <v>10449.38</v>
       </c>
       <c r="C5" t="n">
-        <v>8723.690000000001</v>
+        <v>10410.5</v>
       </c>
       <c r="D5" t="n">
-        <v>11143.05</v>
+        <v>14614.91</v>
       </c>
       <c r="E5" t="n">
-        <v>11216.11</v>
+        <v>15319.51</v>
       </c>
       <c r="F5" t="n">
-        <v>24777.43</v>
+        <v>13888.54</v>
       </c>
       <c r="G5" t="n">
-        <v>24821.73</v>
+        <v>13844.27</v>
       </c>
       <c r="H5" t="n">
-        <v>10933.9</v>
+        <v>11570.8</v>
       </c>
       <c r="I5" t="n">
         <v>288</v>
@@ -9480,25 +9570,25 @@
         <v>46212</v>
       </c>
       <c r="B6" t="n">
-        <v>10505.78</v>
+        <v>10372.94</v>
       </c>
       <c r="C6" t="n">
-        <v>10489.61</v>
+        <v>10295.5</v>
       </c>
       <c r="D6" t="n">
-        <v>10865.44</v>
+        <v>10811.54</v>
       </c>
       <c r="E6" t="n">
-        <v>10922.15</v>
+        <v>10796.7</v>
       </c>
       <c r="F6" t="n">
-        <v>13619.49</v>
+        <v>11598.82</v>
       </c>
       <c r="G6" t="n">
-        <v>14011.22</v>
+        <v>11857.78</v>
       </c>
       <c r="H6" t="n">
-        <v>10931.94</v>
+        <v>10540.25</v>
       </c>
       <c r="I6" t="n">
         <v>288</v>
@@ -9509,25 +9599,25 @@
         <v>46213</v>
       </c>
       <c r="B7" t="n">
-        <v>8399.889999999999</v>
+        <v>8512.870000000001</v>
       </c>
       <c r="C7" t="n">
-        <v>8514.459999999999</v>
+        <v>8514.48</v>
       </c>
       <c r="D7" t="n">
-        <v>13467.62</v>
+        <v>10811.07</v>
       </c>
       <c r="E7" t="n">
-        <v>14179.78</v>
+        <v>11201</v>
       </c>
       <c r="F7" t="n">
-        <v>12085.15</v>
+        <v>11923.74</v>
       </c>
       <c r="G7" t="n">
-        <v>12323.97</v>
+        <v>12043.12</v>
       </c>
       <c r="H7" t="n">
-        <v>9827.709999999999</v>
+        <v>9321.620000000001</v>
       </c>
       <c r="I7" t="n">
         <v>288</v>
@@ -9538,25 +9628,25 @@
         <v>46214</v>
       </c>
       <c r="B8" t="n">
-        <v>4438.67</v>
+        <v>4452.64</v>
       </c>
       <c r="C8" t="n">
-        <v>4379.39</v>
+        <v>4379.4</v>
       </c>
       <c r="D8" t="n">
-        <v>7692.64</v>
+        <v>7346.37</v>
       </c>
       <c r="E8" t="n">
-        <v>8284.139999999999</v>
+        <v>7895.81</v>
       </c>
       <c r="F8" t="n">
-        <v>7450.6</v>
+        <v>7464.57</v>
       </c>
       <c r="G8" t="n">
         <v>7643.61</v>
       </c>
       <c r="H8" t="n">
-        <v>5372.17</v>
+        <v>5307.95</v>
       </c>
       <c r="I8" t="n">
         <v>288</v>
@@ -9567,25 +9657,25 @@
         <v>46215</v>
       </c>
       <c r="B9" t="n">
-        <v>3792.52</v>
+        <v>2642.16</v>
       </c>
       <c r="C9" t="n">
-        <v>2976.07</v>
+        <v>2580.32</v>
       </c>
       <c r="D9" t="n">
-        <v>6810.65</v>
+        <v>5928.22</v>
       </c>
       <c r="E9" t="n">
-        <v>7184.38</v>
+        <v>6302.98</v>
       </c>
       <c r="F9" t="n">
-        <v>6886.49</v>
+        <v>6034.67</v>
       </c>
       <c r="G9" t="n">
-        <v>6751.25</v>
+        <v>5861.36</v>
       </c>
       <c r="H9" t="n">
-        <v>4136.5</v>
+        <v>3600.12</v>
       </c>
       <c r="I9" t="n">
         <v>288</v>
@@ -9596,25 +9686,25 @@
         <v>46216</v>
       </c>
       <c r="B10" t="n">
-        <v>9187.74</v>
+        <v>9189.700000000001</v>
       </c>
       <c r="C10" t="n">
         <v>9461.110000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>13874.25</v>
+        <v>13475.05</v>
       </c>
       <c r="E10" t="n">
-        <v>14812.95</v>
+        <v>14359.01</v>
       </c>
       <c r="F10" t="n">
-        <v>17198.04</v>
+        <v>14279.83</v>
       </c>
       <c r="G10" t="n">
-        <v>18564.35</v>
+        <v>15346.19</v>
       </c>
       <c r="H10" t="n">
-        <v>11445.79</v>
+        <v>10993.14</v>
       </c>
       <c r="I10" t="n">
         <v>288</v>
@@ -9625,25 +9715,25 @@
         <v>46217</v>
       </c>
       <c r="B11" t="n">
-        <v>8226.719999999999</v>
+        <v>8732.280000000001</v>
       </c>
       <c r="C11" t="n">
-        <v>8477.48</v>
+        <v>8989.16</v>
       </c>
       <c r="D11" t="n">
-        <v>17337.68</v>
+        <v>13415.44</v>
       </c>
       <c r="E11" t="n">
-        <v>18997.2</v>
+        <v>14548.59</v>
       </c>
       <c r="F11" t="n">
-        <v>19351.91</v>
+        <v>13763.51</v>
       </c>
       <c r="G11" t="n">
-        <v>20533.29</v>
+        <v>14492.4</v>
       </c>
       <c r="H11" t="n">
-        <v>11645.35</v>
+        <v>10564.2</v>
       </c>
       <c r="I11" t="n">
         <v>288</v>
@@ -9654,25 +9744,25 @@
         <v>46218</v>
       </c>
       <c r="B12" t="n">
-        <v>6814.86</v>
+        <v>6750.34</v>
       </c>
       <c r="C12" t="n">
-        <v>6901.48</v>
+        <v>6786.58</v>
       </c>
       <c r="D12" t="n">
-        <v>24079.76</v>
+        <v>14360.79</v>
       </c>
       <c r="E12" t="n">
-        <v>26607.52</v>
+        <v>15563.45</v>
       </c>
       <c r="F12" t="n">
-        <v>20605.38</v>
+        <v>14389.92</v>
       </c>
       <c r="G12" t="n">
-        <v>22002.68</v>
+        <v>15255.27</v>
       </c>
       <c r="H12" t="n">
-        <v>11847.2</v>
+        <v>9195.32</v>
       </c>
       <c r="I12" t="n">
         <v>288</v>
@@ -9683,25 +9773,25 @@
         <v>46219</v>
       </c>
       <c r="B13" t="n">
-        <v>7804.14</v>
+        <v>7864.06</v>
       </c>
       <c r="C13" t="n">
-        <v>7867.15</v>
+        <v>7864.9</v>
       </c>
       <c r="D13" t="n">
-        <v>13503.7</v>
+        <v>13279.45</v>
       </c>
       <c r="E13" t="n">
-        <v>14757.78</v>
+        <v>14417.8</v>
       </c>
       <c r="F13" t="n">
-        <v>16703.67</v>
+        <v>13883.19</v>
       </c>
       <c r="G13" t="n">
-        <v>17335.99</v>
+        <v>14372.59</v>
       </c>
       <c r="H13" t="n">
-        <v>10052.32</v>
+        <v>9653.74</v>
       </c>
       <c r="I13" t="n">
         <v>288</v>
@@ -9712,25 +9802,25 @@
         <v>46220</v>
       </c>
       <c r="B14" t="n">
-        <v>8389.67</v>
+        <v>8464.02</v>
       </c>
       <c r="C14" t="n">
-        <v>8619.52</v>
+        <v>8599.91</v>
       </c>
       <c r="D14" t="n">
-        <v>11237.12</v>
+        <v>10344.33</v>
       </c>
       <c r="E14" t="n">
-        <v>12106.71</v>
+        <v>10955.45</v>
       </c>
       <c r="F14" t="n">
-        <v>12006.05</v>
+        <v>11423.06</v>
       </c>
       <c r="G14" t="n">
-        <v>12084.84</v>
+        <v>11405.41</v>
       </c>
       <c r="H14" t="n">
-        <v>9568.57</v>
+        <v>9294.02</v>
       </c>
       <c r="I14" t="n">
         <v>288</v>
@@ -9741,25 +9831,25 @@
         <v>46221</v>
       </c>
       <c r="B15" t="n">
-        <v>5250.35</v>
+        <v>5117.03</v>
       </c>
       <c r="C15" t="n">
-        <v>5193.71</v>
+        <v>5019.04</v>
       </c>
       <c r="D15" t="n">
-        <v>10814.91</v>
+        <v>9862.98</v>
       </c>
       <c r="E15" t="n">
-        <v>11647.93</v>
+        <v>10643.07</v>
       </c>
       <c r="F15" t="n">
-        <v>10671.46</v>
+        <v>10347.97</v>
       </c>
       <c r="G15" t="n">
-        <v>10837.19</v>
+        <v>10434.57</v>
       </c>
       <c r="H15" t="n">
-        <v>6870.18</v>
+        <v>6536.64</v>
       </c>
       <c r="I15" t="n">
         <v>288</v>
@@ -9770,25 +9860,25 @@
         <v>46222</v>
       </c>
       <c r="B16" t="n">
-        <v>4947.37</v>
+        <v>4970.86</v>
       </c>
       <c r="C16" t="n">
-        <v>4889.15</v>
+        <v>4889.18</v>
       </c>
       <c r="D16" t="n">
-        <v>7256.89</v>
+        <v>7237.53</v>
       </c>
       <c r="E16" t="n">
-        <v>7584.01</v>
+        <v>7578.38</v>
       </c>
       <c r="F16" t="n">
-        <v>7157.79</v>
+        <v>7220.62</v>
       </c>
       <c r="G16" t="n">
-        <v>7110.18</v>
+        <v>7149.63</v>
       </c>
       <c r="H16" t="n">
-        <v>5570.37</v>
+        <v>5574.14</v>
       </c>
       <c r="I16" t="n">
         <v>288</v>
@@ -9799,25 +9889,25 @@
         <v>46223</v>
       </c>
       <c r="B17" t="n">
-        <v>6926.35</v>
+        <v>6890.82</v>
       </c>
       <c r="C17" t="n">
-        <v>6986.18</v>
+        <v>6919</v>
       </c>
       <c r="D17" t="n">
-        <v>14557.21</v>
+        <v>14544.17</v>
       </c>
       <c r="E17" t="n">
-        <v>15075.84</v>
+        <v>15049</v>
       </c>
       <c r="F17" t="n">
-        <v>14019.76</v>
+        <v>13865.49</v>
       </c>
       <c r="G17" t="n">
-        <v>14903.55</v>
+        <v>14718.66</v>
       </c>
       <c r="H17" t="n">
-        <v>9143.940000000001</v>
+        <v>9069.639999999999</v>
       </c>
       <c r="I17" t="n">
         <v>288</v>
@@ -9828,25 +9918,25 @@
         <v>46224</v>
       </c>
       <c r="B18" t="n">
-        <v>6048.51</v>
+        <v>6083.68</v>
       </c>
       <c r="C18" t="n">
-        <v>6032.3</v>
+        <v>6032.71</v>
       </c>
       <c r="D18" t="n">
-        <v>10749.31</v>
+        <v>10562.24</v>
       </c>
       <c r="E18" t="n">
-        <v>11074.21</v>
+        <v>10893.95</v>
       </c>
       <c r="F18" t="n">
-        <v>10376.66</v>
+        <v>10411.83</v>
       </c>
       <c r="G18" t="n">
-        <v>10794.22</v>
+        <v>10794.6</v>
       </c>
       <c r="H18" t="n">
-        <v>7342.73</v>
+        <v>7315.27</v>
       </c>
       <c r="I18" t="n">
         <v>288</v>
@@ -9857,25 +9947,25 @@
         <v>46225</v>
       </c>
       <c r="B19" t="n">
-        <v>8250.99</v>
+        <v>8257.85</v>
       </c>
       <c r="C19" t="n">
-        <v>8438.17</v>
+        <v>8404.51</v>
       </c>
       <c r="D19" t="n">
-        <v>11348.61</v>
+        <v>11589.02</v>
       </c>
       <c r="E19" t="n">
-        <v>11767.1</v>
+        <v>12013.28</v>
       </c>
       <c r="F19" t="n">
-        <v>12831.69</v>
+        <v>12154.8</v>
       </c>
       <c r="G19" t="n">
-        <v>13409.22</v>
+        <v>12654.33</v>
       </c>
       <c r="H19" t="n">
-        <v>9516.139999999999</v>
+        <v>9444.48</v>
       </c>
       <c r="I19" t="n">
         <v>288</v>
@@ -9886,25 +9976,25 @@
         <v>46226</v>
       </c>
       <c r="B20" t="n">
-        <v>6042.33</v>
+        <v>6056.21</v>
       </c>
       <c r="C20" t="n">
-        <v>3919.03</v>
+        <v>6022.27</v>
       </c>
       <c r="D20" t="n">
-        <v>9834.950000000001</v>
+        <v>9989.58</v>
       </c>
       <c r="E20" t="n">
-        <v>9903.620000000001</v>
+        <v>10052.23</v>
       </c>
       <c r="F20" t="n">
-        <v>10775.91</v>
+        <v>10789.8</v>
       </c>
       <c r="G20" t="n">
-        <v>11236.29</v>
+        <v>11237.63</v>
       </c>
       <c r="H20" t="n">
-        <v>5640.45</v>
+        <v>7213.38</v>
       </c>
       <c r="I20" t="n">
         <v>288</v>
@@ -9915,25 +10005,25 @@
         <v>46227</v>
       </c>
       <c r="B21" t="n">
-        <v>5338.66</v>
+        <v>4921.19</v>
       </c>
       <c r="C21" t="n">
-        <v>-928.1799999999999</v>
+        <v>4735.12</v>
       </c>
       <c r="D21" t="n">
-        <v>8312.16</v>
+        <v>8436.879999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>8483.809999999999</v>
+        <v>8587.530000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>8577.41</v>
+        <v>8242.719999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>8585.620000000001</v>
+        <v>8254.559999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>1648.04</v>
+        <v>5747.3</v>
       </c>
       <c r="I21" t="n">
         <v>288</v>
@@ -9944,25 +10034,25 @@
         <v>46228</v>
       </c>
       <c r="B22" t="n">
-        <v>4781.28</v>
+        <v>4805</v>
       </c>
       <c r="C22" t="n">
-        <v>4702.03</v>
+        <v>4700.18</v>
       </c>
       <c r="D22" t="n">
-        <v>8963.35</v>
+        <v>8386.870000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>9713.17</v>
+        <v>9041.049999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>8628.34</v>
+        <v>8652.07</v>
       </c>
       <c r="G22" t="n">
-        <v>8660.15</v>
+        <v>8668.809999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>6002.38</v>
+        <v>5890.4</v>
       </c>
       <c r="I22" t="n">
         <v>288</v>
@@ -9973,25 +10063,25 @@
         <v>46229</v>
       </c>
       <c r="B23" t="n">
-        <v>3886.3</v>
+        <v>3886.71</v>
       </c>
       <c r="C23" t="n">
-        <v>3810.18</v>
+        <v>3810.56</v>
       </c>
       <c r="D23" t="n">
-        <v>4629.28</v>
+        <v>4629.7</v>
       </c>
       <c r="E23" t="n">
-        <v>4905.96</v>
+        <v>4906.32</v>
       </c>
       <c r="F23" t="n">
-        <v>5239.44</v>
+        <v>5239.84</v>
       </c>
       <c r="G23" t="n">
-        <v>5156.23</v>
+        <v>5156.64</v>
       </c>
       <c r="H23" t="n">
-        <v>4151.5</v>
+        <v>4151.87</v>
       </c>
       <c r="I23" t="n">
         <v>288</v>
@@ -10002,25 +10092,25 @@
         <v>46230</v>
       </c>
       <c r="B24" t="n">
-        <v>6399.86</v>
+        <v>6405.59</v>
       </c>
       <c r="C24" t="n">
-        <v>6502.59</v>
+        <v>6502.12</v>
       </c>
       <c r="D24" t="n">
-        <v>10422.27</v>
+        <v>10443.03</v>
       </c>
       <c r="E24" t="n">
-        <v>11354.72</v>
+        <v>11376.72</v>
       </c>
       <c r="F24" t="n">
-        <v>11449.27</v>
+        <v>11455</v>
       </c>
       <c r="G24" t="n">
-        <v>12186.32</v>
+        <v>12185.79</v>
       </c>
       <c r="H24" t="n">
-        <v>7929.21</v>
+        <v>7932.45</v>
       </c>
       <c r="I24" t="n">
         <v>288</v>
@@ -10031,25 +10121,25 @@
         <v>46231</v>
       </c>
       <c r="B25" t="n">
-        <v>5885</v>
+        <v>5886.06</v>
       </c>
       <c r="C25" t="n">
         <v>5882.75</v>
       </c>
       <c r="D25" t="n">
-        <v>11666.25</v>
+        <v>11653.53</v>
       </c>
       <c r="E25" t="n">
-        <v>12174.42</v>
+        <v>12162.51</v>
       </c>
       <c r="F25" t="n">
-        <v>11580.55</v>
+        <v>11581.61</v>
       </c>
       <c r="G25" t="n">
         <v>12148.18</v>
       </c>
       <c r="H25" t="n">
-        <v>7601.59</v>
+        <v>7599.62</v>
       </c>
       <c r="I25" t="n">
         <v>288</v>
@@ -10060,25 +10150,25 @@
         <v>46232</v>
       </c>
       <c r="B26" t="n">
-        <v>5148.51</v>
+        <v>5205.21</v>
       </c>
       <c r="C26" t="n">
-        <v>5095.32</v>
+        <v>5092.37</v>
       </c>
       <c r="D26" t="n">
-        <v>20746.04</v>
+        <v>16579.68</v>
       </c>
       <c r="E26" t="n">
-        <v>21357.05</v>
+        <v>16812.99</v>
       </c>
       <c r="F26" t="n">
-        <v>19762.43</v>
+        <v>14951.17</v>
       </c>
       <c r="G26" t="n">
-        <v>20783.03</v>
+        <v>15917.1</v>
       </c>
       <c r="H26" t="n">
-        <v>9871.66</v>
+        <v>8475.549999999999</v>
       </c>
       <c r="I26" t="n">
         <v>288</v>
@@ -10089,25 +10179,25 @@
         <v>46233</v>
       </c>
       <c r="B27" t="n">
-        <v>5544.86</v>
+        <v>5603.98</v>
       </c>
       <c r="C27" t="n">
-        <v>5609.44</v>
+        <v>5657.95</v>
       </c>
       <c r="D27" t="n">
-        <v>17111.49</v>
+        <v>11030.67</v>
       </c>
       <c r="E27" t="n">
-        <v>18087.01</v>
+        <v>11003.06</v>
       </c>
       <c r="F27" t="n">
-        <v>16950.35</v>
+        <v>10563.8</v>
       </c>
       <c r="G27" t="n">
-        <v>17941.72</v>
+        <v>11622.59</v>
       </c>
       <c r="H27" t="n">
-        <v>9134.290000000001</v>
+        <v>7247.46</v>
       </c>
       <c r="I27" t="n">
         <v>288</v>
@@ -10118,25 +10208,25 @@
         <v>46234</v>
       </c>
       <c r="B28" t="n">
-        <v>5783.4</v>
+        <v>5857.44</v>
       </c>
       <c r="C28" t="n">
-        <v>5822.68</v>
+        <v>5898.87</v>
       </c>
       <c r="D28" t="n">
-        <v>14688.65</v>
+        <v>11943.7</v>
       </c>
       <c r="E28" t="n">
-        <v>15122.53</v>
+        <v>11684.11</v>
       </c>
       <c r="F28" t="n">
-        <v>14104.07</v>
+        <v>10717.52</v>
       </c>
       <c r="G28" t="n">
-        <v>14653.93</v>
+        <v>11746.61</v>
       </c>
       <c r="H28" t="n">
-        <v>8302.57</v>
+        <v>7479.21</v>
       </c>
       <c r="I28" t="n">
         <v>288</v>
@@ -10147,25 +10237,25 @@
         <v>46235</v>
       </c>
       <c r="B29" t="n">
-        <v>4598.28</v>
+        <v>4561.83</v>
       </c>
       <c r="C29" t="n">
-        <v>4580.2</v>
+        <v>4536.01</v>
       </c>
       <c r="D29" t="n">
-        <v>10417.72</v>
+        <v>9239.18</v>
       </c>
       <c r="E29" t="n">
-        <v>11099.14</v>
+        <v>9848.459999999999</v>
       </c>
       <c r="F29" t="n">
-        <v>9378.17</v>
+        <v>9263.35</v>
       </c>
       <c r="G29" t="n">
-        <v>9630.83</v>
+        <v>9487.559999999999</v>
       </c>
       <c r="H29" t="n">
-        <v>6192.73</v>
+        <v>5941.07</v>
       </c>
       <c r="I29" t="n">
         <v>288</v>
@@ -10182,19 +10272,19 @@
         <v>3719.33</v>
       </c>
       <c r="D30" t="n">
-        <v>10885.3</v>
+        <v>10845.88</v>
       </c>
       <c r="E30" t="n">
-        <v>11757.16</v>
+        <v>11707.71</v>
       </c>
       <c r="F30" t="n">
-        <v>12690.92</v>
+        <v>11969.25</v>
       </c>
       <c r="G30" t="n">
-        <v>12844.67</v>
+        <v>12071.67</v>
       </c>
       <c r="H30" t="n">
-        <v>6115.01</v>
+        <v>6019.07</v>
       </c>
       <c r="I30" t="n">
         <v>288</v>
@@ -10205,25 +10295,25 @@
         <v>46237</v>
       </c>
       <c r="B31" t="n">
-        <v>4017.63</v>
+        <v>3787.23</v>
       </c>
       <c r="C31" t="n">
-        <v>3960.01</v>
+        <v>3756.82</v>
       </c>
       <c r="D31" t="n">
-        <v>22143.26</v>
+        <v>17908.14</v>
       </c>
       <c r="E31" t="n">
-        <v>24309.61</v>
+        <v>19382.56</v>
       </c>
       <c r="F31" t="n">
-        <v>25267.3</v>
+        <v>17100.04</v>
       </c>
       <c r="G31" t="n">
-        <v>26541.4</v>
+        <v>18380.11</v>
       </c>
       <c r="H31" t="n">
-        <v>10281.57</v>
+        <v>8292.440000000001</v>
       </c>
       <c r="I31" t="n">
         <v>288</v>
@@ -10234,25 +10324,25 @@
         <v>46238</v>
       </c>
       <c r="B32" t="n">
-        <v>3572.86</v>
+        <v>3535.25</v>
       </c>
       <c r="C32" t="n">
-        <v>3593.56</v>
+        <v>3560.65</v>
       </c>
       <c r="D32" t="n">
-        <v>52165.17</v>
+        <v>9861.610000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>57655.42</v>
+        <v>9420.85</v>
       </c>
       <c r="F32" t="n">
-        <v>79023.75</v>
+        <v>7882.29</v>
       </c>
       <c r="G32" t="n">
-        <v>82213.88</v>
+        <v>9166.35</v>
       </c>
       <c r="H32" t="n">
-        <v>22586.34</v>
+        <v>5271.2</v>
       </c>
       <c r="I32" t="n">
         <v>288</v>
@@ -10263,25 +10353,25 @@
         <v>46239</v>
       </c>
       <c r="B33" t="n">
-        <v>3504.75</v>
+        <v>2973.33</v>
       </c>
       <c r="C33" t="n">
-        <v>2985.85</v>
+        <v>2816.44</v>
       </c>
       <c r="D33" t="n">
-        <v>21345.89</v>
+        <v>11277.64</v>
       </c>
       <c r="E33" t="n">
-        <v>23896.55</v>
+        <v>10799.2</v>
       </c>
       <c r="F33" t="n">
-        <v>34533.15</v>
+        <v>10675.1</v>
       </c>
       <c r="G33" t="n">
-        <v>37792.88</v>
+        <v>11763.41</v>
       </c>
       <c r="H33" t="n">
-        <v>11010.48</v>
+        <v>5353.01</v>
       </c>
       <c r="I33" t="n">
         <v>288</v>
@@ -10292,25 +10382,25 @@
         <v>46240</v>
       </c>
       <c r="B34" t="n">
-        <v>4570.63</v>
+        <v>3782.31</v>
       </c>
       <c r="C34" t="n">
-        <v>3853.52</v>
+        <v>3741.39</v>
       </c>
       <c r="D34" t="n">
-        <v>19537.48</v>
+        <v>18459.61</v>
       </c>
       <c r="E34" t="n">
-        <v>22531.22</v>
+        <v>19140.12</v>
       </c>
       <c r="F34" t="n">
-        <v>22139.92</v>
+        <v>16623.05</v>
       </c>
       <c r="G34" t="n">
-        <v>25085.86</v>
+        <v>18334.86</v>
       </c>
       <c r="H34" t="n">
-        <v>9969.280000000001</v>
+        <v>8414.84</v>
       </c>
       <c r="I34" t="n">
         <v>288</v>
@@ -10321,25 +10411,25 @@
         <v>46241</v>
       </c>
       <c r="B35" t="n">
-        <v>4651.96</v>
+        <v>4346.28</v>
       </c>
       <c r="C35" t="n">
-        <v>3869.99</v>
+        <v>4284.05</v>
       </c>
       <c r="D35" t="n">
-        <v>44308.6</v>
+        <v>9740.26</v>
       </c>
       <c r="E35" t="n">
-        <v>49377.28</v>
+        <v>8981.6</v>
       </c>
       <c r="F35" t="n">
-        <v>45907.29</v>
+        <v>8291.66</v>
       </c>
       <c r="G35" t="n">
-        <v>50853.74</v>
+        <v>9051.639999999999</v>
       </c>
       <c r="H35" t="n">
-        <v>18196.41</v>
+        <v>5750.38</v>
       </c>
       <c r="I35" t="n">
         <v>288</v>
@@ -10350,25 +10440,25 @@
         <v>46242</v>
       </c>
       <c r="B36" t="n">
-        <v>4805.88</v>
+        <v>4663.58</v>
       </c>
       <c r="C36" t="n">
-        <v>4165.02</v>
+        <v>4616.14</v>
       </c>
       <c r="D36" t="n">
-        <v>20013.61</v>
+        <v>11438.52</v>
       </c>
       <c r="E36" t="n">
-        <v>22354.35</v>
+        <v>10564.01</v>
       </c>
       <c r="F36" t="n">
-        <v>27860.31</v>
+        <v>10483</v>
       </c>
       <c r="G36" t="n">
-        <v>29851.46</v>
+        <v>11642.64</v>
       </c>
       <c r="H36" t="n">
-        <v>10841.3</v>
+        <v>6626.09</v>
       </c>
       <c r="I36" t="n">
         <v>288</v>
@@ -10379,25 +10469,25 @@
         <v>46243</v>
       </c>
       <c r="B37" t="n">
-        <v>1959.87</v>
+        <v>1547.8</v>
       </c>
       <c r="C37" t="n">
         <v>1586.14</v>
       </c>
       <c r="D37" t="n">
-        <v>26635.01</v>
+        <v>16176.46</v>
       </c>
       <c r="E37" t="n">
-        <v>28560.95</v>
+        <v>16040.27</v>
       </c>
       <c r="F37" t="n">
-        <v>25227.6</v>
+        <v>14741.54</v>
       </c>
       <c r="G37" t="n">
-        <v>28298.45</v>
+        <v>15830.66</v>
       </c>
       <c r="H37" t="n">
-        <v>10366.98</v>
+        <v>6281.53</v>
       </c>
       <c r="I37" t="n">
         <v>288</v>
@@ -10408,25 +10498,25 @@
         <v>46244</v>
       </c>
       <c r="B38" t="n">
-        <v>4981.25</v>
+        <v>4929.35</v>
       </c>
       <c r="C38" t="n">
-        <v>4605.46</v>
+        <v>5029.18</v>
       </c>
       <c r="D38" t="n">
-        <v>71627.39</v>
+        <v>12159.54</v>
       </c>
       <c r="E38" t="n">
-        <v>74825.17999999999</v>
+        <v>11456.31</v>
       </c>
       <c r="F38" t="n">
-        <v>16254.63</v>
+        <v>11145.99</v>
       </c>
       <c r="G38" t="n">
-        <v>15084.33</v>
+        <v>10801.9</v>
       </c>
       <c r="H38" t="n">
-        <v>18581.18</v>
+        <v>6981.24</v>
       </c>
       <c r="I38" t="n">
         <v>288</v>
@@ -10437,25 +10527,25 @@
         <v>46245</v>
       </c>
       <c r="B39" t="n">
-        <v>6102.37</v>
+        <v>7358.18</v>
       </c>
       <c r="C39" t="n">
-        <v>5688.94</v>
+        <v>7463.11</v>
       </c>
       <c r="D39" t="n">
-        <v>35825.91</v>
+        <v>11054.31</v>
       </c>
       <c r="E39" t="n">
-        <v>37872.47</v>
+        <v>10730.01</v>
       </c>
       <c r="F39" t="n">
-        <v>14253.26</v>
+        <v>11435.63</v>
       </c>
       <c r="G39" t="n">
-        <v>10981.67</v>
+        <v>11420.47</v>
       </c>
       <c r="H39" t="n">
-        <v>11983.22</v>
+        <v>8561.950000000001</v>
       </c>
       <c r="I39" t="n">
         <v>288</v>
@@ -10466,25 +10556,25 @@
         <v>46246</v>
       </c>
       <c r="B40" t="n">
-        <v>7018.91</v>
+        <v>11501.98</v>
       </c>
       <c r="C40" t="n">
-        <v>6702.34</v>
+        <v>11600.2</v>
       </c>
       <c r="D40" t="n">
-        <v>16739.9</v>
+        <v>15848.95</v>
       </c>
       <c r="E40" t="n">
-        <v>17685.34</v>
+        <v>15752.29</v>
       </c>
       <c r="F40" t="n">
-        <v>14112.64</v>
+        <v>14012.1</v>
       </c>
       <c r="G40" t="n">
-        <v>9583.200000000001</v>
+        <v>13621.08</v>
       </c>
       <c r="H40" t="n">
-        <v>9002.67</v>
+        <v>12596.9</v>
       </c>
       <c r="I40" t="n">
         <v>288</v>
@@ -10495,25 +10585,25 @@
         <v>46247</v>
       </c>
       <c r="B41" t="n">
-        <v>6447.6</v>
+        <v>6684.9</v>
       </c>
       <c r="C41" t="n">
-        <v>5967.88</v>
+        <v>6562.33</v>
       </c>
       <c r="D41" t="n">
-        <v>66349.28999999999</v>
+        <v>12404.99</v>
       </c>
       <c r="E41" t="n">
-        <v>69733.53999999999</v>
+        <v>11609.74</v>
       </c>
       <c r="F41" t="n">
-        <v>13353.34</v>
+        <v>12051.29</v>
       </c>
       <c r="G41" t="n">
-        <v>13386.37</v>
+        <v>11567.03</v>
       </c>
       <c r="H41" t="n">
-        <v>18248</v>
+        <v>8147.31</v>
       </c>
       <c r="I41" t="n">
         <v>288</v>
@@ -10524,25 +10614,25 @@
         <v>46248</v>
       </c>
       <c r="B42" t="n">
-        <v>5295.29</v>
+        <v>5263.8</v>
       </c>
       <c r="C42" t="n">
-        <v>4609.41</v>
+        <v>5163.03</v>
       </c>
       <c r="D42" t="n">
-        <v>26485.7</v>
+        <v>11076.78</v>
       </c>
       <c r="E42" t="n">
-        <v>29257.2</v>
+        <v>10542.4</v>
       </c>
       <c r="F42" t="n">
-        <v>21911.28</v>
+        <v>10940.16</v>
       </c>
       <c r="G42" t="n">
-        <v>22234.41</v>
+        <v>11339.52</v>
       </c>
       <c r="H42" t="n">
-        <v>11365.62</v>
+        <v>6953.75</v>
       </c>
       <c r="I42" t="n">
         <v>288</v>
@@ -10553,25 +10643,25 @@
         <v>46249</v>
       </c>
       <c r="B43" t="n">
-        <v>4777.12</v>
+        <v>4857.89</v>
       </c>
       <c r="C43" t="n">
-        <v>4444.53</v>
+        <v>4891.27</v>
       </c>
       <c r="D43" t="n">
-        <v>23616.75</v>
+        <v>15791.65</v>
       </c>
       <c r="E43" t="n">
-        <v>25012.97</v>
+        <v>15716.34</v>
       </c>
       <c r="F43" t="n">
-        <v>14532.99</v>
+        <v>13485.61</v>
       </c>
       <c r="G43" t="n">
-        <v>12720.97</v>
+        <v>13710.53</v>
       </c>
       <c r="H43" t="n">
-        <v>9177.190000000001</v>
+        <v>7985.04</v>
       </c>
       <c r="I43" t="n">
         <v>288</v>
@@ -10582,25 +10672,25 @@
         <v>46250</v>
       </c>
       <c r="B44" t="n">
-        <v>3651.33</v>
+        <v>3048.5</v>
       </c>
       <c r="C44" t="n">
-        <v>3307.01</v>
+        <v>3013.33</v>
       </c>
       <c r="D44" t="n">
-        <v>48255.74</v>
+        <v>12622.72</v>
       </c>
       <c r="E44" t="n">
-        <v>53683.37</v>
+        <v>12488.6</v>
       </c>
       <c r="F44" t="n">
-        <v>51025.44</v>
+        <v>12190.58</v>
       </c>
       <c r="G44" t="n">
-        <v>54076.97</v>
+        <v>12554.02</v>
       </c>
       <c r="H44" t="n">
-        <v>18722.31</v>
+        <v>5911.66</v>
       </c>
       <c r="I44" t="n">
         <v>288</v>
@@ -10611,25 +10701,25 @@
         <v>46251</v>
       </c>
       <c r="B45" t="n">
-        <v>3737.85</v>
+        <v>2960.13</v>
       </c>
       <c r="C45" t="n">
-        <v>3501.17</v>
+        <v>2980.92</v>
       </c>
       <c r="D45" t="n">
-        <v>38632.25</v>
+        <v>10931.23</v>
       </c>
       <c r="E45" t="n">
-        <v>40950.44</v>
+        <v>10559.56</v>
       </c>
       <c r="F45" t="n">
-        <v>14056.2</v>
+        <v>11313.86</v>
       </c>
       <c r="G45" t="n">
-        <v>13076.19</v>
+        <v>11501.14</v>
       </c>
       <c r="H45" t="n">
-        <v>11474.49</v>
+        <v>5471.29</v>
       </c>
       <c r="I45" t="n">
         <v>288</v>
@@ -10640,25 +10730,25 @@
         <v>46252</v>
       </c>
       <c r="B46" t="n">
-        <v>4590.85</v>
+        <v>4502.67</v>
       </c>
       <c r="C46" t="n">
-        <v>4332.99</v>
+        <v>4567.86</v>
       </c>
       <c r="D46" t="n">
-        <v>14977.15</v>
+        <v>14083.82</v>
       </c>
       <c r="E46" t="n">
-        <v>15716.14</v>
+        <v>13964.53</v>
       </c>
       <c r="F46" t="n">
-        <v>14409.3</v>
+        <v>11769.83</v>
       </c>
       <c r="G46" t="n">
-        <v>15277.39</v>
+        <v>12336.72</v>
       </c>
       <c r="H46" t="n">
-        <v>7853.76</v>
+        <v>7308.67</v>
       </c>
       <c r="I46" t="n">
         <v>288</v>
@@ -10669,25 +10759,25 @@
         <v>46253</v>
       </c>
       <c r="B47" t="n">
-        <v>4726.91</v>
+        <v>4582.48</v>
       </c>
       <c r="C47" t="n">
-        <v>4504.52</v>
+        <v>4552.45</v>
       </c>
       <c r="D47" t="n">
-        <v>24509.83</v>
+        <v>14413.45</v>
       </c>
       <c r="E47" t="n">
-        <v>26344.23</v>
+        <v>14379.02</v>
       </c>
       <c r="F47" t="n">
-        <v>68907.00999999999</v>
+        <v>13771.67</v>
       </c>
       <c r="G47" t="n">
-        <v>71610.89999999999</v>
+        <v>14949.09</v>
       </c>
       <c r="H47" t="n">
-        <v>17684.31</v>
+        <v>7808.81</v>
       </c>
       <c r="I47" t="n">
         <v>288</v>
@@ -10698,25 +10788,25 @@
         <v>46254</v>
       </c>
       <c r="B48" t="n">
-        <v>4616.53</v>
+        <v>5275.79</v>
       </c>
       <c r="C48" t="n">
-        <v>4176.25</v>
+        <v>5288.95</v>
       </c>
       <c r="D48" t="n">
-        <v>25955.98</v>
+        <v>9706.99</v>
       </c>
       <c r="E48" t="n">
-        <v>28417.96</v>
+        <v>9382.870000000001</v>
       </c>
       <c r="F48" t="n">
-        <v>40078.1</v>
+        <v>9226.67</v>
       </c>
       <c r="G48" t="n">
-        <v>43305.18</v>
+        <v>10124.96</v>
       </c>
       <c r="H48" t="n">
-        <v>13508.78</v>
+        <v>6640.83</v>
       </c>
       <c r="I48" t="n">
         <v>288</v>
@@ -10727,25 +10817,25 @@
         <v>46255</v>
       </c>
       <c r="B49" t="n">
-        <v>4546.29</v>
+        <v>4556.96</v>
       </c>
       <c r="C49" t="n">
-        <v>4562</v>
+        <v>4576.76</v>
       </c>
       <c r="D49" t="n">
-        <v>15531.78</v>
+        <v>13802.96</v>
       </c>
       <c r="E49" t="n">
-        <v>16341.81</v>
+        <v>14383.02</v>
       </c>
       <c r="F49" t="n">
-        <v>17481.12</v>
+        <v>14055.76</v>
       </c>
       <c r="G49" t="n">
-        <v>17984.07</v>
+        <v>14526.74</v>
       </c>
       <c r="H49" t="n">
-        <v>8228.33</v>
+        <v>7477.01</v>
       </c>
       <c r="I49" t="n">
         <v>288</v>
@@ -10756,25 +10846,25 @@
         <v>46256</v>
       </c>
       <c r="B50" t="n">
-        <v>3566.44</v>
+        <v>3481.62</v>
       </c>
       <c r="C50" t="n">
-        <v>3473.41</v>
+        <v>3399.42</v>
       </c>
       <c r="D50" t="n">
-        <v>19443.56</v>
+        <v>15250.68</v>
       </c>
       <c r="E50" t="n">
-        <v>20500.05</v>
+        <v>15861.71</v>
       </c>
       <c r="F50" t="n">
-        <v>19381.75</v>
+        <v>13602.04</v>
       </c>
       <c r="G50" t="n">
-        <v>19968.85</v>
+        <v>14541.28</v>
       </c>
       <c r="H50" t="n">
-        <v>8371.43</v>
+        <v>6872.06</v>
       </c>
       <c r="I50" t="n">
         <v>288</v>
@@ -10785,25 +10875,25 @@
         <v>46257</v>
       </c>
       <c r="B51" t="n">
-        <v>3217.07</v>
+        <v>3216.95</v>
       </c>
       <c r="C51" t="n">
-        <v>3137.7</v>
+        <v>3137.57</v>
       </c>
       <c r="D51" t="n">
-        <v>22914</v>
+        <v>9933.52</v>
       </c>
       <c r="E51" t="n">
-        <v>25019.55</v>
+        <v>9659.299999999999</v>
       </c>
       <c r="F51" t="n">
-        <v>23820.62</v>
+        <v>9254.389999999999</v>
       </c>
       <c r="G51" t="n">
-        <v>24604.11</v>
+        <v>10047.39</v>
       </c>
       <c r="H51" t="n">
-        <v>9503.93</v>
+        <v>5096.92</v>
       </c>
       <c r="I51" t="n">
         <v>288</v>
@@ -10814,25 +10904,25 @@
         <v>46258</v>
       </c>
       <c r="B52" t="n">
-        <v>6282.61</v>
+        <v>6217.28</v>
       </c>
       <c r="C52" t="n">
-        <v>6137.58</v>
+        <v>6165.84</v>
       </c>
       <c r="D52" t="n">
-        <v>81493.41</v>
+        <v>14273.03</v>
       </c>
       <c r="E52" t="n">
-        <v>86935.61</v>
+        <v>14431.04</v>
       </c>
       <c r="F52" t="n">
-        <v>21512.43</v>
+        <v>13592.9</v>
       </c>
       <c r="G52" t="n">
-        <v>23878.12</v>
+        <v>14368.59</v>
       </c>
       <c r="H52" t="n">
-        <v>22184.25</v>
+        <v>8580.09</v>
       </c>
       <c r="I52" t="n">
         <v>288</v>
@@ -10843,25 +10933,25 @@
         <v>46259</v>
       </c>
       <c r="B53" t="n">
-        <v>6276.87</v>
+        <v>7128.3</v>
       </c>
       <c r="C53" t="n">
-        <v>6042.21</v>
+        <v>6998.55</v>
       </c>
       <c r="D53" t="n">
-        <v>11247.44</v>
+        <v>15772.83</v>
       </c>
       <c r="E53" t="n">
-        <v>11885.4</v>
+        <v>15610.47</v>
       </c>
       <c r="F53" t="n">
-        <v>14108.39</v>
+        <v>13399.38</v>
       </c>
       <c r="G53" t="n">
-        <v>12629.67</v>
+        <v>13535.83</v>
       </c>
       <c r="H53" t="n">
-        <v>7833.29</v>
+        <v>9261.51</v>
       </c>
       <c r="I53" t="n">
         <v>288</v>
@@ -11966,6 +12056,35 @@
         <v>11096.66</v>
       </c>
       <c r="I91" t="n">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B92" t="n">
+        <v>6912.95</v>
+      </c>
+      <c r="C92" t="n">
+        <v>6741.95</v>
+      </c>
+      <c r="D92" t="n">
+        <v>12296.48</v>
+      </c>
+      <c r="E92" t="n">
+        <v>13441.88</v>
+      </c>
+      <c r="F92" t="n">
+        <v>12747.33</v>
+      </c>
+      <c r="G92" t="n">
+        <v>12696.09</v>
+      </c>
+      <c r="H92" t="n">
+        <v>8587.59</v>
+      </c>
+      <c r="I92" t="n">
         <v>288</v>
       </c>
     </row>

--- a/output/Data and Chart Outputs/philippines_power_market.xlsx
+++ b/output/Data and Chart Outputs/philippines_power_market.xlsx
@@ -345,7 +345,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Philippines WESM system marginal price by grid (IEMOP, daily average) (to Oct/26)</a:t>
+              <a:t>Philippines WESM system marginal price by grid (IEMOP final prices, daily average) (to Aug/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -381,12 +381,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - Prices'!$E$2:$E$92</f>
+              <f>'Chart - Prices'!$E$2:$E$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Prices'!$B$2:$B$92</f>
+              <f>'Chart - Prices'!$B$2:$B$52</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -417,12 +417,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - Prices'!$E$2:$E$92</f>
+              <f>'Chart - Prices'!$E$2:$E$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Prices'!$C$2:$C$92</f>
+              <f>'Chart - Prices'!$C$2:$C$52</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -453,12 +453,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - Prices'!$E$2:$E$92</f>
+              <f>'Chart - Prices'!$E$2:$E$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Prices'!$D$2:$D$92</f>
+              <f>'Chart - Prices'!$D$2:$D$52</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -888,7 +888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -922,31 +922,38 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Price_source = 'final' (DIPCEF, after IEMOP's price review, about 5-6 weeks after the day) or 'provisional' (DIPCER, raw; replaced by the final file once listed). Raw Visayas / Mindanao prices can run 3-10x the final ones (4 Aug 2026 Visayas SMP 79,024 raw vs 7,882 final), so on provisional days a price above the 32,000 PHP/MWh WESM offer cap is left blank (and so is Philippines_LMP_genweighted that day); every provisional value is kept as published in &lt;col&gt;_provisional. Provisional prices below the cap can still be revised; use final days for analysis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>COVERAGE</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Demand from 2026-07-05 to 2026-10-03; prices from 2026-07-05 to 2026-10-03. IEMOP lists about 90 days of files; older days are kept from previous runs. Grid-connected WESM regions (Mindanao joined WESM in 2023); off-grid islands are not included.</t>
         </is>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>SOURCE</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>IEMOP (Independent Electricity Market Operator of the Philippines), market data: RTD Regional Summaries and DIPC Energy Results - Raw, https://www.iemop.ph/market-data/</t>
         </is>
@@ -2302,7 +2309,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E92"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2337,16 +2344,16 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="B2" t="n">
-        <v>5481.43</v>
+        <v>9674.01</v>
       </c>
       <c r="C2" t="n">
-        <v>7319.85</v>
+        <v>15156.17</v>
       </c>
       <c r="D2" t="n">
-        <v>6564.1</v>
+        <v>14460.04</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -2356,1277 +2363,707 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B3" t="n">
-        <v>9674.01</v>
+        <v>15492.4</v>
       </c>
       <c r="C3" t="n">
-        <v>15156.17</v>
+        <v>17820.99</v>
       </c>
       <c r="D3" t="n">
-        <v>14460.04</v>
+        <v>15246.13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B4" t="n">
-        <v>15492.4</v>
+        <v>10449.38</v>
       </c>
       <c r="C4" t="n">
-        <v>17820.99</v>
+        <v>13888.54</v>
       </c>
       <c r="D4" t="n">
-        <v>15246.13</v>
+        <v>14614.91</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B5" t="n">
-        <v>10449.38</v>
+        <v>10372.94</v>
       </c>
       <c r="C5" t="n">
-        <v>13888.54</v>
+        <v>11598.82</v>
       </c>
       <c r="D5" t="n">
-        <v>14614.91</v>
+        <v>10811.54</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B6" t="n">
-        <v>10372.94</v>
+        <v>8512.870000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>11598.82</v>
+        <v>11923.74</v>
       </c>
       <c r="D6" t="n">
-        <v>10811.54</v>
+        <v>10811.07</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>46213</v>
+        <v>46214</v>
       </c>
       <c r="B7" t="n">
-        <v>8512.870000000001</v>
+        <v>4452.64</v>
       </c>
       <c r="C7" t="n">
-        <v>11923.74</v>
+        <v>7464.57</v>
       </c>
       <c r="D7" t="n">
-        <v>10811.07</v>
+        <v>7346.37</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>46214</v>
+        <v>46215</v>
       </c>
       <c r="B8" t="n">
-        <v>4452.64</v>
+        <v>2642.16</v>
       </c>
       <c r="C8" t="n">
-        <v>7464.57</v>
+        <v>6034.67</v>
       </c>
       <c r="D8" t="n">
-        <v>7346.37</v>
+        <v>5928.22</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="B9" t="n">
-        <v>2642.16</v>
+        <v>9189.700000000001</v>
       </c>
       <c r="C9" t="n">
-        <v>6034.67</v>
+        <v>14279.83</v>
       </c>
       <c r="D9" t="n">
-        <v>5928.22</v>
+        <v>13475.05</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B10" t="n">
-        <v>9189.700000000001</v>
+        <v>8732.280000000001</v>
       </c>
       <c r="C10" t="n">
-        <v>14279.83</v>
+        <v>13763.51</v>
       </c>
       <c r="D10" t="n">
-        <v>13475.05</v>
+        <v>13415.44</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B11" t="n">
-        <v>8732.280000000001</v>
+        <v>6750.34</v>
       </c>
       <c r="C11" t="n">
-        <v>13763.51</v>
+        <v>14389.92</v>
       </c>
       <c r="D11" t="n">
-        <v>13415.44</v>
+        <v>14360.79</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B12" t="n">
-        <v>6750.34</v>
+        <v>7864.06</v>
       </c>
       <c r="C12" t="n">
-        <v>14389.92</v>
+        <v>13883.19</v>
       </c>
       <c r="D12" t="n">
-        <v>14360.79</v>
+        <v>13279.45</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B13" t="n">
-        <v>7864.06</v>
+        <v>8464.02</v>
       </c>
       <c r="C13" t="n">
-        <v>13883.19</v>
+        <v>11423.06</v>
       </c>
       <c r="D13" t="n">
-        <v>13279.45</v>
+        <v>10344.33</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="B14" t="n">
-        <v>8464.02</v>
+        <v>5117.03</v>
       </c>
       <c r="C14" t="n">
-        <v>11423.06</v>
+        <v>10347.97</v>
       </c>
       <c r="D14" t="n">
-        <v>10344.33</v>
+        <v>9862.98</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B15" t="n">
-        <v>5117.03</v>
+        <v>4970.86</v>
       </c>
       <c r="C15" t="n">
-        <v>10347.97</v>
+        <v>7220.62</v>
       </c>
       <c r="D15" t="n">
-        <v>9862.98</v>
+        <v>7237.53</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B16" t="n">
-        <v>4970.86</v>
+        <v>6890.82</v>
       </c>
       <c r="C16" t="n">
-        <v>7220.62</v>
+        <v>13865.49</v>
       </c>
       <c r="D16" t="n">
-        <v>7237.53</v>
+        <v>14544.17</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B17" t="n">
-        <v>6890.82</v>
+        <v>6083.68</v>
       </c>
       <c r="C17" t="n">
-        <v>13865.49</v>
+        <v>10411.83</v>
       </c>
       <c r="D17" t="n">
-        <v>14544.17</v>
+        <v>10562.24</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B18" t="n">
-        <v>6083.68</v>
+        <v>8257.85</v>
       </c>
       <c r="C18" t="n">
-        <v>10411.83</v>
+        <v>12154.8</v>
       </c>
       <c r="D18" t="n">
-        <v>10562.24</v>
+        <v>11589.02</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B19" t="n">
-        <v>8257.85</v>
+        <v>6056.21</v>
       </c>
       <c r="C19" t="n">
-        <v>12154.8</v>
+        <v>10789.8</v>
       </c>
       <c r="D19" t="n">
-        <v>11589.02</v>
+        <v>9989.58</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B20" t="n">
-        <v>6056.21</v>
+        <v>4921.19</v>
       </c>
       <c r="C20" t="n">
-        <v>10789.8</v>
+        <v>8242.719999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>9989.58</v>
+        <v>8436.879999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B21" t="n">
-        <v>4921.19</v>
+        <v>4805</v>
       </c>
       <c r="C21" t="n">
-        <v>8242.719999999999</v>
+        <v>8652.07</v>
       </c>
       <c r="D21" t="n">
-        <v>8436.879999999999</v>
+        <v>8386.870000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="B22" t="n">
-        <v>4805</v>
+        <v>3886.71</v>
       </c>
       <c r="C22" t="n">
-        <v>8652.07</v>
+        <v>5239.84</v>
       </c>
       <c r="D22" t="n">
-        <v>8386.870000000001</v>
+        <v>4629.7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="B23" t="n">
-        <v>3886.71</v>
+        <v>6405.59</v>
       </c>
       <c r="C23" t="n">
-        <v>5239.84</v>
+        <v>11455</v>
       </c>
       <c r="D23" t="n">
-        <v>4629.7</v>
+        <v>10443.03</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B24" t="n">
-        <v>6405.59</v>
+        <v>5886.06</v>
       </c>
       <c r="C24" t="n">
-        <v>11455</v>
+        <v>11581.61</v>
       </c>
       <c r="D24" t="n">
-        <v>10443.03</v>
+        <v>11653.53</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B25" t="n">
-        <v>5886.06</v>
+        <v>5205.21</v>
       </c>
       <c r="C25" t="n">
-        <v>11581.61</v>
+        <v>14951.17</v>
       </c>
       <c r="D25" t="n">
-        <v>11653.53</v>
+        <v>16579.68</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B26" t="n">
-        <v>5205.21</v>
+        <v>5603.98</v>
       </c>
       <c r="C26" t="n">
-        <v>14951.17</v>
+        <v>10563.8</v>
       </c>
       <c r="D26" t="n">
-        <v>16579.68</v>
+        <v>11030.67</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B27" t="n">
-        <v>5603.98</v>
+        <v>5857.44</v>
       </c>
       <c r="C27" t="n">
-        <v>10563.8</v>
+        <v>10717.52</v>
       </c>
       <c r="D27" t="n">
-        <v>11030.67</v>
+        <v>11943.7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B28" t="n">
-        <v>5857.44</v>
+        <v>4561.83</v>
       </c>
       <c r="C28" t="n">
-        <v>10717.52</v>
+        <v>9263.35</v>
       </c>
       <c r="D28" t="n">
-        <v>11943.7</v>
+        <v>9239.18</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Aug/26</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B29" t="n">
-        <v>4561.83</v>
+        <v>3796.44</v>
       </c>
       <c r="C29" t="n">
-        <v>9263.35</v>
+        <v>11969.25</v>
       </c>
       <c r="D29" t="n">
-        <v>9239.18</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Aug/26</t>
-        </is>
+        <v>10845.88</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="B30" t="n">
-        <v>3796.44</v>
+        <v>3787.23</v>
       </c>
       <c r="C30" t="n">
-        <v>11969.25</v>
+        <v>17100.04</v>
       </c>
       <c r="D30" t="n">
-        <v>10845.88</v>
+        <v>17908.14</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B31" t="n">
-        <v>3787.23</v>
+        <v>3535.25</v>
       </c>
       <c r="C31" t="n">
-        <v>17100.04</v>
+        <v>7882.29</v>
       </c>
       <c r="D31" t="n">
-        <v>17908.14</v>
+        <v>9861.610000000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B32" t="n">
-        <v>3535.25</v>
+        <v>2973.33</v>
       </c>
       <c r="C32" t="n">
-        <v>7882.29</v>
+        <v>10675.1</v>
       </c>
       <c r="D32" t="n">
-        <v>9861.610000000001</v>
+        <v>11277.64</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B33" t="n">
-        <v>2973.33</v>
+        <v>3782.31</v>
       </c>
       <c r="C33" t="n">
-        <v>10675.1</v>
+        <v>16623.05</v>
       </c>
       <c r="D33" t="n">
-        <v>11277.64</v>
+        <v>18459.61</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B34" t="n">
-        <v>3782.31</v>
+        <v>4346.28</v>
       </c>
       <c r="C34" t="n">
-        <v>16623.05</v>
+        <v>8291.66</v>
       </c>
       <c r="D34" t="n">
-        <v>18459.61</v>
+        <v>9740.26</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B35" t="n">
-        <v>4346.28</v>
+        <v>4663.58</v>
       </c>
       <c r="C35" t="n">
-        <v>8291.66</v>
+        <v>10483</v>
       </c>
       <c r="D35" t="n">
-        <v>9740.26</v>
+        <v>11438.52</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B36" t="n">
-        <v>4663.58</v>
+        <v>1547.8</v>
       </c>
       <c r="C36" t="n">
-        <v>10483</v>
+        <v>14741.54</v>
       </c>
       <c r="D36" t="n">
-        <v>11438.52</v>
+        <v>16176.46</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B37" t="n">
-        <v>1547.8</v>
+        <v>4929.35</v>
       </c>
       <c r="C37" t="n">
-        <v>14741.54</v>
+        <v>11145.99</v>
       </c>
       <c r="D37" t="n">
-        <v>16176.46</v>
+        <v>12159.54</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B38" t="n">
-        <v>4929.35</v>
+        <v>7358.18</v>
       </c>
       <c r="C38" t="n">
-        <v>11145.99</v>
+        <v>11435.63</v>
       </c>
       <c r="D38" t="n">
-        <v>12159.54</v>
+        <v>11054.31</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B39" t="n">
-        <v>7358.18</v>
+        <v>11501.98</v>
       </c>
       <c r="C39" t="n">
-        <v>11435.63</v>
+        <v>14012.1</v>
       </c>
       <c r="D39" t="n">
-        <v>11054.31</v>
+        <v>15848.95</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B40" t="n">
-        <v>11501.98</v>
+        <v>6684.9</v>
       </c>
       <c r="C40" t="n">
-        <v>14012.1</v>
+        <v>12051.29</v>
       </c>
       <c r="D40" t="n">
-        <v>15848.95</v>
+        <v>12404.99</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B41" t="n">
-        <v>6684.9</v>
+        <v>5263.8</v>
       </c>
       <c r="C41" t="n">
-        <v>12051.29</v>
+        <v>10940.16</v>
       </c>
       <c r="D41" t="n">
-        <v>12404.99</v>
+        <v>11076.78</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B42" t="n">
-        <v>5263.8</v>
+        <v>4857.89</v>
       </c>
       <c r="C42" t="n">
-        <v>10940.16</v>
+        <v>13485.61</v>
       </c>
       <c r="D42" t="n">
-        <v>11076.78</v>
+        <v>15791.65</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B43" t="n">
-        <v>4857.89</v>
+        <v>3048.5</v>
       </c>
       <c r="C43" t="n">
-        <v>13485.61</v>
+        <v>12190.58</v>
       </c>
       <c r="D43" t="n">
-        <v>15791.65</v>
+        <v>12622.72</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B44" t="n">
-        <v>3048.5</v>
+        <v>2960.13</v>
       </c>
       <c r="C44" t="n">
-        <v>12190.58</v>
+        <v>11313.86</v>
       </c>
       <c r="D44" t="n">
-        <v>12622.72</v>
+        <v>10931.23</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B45" t="n">
-        <v>2960.13</v>
+        <v>4502.67</v>
       </c>
       <c r="C45" t="n">
-        <v>11313.86</v>
+        <v>11769.83</v>
       </c>
       <c r="D45" t="n">
-        <v>10931.23</v>
+        <v>14083.82</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B46" t="n">
-        <v>4502.67</v>
+        <v>4582.48</v>
       </c>
       <c r="C46" t="n">
-        <v>11769.83</v>
+        <v>13771.67</v>
       </c>
       <c r="D46" t="n">
-        <v>14083.82</v>
+        <v>14413.45</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B47" t="n">
-        <v>4582.48</v>
+        <v>5275.79</v>
       </c>
       <c r="C47" t="n">
-        <v>13771.67</v>
+        <v>9226.67</v>
       </c>
       <c r="D47" t="n">
-        <v>14413.45</v>
+        <v>9706.99</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B48" t="n">
-        <v>5275.79</v>
+        <v>4556.96</v>
       </c>
       <c r="C48" t="n">
-        <v>9226.67</v>
+        <v>14055.76</v>
       </c>
       <c r="D48" t="n">
-        <v>9706.99</v>
+        <v>13802.96</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B49" t="n">
-        <v>4556.96</v>
+        <v>3481.62</v>
       </c>
       <c r="C49" t="n">
-        <v>14055.76</v>
+        <v>13602.04</v>
       </c>
       <c r="D49" t="n">
-        <v>13802.96</v>
+        <v>15250.68</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B50" t="n">
-        <v>3481.62</v>
+        <v>3216.95</v>
       </c>
       <c r="C50" t="n">
-        <v>13602.04</v>
+        <v>9254.389999999999</v>
       </c>
       <c r="D50" t="n">
-        <v>15250.68</v>
+        <v>9933.52</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="B51" t="n">
-        <v>3216.95</v>
+        <v>6217.28</v>
       </c>
       <c r="C51" t="n">
-        <v>9254.389999999999</v>
+        <v>13592.9</v>
       </c>
       <c r="D51" t="n">
-        <v>9933.52</v>
+        <v>14273.03</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B52" t="n">
-        <v>6217.28</v>
+        <v>7128.3</v>
       </c>
       <c r="C52" t="n">
-        <v>13592.9</v>
+        <v>13399.38</v>
       </c>
       <c r="D52" t="n">
-        <v>14273.03</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="n">
-        <v>46259</v>
-      </c>
-      <c r="B53" t="n">
-        <v>7128.3</v>
-      </c>
-      <c r="C53" t="n">
-        <v>13399.38</v>
-      </c>
-      <c r="D53" t="n">
         <v>15772.83</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="n">
-        <v>46260</v>
-      </c>
-      <c r="B54" t="n">
-        <v>6078.76</v>
-      </c>
-      <c r="C54" t="n">
-        <v>30081.21</v>
-      </c>
-      <c r="D54" t="n">
-        <v>13872.03</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="n">
-        <v>46261</v>
-      </c>
-      <c r="B55" t="n">
-        <v>6870.55</v>
-      </c>
-      <c r="C55" t="n">
-        <v>29186.79</v>
-      </c>
-      <c r="D55" t="n">
-        <v>48368.45</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="n">
-        <v>46262</v>
-      </c>
-      <c r="B56" t="n">
-        <v>5577.55</v>
-      </c>
-      <c r="C56" t="n">
-        <v>29490.31</v>
-      </c>
-      <c r="D56" t="n">
-        <v>27408.76</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="n">
-        <v>46263</v>
-      </c>
-      <c r="B57" t="n">
-        <v>4168.24</v>
-      </c>
-      <c r="C57" t="n">
-        <v>17797.34</v>
-      </c>
-      <c r="D57" t="n">
-        <v>22339.12</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="3" t="n">
-        <v>46264</v>
-      </c>
-      <c r="B58" t="n">
-        <v>136.17</v>
-      </c>
-      <c r="C58" t="n">
-        <v>26602.37</v>
-      </c>
-      <c r="D58" t="n">
-        <v>74656.96000000001</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="3" t="n">
-        <v>46265</v>
-      </c>
-      <c r="B59" t="n">
-        <v>917.6799999999999</v>
-      </c>
-      <c r="C59" t="n">
-        <v>26283.51</v>
-      </c>
-      <c r="D59" t="n">
-        <v>47646.67</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="3" t="n">
-        <v>46266</v>
-      </c>
-      <c r="B60" t="n">
-        <v>4999.71</v>
-      </c>
-      <c r="C60" t="n">
-        <v>17592.81</v>
-      </c>
-      <c r="D60" t="n">
-        <v>26389.21</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Sep/26</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="3" t="n">
-        <v>46267</v>
-      </c>
-      <c r="B61" t="n">
-        <v>4922.72</v>
-      </c>
-      <c r="C61" t="n">
-        <v>21025.3</v>
-      </c>
-      <c r="D61" t="n">
-        <v>78467.69</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="3" t="n">
-        <v>46268</v>
-      </c>
-      <c r="B62" t="n">
-        <v>3924.77</v>
-      </c>
-      <c r="C62" t="n">
-        <v>22076.4</v>
-      </c>
-      <c r="D62" t="n">
-        <v>49958.57</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="3" t="n">
-        <v>46269</v>
-      </c>
-      <c r="B63" t="n">
-        <v>3740.97</v>
-      </c>
-      <c r="C63" t="n">
-        <v>21027.66</v>
-      </c>
-      <c r="D63" t="n">
-        <v>29379.65</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="3" t="n">
-        <v>46270</v>
-      </c>
-      <c r="B64" t="n">
-        <v>3124.51</v>
-      </c>
-      <c r="C64" t="n">
-        <v>30660.64</v>
-      </c>
-      <c r="D64" t="n">
-        <v>43308.92</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="3" t="n">
-        <v>46271</v>
-      </c>
-      <c r="B65" t="n">
-        <v>-217.13</v>
-      </c>
-      <c r="C65" t="n">
-        <v>27312.42</v>
-      </c>
-      <c r="D65" t="n">
-        <v>28406.9</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="3" t="n">
-        <v>46272</v>
-      </c>
-      <c r="B66" t="n">
-        <v>3905.22</v>
-      </c>
-      <c r="C66" t="n">
-        <v>28252.86</v>
-      </c>
-      <c r="D66" t="n">
-        <v>54685.62</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="3" t="n">
-        <v>46273</v>
-      </c>
-      <c r="B67" t="n">
-        <v>5819.31</v>
-      </c>
-      <c r="C67" t="n">
-        <v>17557.2</v>
-      </c>
-      <c r="D67" t="n">
-        <v>47612.04</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="3" t="n">
-        <v>46274</v>
-      </c>
-      <c r="B68" t="n">
-        <v>5750.53</v>
-      </c>
-      <c r="C68" t="n">
-        <v>16668.17</v>
-      </c>
-      <c r="D68" t="n">
-        <v>19976.6</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="3" t="n">
-        <v>46275</v>
-      </c>
-      <c r="B69" t="n">
-        <v>5028.17</v>
-      </c>
-      <c r="C69" t="n">
-        <v>37921.34</v>
-      </c>
-      <c r="D69" t="n">
-        <v>45174.82</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="3" t="n">
-        <v>46276</v>
-      </c>
-      <c r="B70" t="n">
-        <v>5000.77</v>
-      </c>
-      <c r="C70" t="n">
-        <v>22225.63</v>
-      </c>
-      <c r="D70" t="n">
-        <v>46971.34</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="3" t="n">
-        <v>46277</v>
-      </c>
-      <c r="B71" t="n">
-        <v>4778.7</v>
-      </c>
-      <c r="C71" t="n">
-        <v>23501.87</v>
-      </c>
-      <c r="D71" t="n">
-        <v>20506.52</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="3" t="n">
-        <v>46278</v>
-      </c>
-      <c r="B72" t="n">
-        <v>1333.23</v>
-      </c>
-      <c r="C72" t="n">
-        <v>36780</v>
-      </c>
-      <c r="D72" t="n">
-        <v>36724.33</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="n">
-        <v>46279</v>
-      </c>
-      <c r="B73" t="n">
-        <v>5117.86</v>
-      </c>
-      <c r="C73" t="n">
-        <v>20064</v>
-      </c>
-      <c r="D73" t="n">
-        <v>45924.54</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="3" t="n">
-        <v>46280</v>
-      </c>
-      <c r="B74" t="n">
-        <v>5304.31</v>
-      </c>
-      <c r="C74" t="n">
-        <v>21294.75</v>
-      </c>
-      <c r="D74" t="n">
-        <v>32053.39</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="3" t="n">
-        <v>46281</v>
-      </c>
-      <c r="B75" t="n">
-        <v>5146.68</v>
-      </c>
-      <c r="C75" t="n">
-        <v>33351.55</v>
-      </c>
-      <c r="D75" t="n">
-        <v>33342.56</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="3" t="n">
-        <v>46282</v>
-      </c>
-      <c r="B76" t="n">
-        <v>5008.53</v>
-      </c>
-      <c r="C76" t="n">
-        <v>17011.73</v>
-      </c>
-      <c r="D76" t="n">
-        <v>16760.48</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="3" t="n">
-        <v>46283</v>
-      </c>
-      <c r="B77" t="n">
-        <v>4748.07</v>
-      </c>
-      <c r="C77" t="n">
-        <v>11584.08</v>
-      </c>
-      <c r="D77" t="n">
-        <v>11565.77</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="3" t="n">
-        <v>46284</v>
-      </c>
-      <c r="B78" t="n">
-        <v>5548.56</v>
-      </c>
-      <c r="C78" t="n">
-        <v>19003.61</v>
-      </c>
-      <c r="D78" t="n">
-        <v>19244.37</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="3" t="n">
-        <v>46285</v>
-      </c>
-      <c r="B79" t="n">
-        <v>6138.06</v>
-      </c>
-      <c r="C79" t="n">
-        <v>12859.13</v>
-      </c>
-      <c r="D79" t="n">
-        <v>12777.26</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="3" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B80" t="n">
-        <v>13059.41</v>
-      </c>
-      <c r="C80" t="n">
-        <v>26991.73</v>
-      </c>
-      <c r="D80" t="n">
-        <v>43126</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="3" t="n">
-        <v>46287</v>
-      </c>
-      <c r="B81" t="n">
-        <v>8437.129999999999</v>
-      </c>
-      <c r="C81" t="n">
-        <v>11812.5</v>
-      </c>
-      <c r="D81" t="n">
-        <v>10233.09</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="3" t="n">
-        <v>46288</v>
-      </c>
-      <c r="B82" t="n">
-        <v>7752.03</v>
-      </c>
-      <c r="C82" t="n">
-        <v>15571.52</v>
-      </c>
-      <c r="D82" t="n">
-        <v>9844.49</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="3" t="n">
-        <v>46289</v>
-      </c>
-      <c r="B83" t="n">
-        <v>8149.42</v>
-      </c>
-      <c r="C83" t="n">
-        <v>22933.85</v>
-      </c>
-      <c r="D83" t="n">
-        <v>19539.77</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="3" t="n">
-        <v>46290</v>
-      </c>
-      <c r="B84" t="n">
-        <v>6607.58</v>
-      </c>
-      <c r="C84" t="n">
-        <v>31629.85</v>
-      </c>
-      <c r="D84" t="n">
-        <v>15116.29</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="3" t="n">
-        <v>46291</v>
-      </c>
-      <c r="B85" t="n">
-        <v>5849.25</v>
-      </c>
-      <c r="C85" t="n">
-        <v>19719.53</v>
-      </c>
-      <c r="D85" t="n">
-        <v>11834.96</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="3" t="n">
-        <v>46292</v>
-      </c>
-      <c r="B86" t="n">
-        <v>3790.36</v>
-      </c>
-      <c r="C86" t="n">
-        <v>9502.629999999999</v>
-      </c>
-      <c r="D86" t="n">
-        <v>6585.73</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B87" t="n">
-        <v>7540.45</v>
-      </c>
-      <c r="C87" t="n">
-        <v>18575.15</v>
-      </c>
-      <c r="D87" t="n">
-        <v>17110.17</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="3" t="n">
-        <v>46294</v>
-      </c>
-      <c r="B88" t="n">
-        <v>8665.74</v>
-      </c>
-      <c r="C88" t="n">
-        <v>16565.39</v>
-      </c>
-      <c r="D88" t="n">
-        <v>15449.29</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="3" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B89" t="n">
-        <v>7424.52</v>
-      </c>
-      <c r="C89" t="n">
-        <v>15153.6</v>
-      </c>
-      <c r="D89" t="n">
-        <v>14371.01</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="3" t="n">
-        <v>46296</v>
-      </c>
-      <c r="B90" t="n">
-        <v>8633.639999999999</v>
-      </c>
-      <c r="C90" t="n">
-        <v>16649.09</v>
-      </c>
-      <c r="D90" t="n">
-        <v>15989.16</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>Oct/26</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="3" t="n">
-        <v>46297</v>
-      </c>
-      <c r="B91" t="n">
-        <v>9278.48</v>
-      </c>
-      <c r="C91" t="n">
-        <v>16025.06</v>
-      </c>
-      <c r="D91" t="n">
-        <v>15518.65</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="3" t="n">
-        <v>46298</v>
-      </c>
-      <c r="B92" t="n">
-        <v>6912.95</v>
-      </c>
-      <c r="C92" t="n">
-        <v>12747.33</v>
-      </c>
-      <c r="D92" t="n">
-        <v>12296.48</v>
       </c>
     </row>
   </sheetData>
@@ -9399,7 +8836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I92"/>
+  <dimension ref="A1:Q92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9448,6 +8885,46 @@
           <t>Intervals</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Price_source</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Luzon_SMP_PHP_per_MWh_provisional</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Luzon_LMP_genweighted_PHP_per_MWh_provisional</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Visayas_SMP_PHP_per_MWh_provisional</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Visayas_LMP_genweighted_PHP_per_MWh_provisional</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Mindanao_SMP_PHP_per_MWh_provisional</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Mindanao_LMP_genweighted_PHP_per_MWh_provisional</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Philippines_LMP_genweighted_PHP_per_MWh_provisional</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
@@ -9506,6 +8983,11 @@
       <c r="I3" t="n">
         <v>288</v>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -9535,6 +9017,11 @@
       <c r="I4" t="n">
         <v>288</v>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -9564,6 +9051,11 @@
       <c r="I5" t="n">
         <v>288</v>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -9593,6 +9085,11 @@
       <c r="I6" t="n">
         <v>288</v>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -9622,6 +9119,11 @@
       <c r="I7" t="n">
         <v>288</v>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -9651,6 +9153,11 @@
       <c r="I8" t="n">
         <v>288</v>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -9680,6 +9187,11 @@
       <c r="I9" t="n">
         <v>288</v>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -9709,6 +9221,11 @@
       <c r="I10" t="n">
         <v>288</v>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -9738,6 +9255,11 @@
       <c r="I11" t="n">
         <v>288</v>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -9767,6 +9289,11 @@
       <c r="I12" t="n">
         <v>288</v>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -9796,6 +9323,11 @@
       <c r="I13" t="n">
         <v>288</v>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -9825,6 +9357,11 @@
       <c r="I14" t="n">
         <v>288</v>
       </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -9854,6 +9391,11 @@
       <c r="I15" t="n">
         <v>288</v>
       </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -9883,6 +9425,11 @@
       <c r="I16" t="n">
         <v>288</v>
       </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -9912,6 +9459,11 @@
       <c r="I17" t="n">
         <v>288</v>
       </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -9941,6 +9493,11 @@
       <c r="I18" t="n">
         <v>288</v>
       </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -9970,6 +9527,11 @@
       <c r="I19" t="n">
         <v>288</v>
       </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -9999,6 +9561,11 @@
       <c r="I20" t="n">
         <v>288</v>
       </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -10028,6 +9595,11 @@
       <c r="I21" t="n">
         <v>288</v>
       </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -10057,6 +9629,11 @@
       <c r="I22" t="n">
         <v>288</v>
       </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -10086,6 +9663,11 @@
       <c r="I23" t="n">
         <v>288</v>
       </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -10115,6 +9697,11 @@
       <c r="I24" t="n">
         <v>288</v>
       </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -10144,6 +9731,11 @@
       <c r="I25" t="n">
         <v>288</v>
       </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -10173,6 +9765,11 @@
       <c r="I26" t="n">
         <v>288</v>
       </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -10202,6 +9799,11 @@
       <c r="I27" t="n">
         <v>288</v>
       </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
@@ -10231,6 +9833,11 @@
       <c r="I28" t="n">
         <v>288</v>
       </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
@@ -10260,6 +9867,11 @@
       <c r="I29" t="n">
         <v>288</v>
       </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
@@ -10289,6 +9901,11 @@
       <c r="I30" t="n">
         <v>288</v>
       </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -10318,6 +9935,11 @@
       <c r="I31" t="n">
         <v>288</v>
       </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
@@ -10347,6 +9969,11 @@
       <c r="I32" t="n">
         <v>288</v>
       </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
@@ -10376,6 +10003,11 @@
       <c r="I33" t="n">
         <v>288</v>
       </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
@@ -10405,6 +10037,11 @@
       <c r="I34" t="n">
         <v>288</v>
       </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
@@ -10434,6 +10071,11 @@
       <c r="I35" t="n">
         <v>288</v>
       </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
@@ -10463,6 +10105,11 @@
       <c r="I36" t="n">
         <v>288</v>
       </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
@@ -10492,6 +10139,11 @@
       <c r="I37" t="n">
         <v>288</v>
       </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
@@ -10521,6 +10173,11 @@
       <c r="I38" t="n">
         <v>288</v>
       </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
@@ -10550,6 +10207,11 @@
       <c r="I39" t="n">
         <v>288</v>
       </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
@@ -10579,6 +10241,11 @@
       <c r="I40" t="n">
         <v>288</v>
       </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
@@ -10608,6 +10275,11 @@
       <c r="I41" t="n">
         <v>288</v>
       </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
@@ -10637,6 +10309,11 @@
       <c r="I42" t="n">
         <v>288</v>
       </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
@@ -10666,6 +10343,11 @@
       <c r="I43" t="n">
         <v>288</v>
       </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
@@ -10695,6 +10377,11 @@
       <c r="I44" t="n">
         <v>288</v>
       </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
@@ -10724,6 +10411,11 @@
       <c r="I45" t="n">
         <v>288</v>
       </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
@@ -10753,6 +10445,11 @@
       <c r="I46" t="n">
         <v>288</v>
       </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
@@ -10782,6 +10479,11 @@
       <c r="I47" t="n">
         <v>288</v>
       </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
@@ -10811,6 +10513,11 @@
       <c r="I48" t="n">
         <v>288</v>
       </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
@@ -10840,6 +10547,11 @@
       <c r="I49" t="n">
         <v>288</v>
       </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n">
@@ -10869,6 +10581,11 @@
       <c r="I50" t="n">
         <v>288</v>
       </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n">
@@ -10898,6 +10615,11 @@
       <c r="I51" t="n">
         <v>288</v>
       </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n">
@@ -10927,6 +10649,11 @@
       <c r="I52" t="n">
         <v>288</v>
       </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
@@ -10956,6 +10683,11 @@
       <c r="I53" t="n">
         <v>288</v>
       </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n">
@@ -10985,6 +10717,32 @@
       <c r="I54" t="n">
         <v>288</v>
       </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
+        <v>6078.76</v>
+      </c>
+      <c r="L54" t="n">
+        <v>5886.5</v>
+      </c>
+      <c r="M54" t="n">
+        <v>30081.21</v>
+      </c>
+      <c r="N54" t="n">
+        <v>20268.74</v>
+      </c>
+      <c r="O54" t="n">
+        <v>13872.03</v>
+      </c>
+      <c r="P54" t="n">
+        <v>14586.59</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>9044.91</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
@@ -10996,23 +10754,40 @@
       <c r="C55" t="n">
         <v>6816.7</v>
       </c>
-      <c r="D55" t="n">
-        <v>48368.45</v>
-      </c>
-      <c r="E55" t="n">
-        <v>50413.37</v>
-      </c>
       <c r="F55" t="n">
         <v>29186.79</v>
       </c>
       <c r="G55" t="n">
         <v>31061.65</v>
       </c>
-      <c r="H55" t="n">
-        <v>16980.07</v>
-      </c>
       <c r="I55" t="n">
         <v>288</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
+        <v>6870.55</v>
+      </c>
+      <c r="L55" t="n">
+        <v>6816.7</v>
+      </c>
+      <c r="M55" t="n">
+        <v>29186.79</v>
+      </c>
+      <c r="N55" t="n">
+        <v>31061.65</v>
+      </c>
+      <c r="O55" t="n">
+        <v>48368.45</v>
+      </c>
+      <c r="P55" t="n">
+        <v>50413.37</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>16980.07</v>
       </c>
     </row>
     <row r="56">
@@ -11043,6 +10818,32 @@
       <c r="I56" t="n">
         <v>288</v>
       </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>5577.55</v>
+      </c>
+      <c r="L56" t="n">
+        <v>5525.42</v>
+      </c>
+      <c r="M56" t="n">
+        <v>29490.31</v>
+      </c>
+      <c r="N56" t="n">
+        <v>30487.38</v>
+      </c>
+      <c r="O56" t="n">
+        <v>27408.76</v>
+      </c>
+      <c r="P56" t="n">
+        <v>28393.79</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>12589.5</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="n">
@@ -11072,6 +10873,32 @@
       <c r="I57" t="n">
         <v>288</v>
       </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>4168.24</v>
+      </c>
+      <c r="L57" t="n">
+        <v>3639.11</v>
+      </c>
+      <c r="M57" t="n">
+        <v>17797.34</v>
+      </c>
+      <c r="N57" t="n">
+        <v>16328.46</v>
+      </c>
+      <c r="O57" t="n">
+        <v>22339.12</v>
+      </c>
+      <c r="P57" t="n">
+        <v>24022.46</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>9117.01</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="n">
@@ -11083,23 +10910,40 @@
       <c r="C58" t="n">
         <v>24.3</v>
       </c>
-      <c r="D58" t="n">
-        <v>74656.96000000001</v>
-      </c>
-      <c r="E58" t="n">
-        <v>77904.85000000001</v>
-      </c>
       <c r="F58" t="n">
         <v>26602.37</v>
       </c>
       <c r="G58" t="n">
         <v>27178.76</v>
       </c>
-      <c r="H58" t="n">
-        <v>17921.41</v>
-      </c>
       <c r="I58" t="n">
         <v>288</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K58" t="n">
+        <v>136.17</v>
+      </c>
+      <c r="L58" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="M58" t="n">
+        <v>26602.37</v>
+      </c>
+      <c r="N58" t="n">
+        <v>27178.76</v>
+      </c>
+      <c r="O58" t="n">
+        <v>74656.96000000001</v>
+      </c>
+      <c r="P58" t="n">
+        <v>77904.85000000001</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>17921.41</v>
       </c>
     </row>
     <row r="59">
@@ -11112,23 +10956,40 @@
       <c r="C59" t="n">
         <v>802.91</v>
       </c>
-      <c r="D59" t="n">
-        <v>47646.67</v>
-      </c>
-      <c r="E59" t="n">
-        <v>49886.35</v>
-      </c>
       <c r="F59" t="n">
         <v>26283.51</v>
       </c>
       <c r="G59" t="n">
         <v>26864.61</v>
       </c>
-      <c r="H59" t="n">
-        <v>12743.32</v>
-      </c>
       <c r="I59" t="n">
         <v>288</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
+        <v>917.6799999999999</v>
+      </c>
+      <c r="L59" t="n">
+        <v>802.91</v>
+      </c>
+      <c r="M59" t="n">
+        <v>26283.51</v>
+      </c>
+      <c r="N59" t="n">
+        <v>26864.61</v>
+      </c>
+      <c r="O59" t="n">
+        <v>47646.67</v>
+      </c>
+      <c r="P59" t="n">
+        <v>49886.35</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>12743.32</v>
       </c>
     </row>
     <row r="60">
@@ -11159,6 +11020,32 @@
       <c r="I60" t="n">
         <v>288</v>
       </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K60" t="n">
+        <v>4999.71</v>
+      </c>
+      <c r="L60" t="n">
+        <v>4568.92</v>
+      </c>
+      <c r="M60" t="n">
+        <v>17592.81</v>
+      </c>
+      <c r="N60" t="n">
+        <v>12321.93</v>
+      </c>
+      <c r="O60" t="n">
+        <v>26389.21</v>
+      </c>
+      <c r="P60" t="n">
+        <v>27383.53</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>9307</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="n">
@@ -11170,23 +11057,40 @@
       <c r="C61" t="n">
         <v>4483.62</v>
       </c>
-      <c r="D61" t="n">
-        <v>78467.69</v>
-      </c>
-      <c r="E61" t="n">
-        <v>78776.75</v>
-      </c>
       <c r="F61" t="n">
         <v>21025.3</v>
       </c>
       <c r="G61" t="n">
         <v>14115.39</v>
       </c>
-      <c r="H61" t="n">
-        <v>17407.5</v>
-      </c>
       <c r="I61" t="n">
         <v>288</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K61" t="n">
+        <v>4922.72</v>
+      </c>
+      <c r="L61" t="n">
+        <v>4483.62</v>
+      </c>
+      <c r="M61" t="n">
+        <v>21025.3</v>
+      </c>
+      <c r="N61" t="n">
+        <v>14115.39</v>
+      </c>
+      <c r="O61" t="n">
+        <v>78467.69</v>
+      </c>
+      <c r="P61" t="n">
+        <v>78776.75</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>17407.5</v>
       </c>
     </row>
     <row r="62">
@@ -11199,23 +11103,40 @@
       <c r="C62" t="n">
         <v>3338.37</v>
       </c>
-      <c r="D62" t="n">
-        <v>49958.57</v>
-      </c>
-      <c r="E62" t="n">
-        <v>47342.5</v>
-      </c>
       <c r="F62" t="n">
         <v>22076.4</v>
       </c>
       <c r="G62" t="n">
         <v>15702.86</v>
       </c>
-      <c r="H62" t="n">
-        <v>12023.45</v>
-      </c>
       <c r="I62" t="n">
         <v>288</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K62" t="n">
+        <v>3924.77</v>
+      </c>
+      <c r="L62" t="n">
+        <v>3338.37</v>
+      </c>
+      <c r="M62" t="n">
+        <v>22076.4</v>
+      </c>
+      <c r="N62" t="n">
+        <v>15702.86</v>
+      </c>
+      <c r="O62" t="n">
+        <v>49958.57</v>
+      </c>
+      <c r="P62" t="n">
+        <v>47342.5</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>12023.45</v>
       </c>
     </row>
     <row r="63">
@@ -11246,6 +11167,32 @@
       <c r="I63" t="n">
         <v>288</v>
       </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K63" t="n">
+        <v>3740.97</v>
+      </c>
+      <c r="L63" t="n">
+        <v>3380.32</v>
+      </c>
+      <c r="M63" t="n">
+        <v>21027.66</v>
+      </c>
+      <c r="N63" t="n">
+        <v>12975.71</v>
+      </c>
+      <c r="O63" t="n">
+        <v>29379.65</v>
+      </c>
+      <c r="P63" t="n">
+        <v>29911.47</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>9132.57</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="n">
@@ -11257,23 +11204,37 @@
       <c r="C64" t="n">
         <v>2499.57</v>
       </c>
-      <c r="D64" t="n">
-        <v>43308.92</v>
-      </c>
-      <c r="E64" t="n">
-        <v>46940.7</v>
-      </c>
       <c r="F64" t="n">
         <v>30660.64</v>
       </c>
-      <c r="G64" t="n">
-        <v>32326.65</v>
-      </c>
-      <c r="H64" t="n">
-        <v>14214.4</v>
-      </c>
       <c r="I64" t="n">
         <v>288</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K64" t="n">
+        <v>3124.51</v>
+      </c>
+      <c r="L64" t="n">
+        <v>2499.57</v>
+      </c>
+      <c r="M64" t="n">
+        <v>30660.64</v>
+      </c>
+      <c r="N64" t="n">
+        <v>32326.65</v>
+      </c>
+      <c r="O64" t="n">
+        <v>43308.92</v>
+      </c>
+      <c r="P64" t="n">
+        <v>46940.7</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>14214.4</v>
       </c>
     </row>
     <row r="65">
@@ -11304,6 +11265,32 @@
       <c r="I65" t="n">
         <v>288</v>
       </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K65" t="n">
+        <v>-217.13</v>
+      </c>
+      <c r="L65" t="n">
+        <v>-89.97</v>
+      </c>
+      <c r="M65" t="n">
+        <v>27312.42</v>
+      </c>
+      <c r="N65" t="n">
+        <v>28945.34</v>
+      </c>
+      <c r="O65" t="n">
+        <v>28406.9</v>
+      </c>
+      <c r="P65" t="n">
+        <v>31257.98</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>9369.870000000001</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="n">
@@ -11315,23 +11302,40 @@
       <c r="C66" t="n">
         <v>3934.67</v>
       </c>
-      <c r="D66" t="n">
-        <v>54685.62</v>
-      </c>
-      <c r="E66" t="n">
-        <v>56975.6</v>
-      </c>
       <c r="F66" t="n">
         <v>28252.86</v>
       </c>
       <c r="G66" t="n">
         <v>26511.99</v>
       </c>
-      <c r="H66" t="n">
-        <v>16337.96</v>
-      </c>
       <c r="I66" t="n">
         <v>288</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K66" t="n">
+        <v>3905.22</v>
+      </c>
+      <c r="L66" t="n">
+        <v>3934.67</v>
+      </c>
+      <c r="M66" t="n">
+        <v>28252.86</v>
+      </c>
+      <c r="N66" t="n">
+        <v>26511.99</v>
+      </c>
+      <c r="O66" t="n">
+        <v>54685.62</v>
+      </c>
+      <c r="P66" t="n">
+        <v>56975.6</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>16337.96</v>
       </c>
     </row>
     <row r="67">
@@ -11344,23 +11348,40 @@
       <c r="C67" t="n">
         <v>5479.98</v>
       </c>
-      <c r="D67" t="n">
-        <v>47612.04</v>
-      </c>
-      <c r="E67" t="n">
-        <v>48776.77</v>
-      </c>
       <c r="F67" t="n">
         <v>17557.2</v>
       </c>
       <c r="G67" t="n">
         <v>14412.46</v>
       </c>
-      <c r="H67" t="n">
-        <v>14178.51</v>
-      </c>
       <c r="I67" t="n">
         <v>288</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K67" t="n">
+        <v>5819.31</v>
+      </c>
+      <c r="L67" t="n">
+        <v>5479.98</v>
+      </c>
+      <c r="M67" t="n">
+        <v>17557.2</v>
+      </c>
+      <c r="N67" t="n">
+        <v>14412.46</v>
+      </c>
+      <c r="O67" t="n">
+        <v>47612.04</v>
+      </c>
+      <c r="P67" t="n">
+        <v>48776.77</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>14178.51</v>
       </c>
     </row>
     <row r="68">
@@ -11391,6 +11412,32 @@
       <c r="I68" t="n">
         <v>288</v>
       </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K68" t="n">
+        <v>5750.53</v>
+      </c>
+      <c r="L68" t="n">
+        <v>5283.45</v>
+      </c>
+      <c r="M68" t="n">
+        <v>16668.17</v>
+      </c>
+      <c r="N68" t="n">
+        <v>10669.6</v>
+      </c>
+      <c r="O68" t="n">
+        <v>19976.6</v>
+      </c>
+      <c r="P68" t="n">
+        <v>20976.41</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>8730.049999999999</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="n">
@@ -11402,23 +11449,34 @@
       <c r="C69" t="n">
         <v>4606.51</v>
       </c>
-      <c r="D69" t="n">
-        <v>45174.82</v>
-      </c>
-      <c r="E69" t="n">
-        <v>47834.7</v>
-      </c>
-      <c r="F69" t="n">
-        <v>37921.34</v>
-      </c>
-      <c r="G69" t="n">
-        <v>36240.03</v>
-      </c>
-      <c r="H69" t="n">
-        <v>16254.06</v>
-      </c>
       <c r="I69" t="n">
         <v>288</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K69" t="n">
+        <v>5028.17</v>
+      </c>
+      <c r="L69" t="n">
+        <v>4606.51</v>
+      </c>
+      <c r="M69" t="n">
+        <v>37921.34</v>
+      </c>
+      <c r="N69" t="n">
+        <v>36240.03</v>
+      </c>
+      <c r="O69" t="n">
+        <v>45174.82</v>
+      </c>
+      <c r="P69" t="n">
+        <v>47834.7</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>16254.06</v>
       </c>
     </row>
     <row r="70">
@@ -11431,23 +11489,40 @@
       <c r="C70" t="n">
         <v>4613.94</v>
       </c>
-      <c r="D70" t="n">
-        <v>46971.34</v>
-      </c>
-      <c r="E70" t="n">
-        <v>49612.85</v>
-      </c>
       <c r="F70" t="n">
         <v>22225.63</v>
       </c>
       <c r="G70" t="n">
         <v>16679.15</v>
       </c>
-      <c r="H70" t="n">
-        <v>13859.61</v>
-      </c>
       <c r="I70" t="n">
         <v>288</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K70" t="n">
+        <v>5000.77</v>
+      </c>
+      <c r="L70" t="n">
+        <v>4613.94</v>
+      </c>
+      <c r="M70" t="n">
+        <v>22225.63</v>
+      </c>
+      <c r="N70" t="n">
+        <v>16679.15</v>
+      </c>
+      <c r="O70" t="n">
+        <v>46971.34</v>
+      </c>
+      <c r="P70" t="n">
+        <v>49612.85</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>13859.61</v>
       </c>
     </row>
     <row r="71">
@@ -11478,6 +11553,32 @@
       <c r="I71" t="n">
         <v>288</v>
       </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K71" t="n">
+        <v>4778.7</v>
+      </c>
+      <c r="L71" t="n">
+        <v>4528.16</v>
+      </c>
+      <c r="M71" t="n">
+        <v>23501.87</v>
+      </c>
+      <c r="N71" t="n">
+        <v>16785.23</v>
+      </c>
+      <c r="O71" t="n">
+        <v>20506.52</v>
+      </c>
+      <c r="P71" t="n">
+        <v>21821.57</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>8989.379999999999</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="n">
@@ -11489,23 +11590,34 @@
       <c r="C72" t="n">
         <v>1322.1</v>
       </c>
-      <c r="D72" t="n">
-        <v>36724.33</v>
-      </c>
-      <c r="E72" t="n">
-        <v>41353.34</v>
-      </c>
-      <c r="F72" t="n">
-        <v>36780</v>
-      </c>
-      <c r="G72" t="n">
-        <v>40352.72</v>
-      </c>
-      <c r="H72" t="n">
-        <v>12649.6</v>
-      </c>
       <c r="I72" t="n">
         <v>288</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K72" t="n">
+        <v>1333.23</v>
+      </c>
+      <c r="L72" t="n">
+        <v>1322.1</v>
+      </c>
+      <c r="M72" t="n">
+        <v>36780</v>
+      </c>
+      <c r="N72" t="n">
+        <v>40352.72</v>
+      </c>
+      <c r="O72" t="n">
+        <v>36724.33</v>
+      </c>
+      <c r="P72" t="n">
+        <v>41353.34</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>12649.6</v>
       </c>
     </row>
     <row r="73">
@@ -11518,23 +11630,40 @@
       <c r="C73" t="n">
         <v>5131.41</v>
       </c>
-      <c r="D73" t="n">
-        <v>45924.54</v>
-      </c>
-      <c r="E73" t="n">
-        <v>48837.97</v>
-      </c>
       <c r="F73" t="n">
         <v>20064</v>
       </c>
       <c r="G73" t="n">
         <v>22556.16</v>
       </c>
-      <c r="H73" t="n">
-        <v>14333.57</v>
-      </c>
       <c r="I73" t="n">
         <v>288</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K73" t="n">
+        <v>5117.86</v>
+      </c>
+      <c r="L73" t="n">
+        <v>5131.41</v>
+      </c>
+      <c r="M73" t="n">
+        <v>20064</v>
+      </c>
+      <c r="N73" t="n">
+        <v>22556.16</v>
+      </c>
+      <c r="O73" t="n">
+        <v>45924.54</v>
+      </c>
+      <c r="P73" t="n">
+        <v>48837.97</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>14333.57</v>
       </c>
     </row>
     <row r="74">
@@ -11547,23 +11676,40 @@
       <c r="C74" t="n">
         <v>5138.45</v>
       </c>
-      <c r="D74" t="n">
-        <v>32053.39</v>
-      </c>
-      <c r="E74" t="n">
-        <v>32612.81</v>
-      </c>
       <c r="F74" t="n">
         <v>21294.75</v>
       </c>
       <c r="G74" t="n">
         <v>22435.8</v>
       </c>
-      <c r="H74" t="n">
-        <v>11658.22</v>
-      </c>
       <c r="I74" t="n">
         <v>288</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K74" t="n">
+        <v>5304.31</v>
+      </c>
+      <c r="L74" t="n">
+        <v>5138.45</v>
+      </c>
+      <c r="M74" t="n">
+        <v>21294.75</v>
+      </c>
+      <c r="N74" t="n">
+        <v>22435.8</v>
+      </c>
+      <c r="O74" t="n">
+        <v>32053.39</v>
+      </c>
+      <c r="P74" t="n">
+        <v>32612.81</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>11658.22</v>
       </c>
     </row>
     <row r="75">
@@ -11576,23 +11722,34 @@
       <c r="C75" t="n">
         <v>4811.89</v>
       </c>
-      <c r="D75" t="n">
-        <v>33342.56</v>
-      </c>
-      <c r="E75" t="n">
-        <v>36649.44</v>
-      </c>
-      <c r="F75" t="n">
-        <v>33351.55</v>
-      </c>
-      <c r="G75" t="n">
-        <v>35528.14</v>
-      </c>
-      <c r="H75" t="n">
-        <v>13594.16</v>
-      </c>
       <c r="I75" t="n">
         <v>288</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K75" t="n">
+        <v>5146.68</v>
+      </c>
+      <c r="L75" t="n">
+        <v>4811.89</v>
+      </c>
+      <c r="M75" t="n">
+        <v>33351.55</v>
+      </c>
+      <c r="N75" t="n">
+        <v>35528.14</v>
+      </c>
+      <c r="O75" t="n">
+        <v>33342.56</v>
+      </c>
+      <c r="P75" t="n">
+        <v>36649.44</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>13594.16</v>
       </c>
     </row>
     <row r="76">
@@ -11623,6 +11780,32 @@
       <c r="I76" t="n">
         <v>288</v>
       </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K76" t="n">
+        <v>5008.53</v>
+      </c>
+      <c r="L76" t="n">
+        <v>4726.3</v>
+      </c>
+      <c r="M76" t="n">
+        <v>17011.73</v>
+      </c>
+      <c r="N76" t="n">
+        <v>18546.02</v>
+      </c>
+      <c r="O76" t="n">
+        <v>16760.48</v>
+      </c>
+      <c r="P76" t="n">
+        <v>19092.79</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>8698.24</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="n">
@@ -11652,6 +11835,32 @@
       <c r="I77" t="n">
         <v>288</v>
       </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K77" t="n">
+        <v>4748.07</v>
+      </c>
+      <c r="L77" t="n">
+        <v>4635.16</v>
+      </c>
+      <c r="M77" t="n">
+        <v>11584.08</v>
+      </c>
+      <c r="N77" t="n">
+        <v>12239.54</v>
+      </c>
+      <c r="O77" t="n">
+        <v>11565.77</v>
+      </c>
+      <c r="P77" t="n">
+        <v>12750.16</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>6919.44</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="n">
@@ -11681,6 +11890,32 @@
       <c r="I78" t="n">
         <v>288</v>
       </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K78" t="n">
+        <v>5548.56</v>
+      </c>
+      <c r="L78" t="n">
+        <v>5593.83</v>
+      </c>
+      <c r="M78" t="n">
+        <v>19003.61</v>
+      </c>
+      <c r="N78" t="n">
+        <v>18999.56</v>
+      </c>
+      <c r="O78" t="n">
+        <v>19244.37</v>
+      </c>
+      <c r="P78" t="n">
+        <v>21062.71</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>9949.85</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="n">
@@ -11710,6 +11945,32 @@
       <c r="I79" t="n">
         <v>288</v>
       </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
+        <v>6138.06</v>
+      </c>
+      <c r="L79" t="n">
+        <v>6209.01</v>
+      </c>
+      <c r="M79" t="n">
+        <v>12859.13</v>
+      </c>
+      <c r="N79" t="n">
+        <v>12940.55</v>
+      </c>
+      <c r="O79" t="n">
+        <v>12777.26</v>
+      </c>
+      <c r="P79" t="n">
+        <v>14353.45</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>8406.51</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="n">
@@ -11721,23 +11982,40 @@
       <c r="C80" t="n">
         <v>13702.61</v>
       </c>
-      <c r="D80" t="n">
-        <v>43126</v>
-      </c>
-      <c r="E80" t="n">
-        <v>48110.7</v>
-      </c>
       <c r="F80" t="n">
         <v>26991.73</v>
       </c>
       <c r="G80" t="n">
         <v>28161.95</v>
       </c>
-      <c r="H80" t="n">
-        <v>21325.63</v>
-      </c>
       <c r="I80" t="n">
         <v>288</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K80" t="n">
+        <v>13059.41</v>
+      </c>
+      <c r="L80" t="n">
+        <v>13702.61</v>
+      </c>
+      <c r="M80" t="n">
+        <v>26991.73</v>
+      </c>
+      <c r="N80" t="n">
+        <v>28161.95</v>
+      </c>
+      <c r="O80" t="n">
+        <v>43126</v>
+      </c>
+      <c r="P80" t="n">
+        <v>48110.7</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>21325.63</v>
       </c>
     </row>
     <row r="81">
@@ -11768,6 +12046,32 @@
       <c r="I81" t="n">
         <v>288</v>
       </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K81" t="n">
+        <v>8437.129999999999</v>
+      </c>
+      <c r="L81" t="n">
+        <v>8353.049999999999</v>
+      </c>
+      <c r="M81" t="n">
+        <v>11812.5</v>
+      </c>
+      <c r="N81" t="n">
+        <v>11543.64</v>
+      </c>
+      <c r="O81" t="n">
+        <v>10233.09</v>
+      </c>
+      <c r="P81" t="n">
+        <v>10177.68</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>9036.719999999999</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="n">
@@ -11797,6 +12101,32 @@
       <c r="I82" t="n">
         <v>288</v>
       </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K82" t="n">
+        <v>7752.03</v>
+      </c>
+      <c r="L82" t="n">
+        <v>7399.98</v>
+      </c>
+      <c r="M82" t="n">
+        <v>15571.52</v>
+      </c>
+      <c r="N82" t="n">
+        <v>10690.2</v>
+      </c>
+      <c r="O82" t="n">
+        <v>9844.49</v>
+      </c>
+      <c r="P82" t="n">
+        <v>9859.1</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>8201.57</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="n">
@@ -11826,6 +12156,32 @@
       <c r="I83" t="n">
         <v>288</v>
       </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K83" t="n">
+        <v>8149.42</v>
+      </c>
+      <c r="L83" t="n">
+        <v>8088.92</v>
+      </c>
+      <c r="M83" t="n">
+        <v>22933.85</v>
+      </c>
+      <c r="N83" t="n">
+        <v>23195.61</v>
+      </c>
+      <c r="O83" t="n">
+        <v>19539.77</v>
+      </c>
+      <c r="P83" t="n">
+        <v>21286.87</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>12071.94</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="n">
@@ -11846,14 +12202,34 @@
       <c r="F84" t="n">
         <v>31629.85</v>
       </c>
-      <c r="G84" t="n">
-        <v>33322.01</v>
-      </c>
-      <c r="H84" t="n">
-        <v>11302.01</v>
-      </c>
       <c r="I84" t="n">
         <v>288</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
+        <v>6607.58</v>
+      </c>
+      <c r="L84" t="n">
+        <v>6536.35</v>
+      </c>
+      <c r="M84" t="n">
+        <v>31629.85</v>
+      </c>
+      <c r="N84" t="n">
+        <v>33322.01</v>
+      </c>
+      <c r="O84" t="n">
+        <v>15116.29</v>
+      </c>
+      <c r="P84" t="n">
+        <v>16720.52</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>11302.01</v>
       </c>
     </row>
     <row r="85">
@@ -11884,6 +12260,32 @@
       <c r="I85" t="n">
         <v>288</v>
       </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K85" t="n">
+        <v>5849.25</v>
+      </c>
+      <c r="L85" t="n">
+        <v>5857.78</v>
+      </c>
+      <c r="M85" t="n">
+        <v>19719.53</v>
+      </c>
+      <c r="N85" t="n">
+        <v>20076.13</v>
+      </c>
+      <c r="O85" t="n">
+        <v>11834.96</v>
+      </c>
+      <c r="P85" t="n">
+        <v>13035.29</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>8667.84</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="n">
@@ -11913,6 +12315,32 @@
       <c r="I86" t="n">
         <v>288</v>
       </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K86" t="n">
+        <v>3790.36</v>
+      </c>
+      <c r="L86" t="n">
+        <v>3888.29</v>
+      </c>
+      <c r="M86" t="n">
+        <v>9502.629999999999</v>
+      </c>
+      <c r="N86" t="n">
+        <v>9520.540000000001</v>
+      </c>
+      <c r="O86" t="n">
+        <v>6585.73</v>
+      </c>
+      <c r="P86" t="n">
+        <v>7588.19</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>5139.19</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="n">
@@ -11942,6 +12370,32 @@
       <c r="I87" t="n">
         <v>288</v>
       </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K87" t="n">
+        <v>7540.45</v>
+      </c>
+      <c r="L87" t="n">
+        <v>7474.02</v>
+      </c>
+      <c r="M87" t="n">
+        <v>18575.15</v>
+      </c>
+      <c r="N87" t="n">
+        <v>19322.75</v>
+      </c>
+      <c r="O87" t="n">
+        <v>17110.17</v>
+      </c>
+      <c r="P87" t="n">
+        <v>18755.44</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>10733.01</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="n">
@@ -11971,6 +12425,32 @@
       <c r="I88" t="n">
         <v>288</v>
       </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K88" t="n">
+        <v>8665.74</v>
+      </c>
+      <c r="L88" t="n">
+        <v>8627.690000000001</v>
+      </c>
+      <c r="M88" t="n">
+        <v>16565.39</v>
+      </c>
+      <c r="N88" t="n">
+        <v>17052.1</v>
+      </c>
+      <c r="O88" t="n">
+        <v>15449.29</v>
+      </c>
+      <c r="P88" t="n">
+        <v>16620.05</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>10962.8</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="n">
@@ -12000,6 +12480,32 @@
       <c r="I89" t="n">
         <v>288</v>
       </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K89" t="n">
+        <v>7424.52</v>
+      </c>
+      <c r="L89" t="n">
+        <v>7313.39</v>
+      </c>
+      <c r="M89" t="n">
+        <v>15153.6</v>
+      </c>
+      <c r="N89" t="n">
+        <v>15215.64</v>
+      </c>
+      <c r="O89" t="n">
+        <v>14371.01</v>
+      </c>
+      <c r="P89" t="n">
+        <v>15863.35</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>9680.059999999999</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="n">
@@ -12029,6 +12535,32 @@
       <c r="I90" t="n">
         <v>288</v>
       </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K90" t="n">
+        <v>8633.639999999999</v>
+      </c>
+      <c r="L90" t="n">
+        <v>8562.48</v>
+      </c>
+      <c r="M90" t="n">
+        <v>16649.09</v>
+      </c>
+      <c r="N90" t="n">
+        <v>16998.94</v>
+      </c>
+      <c r="O90" t="n">
+        <v>15989.16</v>
+      </c>
+      <c r="P90" t="n">
+        <v>17263.16</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>11037.45</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="n">
@@ -12058,6 +12590,32 @@
       <c r="I91" t="n">
         <v>288</v>
       </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K91" t="n">
+        <v>9278.48</v>
+      </c>
+      <c r="L91" t="n">
+        <v>9011.129999999999</v>
+      </c>
+      <c r="M91" t="n">
+        <v>16025.06</v>
+      </c>
+      <c r="N91" t="n">
+        <v>16139.82</v>
+      </c>
+      <c r="O91" t="n">
+        <v>15518.65</v>
+      </c>
+      <c r="P91" t="n">
+        <v>16249.47</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>11096.66</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="n">
@@ -12086,6 +12644,32 @@
       </c>
       <c r="I92" t="n">
         <v>288</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K92" t="n">
+        <v>6912.95</v>
+      </c>
+      <c r="L92" t="n">
+        <v>6741.95</v>
+      </c>
+      <c r="M92" t="n">
+        <v>12747.33</v>
+      </c>
+      <c r="N92" t="n">
+        <v>12696.09</v>
+      </c>
+      <c r="O92" t="n">
+        <v>12296.48</v>
+      </c>
+      <c r="P92" t="n">
+        <v>13441.88</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>8587.59</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/philippines_power_market.xlsx
+++ b/output/Data and Chart Outputs/philippines_power_market.xlsx
@@ -157,6 +157,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Philippines WESM demand by grid (IEMOP, daily average) (to Oct/26)</a:t>
             </a:r>
           </a:p>
@@ -186,12 +187,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$E$2:$E$92</f>
+              <f>'Chart'!$E$2:$E$116</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$92</f>
+              <f>'Chart'!$B$2:$B$116</f>
             </numRef>
           </val>
         </ser>
@@ -214,12 +215,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$E$2:$E$92</f>
+              <f>'Chart'!$E$2:$E$116</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$92</f>
+              <f>'Chart'!$C$2:$C$116</f>
             </numRef>
           </val>
         </ser>
@@ -242,12 +243,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$E$2:$E$92</f>
+              <f>'Chart'!$E$2:$E$116</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$92</f>
+              <f>'Chart'!$D$2:$D$116</f>
             </numRef>
           </val>
         </ser>
@@ -345,7 +346,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Philippines WESM system marginal price by grid (IEMOP final prices, daily average) (to Aug/26)</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>Philippines WESM system marginal price by grid (IEMOP final prices, daily average) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -381,12 +383,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - Prices'!$E$2:$E$52</f>
+              <f>'Chart - Prices'!$E$2:$E$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Prices'!$B$2:$B$52</f>
+              <f>'Chart - Prices'!$B$2:$B$83</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -417,12 +419,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - Prices'!$E$2:$E$52</f>
+              <f>'Chart - Prices'!$E$2:$E$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Prices'!$C$2:$C$52</f>
+              <f>'Chart - Prices'!$C$2:$C$83</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -453,12 +455,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - Prices'!$E$2:$E$52</f>
+              <f>'Chart - Prices'!$E$2:$E$83</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - Prices'!$D$2:$D$52</f>
+              <f>'Chart - Prices'!$D$2:$D$83</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -940,7 +942,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Demand from 2026-07-05 to 2026-10-03; prices from 2026-07-05 to 2026-10-03. IEMOP lists about 90 days of files; older days are kept from previous runs. Grid-connected WESM regions (Mindanao joined WESM in 2023); off-grid islands are not included.</t>
+          <t>Demand from 2026-07-05 to 2026-10-27; prices from 2026-07-05 to 2026-10-27. IEMOP lists about 90 days of files; older days are kept from previous runs. Grid-connected WESM regions (Mindanao joined WESM in 2023); off-grid islands are not included.</t>
         </is>
       </c>
     </row>
@@ -970,7 +972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E92"/>
+  <dimension ref="A1:E116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2295,6 +2297,342 @@
       </c>
       <c r="D92" t="n">
         <v>2023.1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B93" t="n">
+        <v>9671.799999999999</v>
+      </c>
+      <c r="C93" t="n">
+        <v>1911</v>
+      </c>
+      <c r="D93" t="n">
+        <v>1892.4</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B94" t="n">
+        <v>10702.3</v>
+      </c>
+      <c r="C94" t="n">
+        <v>2101.8</v>
+      </c>
+      <c r="D94" t="n">
+        <v>2079.3</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B95" t="n">
+        <v>10675.1</v>
+      </c>
+      <c r="C95" t="n">
+        <v>2100</v>
+      </c>
+      <c r="D95" t="n">
+        <v>2070.1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B96" t="n">
+        <v>10714</v>
+      </c>
+      <c r="C96" t="n">
+        <v>2094.9</v>
+      </c>
+      <c r="D96" t="n">
+        <v>2059.4</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B97" t="n">
+        <v>10427.1</v>
+      </c>
+      <c r="C97" t="n">
+        <v>2108.5</v>
+      </c>
+      <c r="D97" t="n">
+        <v>2069.1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B98" t="n">
+        <v>10434.7</v>
+      </c>
+      <c r="C98" t="n">
+        <v>2049.6</v>
+      </c>
+      <c r="D98" t="n">
+        <v>2062.6</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B99" t="n">
+        <v>10084.6</v>
+      </c>
+      <c r="C99" t="n">
+        <v>1996.7</v>
+      </c>
+      <c r="D99" t="n">
+        <v>1961.6</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B100" t="n">
+        <v>9209</v>
+      </c>
+      <c r="C100" t="n">
+        <v>1909.8</v>
+      </c>
+      <c r="D100" t="n">
+        <v>1891</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B101" t="n">
+        <v>10120.5</v>
+      </c>
+      <c r="C101" t="n">
+        <v>2108.3</v>
+      </c>
+      <c r="D101" t="n">
+        <v>2103.9</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B102" t="n">
+        <v>10452.6</v>
+      </c>
+      <c r="C102" t="n">
+        <v>2116.3</v>
+      </c>
+      <c r="D102" t="n">
+        <v>2128.6</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B103" t="n">
+        <v>10496.9</v>
+      </c>
+      <c r="C103" t="n">
+        <v>2087.8</v>
+      </c>
+      <c r="D103" t="n">
+        <v>2108.1</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B104" t="n">
+        <v>10547.8</v>
+      </c>
+      <c r="C104" t="n">
+        <v>2101.7</v>
+      </c>
+      <c r="D104" t="n">
+        <v>2108.1</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B105" t="n">
+        <v>10560.8</v>
+      </c>
+      <c r="C105" t="n">
+        <v>2093.8</v>
+      </c>
+      <c r="D105" t="n">
+        <v>2072.9</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B106" t="n">
+        <v>10216.1</v>
+      </c>
+      <c r="C106" t="n">
+        <v>2026.7</v>
+      </c>
+      <c r="D106" t="n">
+        <v>2014.6</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B107" t="n">
+        <v>9561.200000000001</v>
+      </c>
+      <c r="C107" t="n">
+        <v>1938.9</v>
+      </c>
+      <c r="D107" t="n">
+        <v>1951</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B108" t="n">
+        <v>10627.1</v>
+      </c>
+      <c r="C108" t="n">
+        <v>2142.2</v>
+      </c>
+      <c r="D108" t="n">
+        <v>2187.8</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B109" t="n">
+        <v>10994.1</v>
+      </c>
+      <c r="C109" t="n">
+        <v>2188.6</v>
+      </c>
+      <c r="D109" t="n">
+        <v>2201.8</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B110" t="n">
+        <v>11268</v>
+      </c>
+      <c r="C110" t="n">
+        <v>2214.6</v>
+      </c>
+      <c r="D110" t="n">
+        <v>2213.3</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B111" t="n">
+        <v>11170</v>
+      </c>
+      <c r="C111" t="n">
+        <v>2199.5</v>
+      </c>
+      <c r="D111" t="n">
+        <v>2229.3</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B112" t="n">
+        <v>10798</v>
+      </c>
+      <c r="C112" t="n">
+        <v>2093.3</v>
+      </c>
+      <c r="D112" t="n">
+        <v>2203.5</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B113" t="n">
+        <v>10232.6</v>
+      </c>
+      <c r="C113" t="n">
+        <v>1947.8</v>
+      </c>
+      <c r="D113" t="n">
+        <v>2079.1</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B114" t="n">
+        <v>9614.700000000001</v>
+      </c>
+      <c r="C114" t="n">
+        <v>1840.8</v>
+      </c>
+      <c r="D114" t="n">
+        <v>1937.7</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B115" t="n">
+        <v>10728.9</v>
+      </c>
+      <c r="C115" t="n">
+        <v>2098.6</v>
+      </c>
+      <c r="D115" t="n">
+        <v>2143.1</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B116" t="n">
+        <v>10936</v>
+      </c>
+      <c r="C116" t="n">
+        <v>2142.9</v>
+      </c>
+      <c r="D116" t="n">
+        <v>2188.3</v>
       </c>
     </row>
   </sheetData>
@@ -2309,7 +2647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3064,6 +3402,445 @@
       </c>
       <c r="D52" t="n">
         <v>15772.83</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B53" t="n">
+        <v>6873.25</v>
+      </c>
+      <c r="C53" t="n">
+        <v>10481.38</v>
+      </c>
+      <c r="D53" t="n">
+        <v>9322.67</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B54" t="n">
+        <v>7656.06</v>
+      </c>
+      <c r="C54" t="n">
+        <v>12623.77</v>
+      </c>
+      <c r="D54" t="n">
+        <v>13905.53</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B55" t="n">
+        <v>5605.03</v>
+      </c>
+      <c r="C55" t="n">
+        <v>15444.54</v>
+      </c>
+      <c r="D55" t="n">
+        <v>15304.79</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B56" t="n">
+        <v>3736.58</v>
+      </c>
+      <c r="C56" t="n">
+        <v>10651.32</v>
+      </c>
+      <c r="D56" t="n">
+        <v>9341.290000000001</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="n">
+        <v>46264</v>
+      </c>
+      <c r="B57" t="n">
+        <v>-176.35</v>
+      </c>
+      <c r="C57" t="n">
+        <v>12130.43</v>
+      </c>
+      <c r="D57" t="n">
+        <v>13992.86</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B58" t="n">
+        <v>564.6799999999999</v>
+      </c>
+      <c r="C58" t="n">
+        <v>13786.92</v>
+      </c>
+      <c r="D58" t="n">
+        <v>15438.84</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B59" t="n">
+        <v>4639.04</v>
+      </c>
+      <c r="C59" t="n">
+        <v>11853.13</v>
+      </c>
+      <c r="D59" t="n">
+        <v>9344.139999999999</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Sep/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B60" t="n">
+        <v>4679.14</v>
+      </c>
+      <c r="C60" t="n">
+        <v>12020.06</v>
+      </c>
+      <c r="D60" t="n">
+        <v>13814.28</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B61" t="n">
+        <v>3498.94</v>
+      </c>
+      <c r="C61" t="n">
+        <v>13171.76</v>
+      </c>
+      <c r="D61" t="n">
+        <v>15731.22</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B62" t="n">
+        <v>3426.25</v>
+      </c>
+      <c r="C62" t="n">
+        <v>11971.85</v>
+      </c>
+      <c r="D62" t="n">
+        <v>9342.450000000001</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B63" t="n">
+        <v>2584.47</v>
+      </c>
+      <c r="C63" t="n">
+        <v>11671.23</v>
+      </c>
+      <c r="D63" t="n">
+        <v>13642.77</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B64" t="n">
+        <v>-322.62</v>
+      </c>
+      <c r="C64" t="n">
+        <v>12473.17</v>
+      </c>
+      <c r="D64" t="n">
+        <v>12809.84</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B65" t="n">
+        <v>3901.67</v>
+      </c>
+      <c r="C65" t="n">
+        <v>13740.55</v>
+      </c>
+      <c r="D65" t="n">
+        <v>12225.79</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B66" t="n">
+        <v>5622.6</v>
+      </c>
+      <c r="C66" t="n">
+        <v>11265.71</v>
+      </c>
+      <c r="D66" t="n">
+        <v>13678.62</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B67" t="n">
+        <v>5448.04</v>
+      </c>
+      <c r="C67" t="n">
+        <v>11433.48</v>
+      </c>
+      <c r="D67" t="n">
+        <v>12656.22</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B68" t="n">
+        <v>4831.19</v>
+      </c>
+      <c r="C68" t="n">
+        <v>14860.35</v>
+      </c>
+      <c r="D68" t="n">
+        <v>11987.1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B69" t="n">
+        <v>4744.52</v>
+      </c>
+      <c r="C69" t="n">
+        <v>11374.15</v>
+      </c>
+      <c r="D69" t="n">
+        <v>13574.06</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="n">
+        <v>46277</v>
+      </c>
+      <c r="B70" t="n">
+        <v>4775.23</v>
+      </c>
+      <c r="C70" t="n">
+        <v>11588.55</v>
+      </c>
+      <c r="D70" t="n">
+        <v>12606.14</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B71" t="n">
+        <v>1319.7</v>
+      </c>
+      <c r="C71" t="n">
+        <v>13180.25</v>
+      </c>
+      <c r="D71" t="n">
+        <v>10642.35</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B72" t="n">
+        <v>5067.07</v>
+      </c>
+      <c r="C72" t="n">
+        <v>12706.07</v>
+      </c>
+      <c r="D72" t="n">
+        <v>14970.03</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B73" t="n">
+        <v>5344.56</v>
+      </c>
+      <c r="C73" t="n">
+        <v>10740.2</v>
+      </c>
+      <c r="D73" t="n">
+        <v>11339.33</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B74" t="n">
+        <v>5066.79</v>
+      </c>
+      <c r="C74" t="n">
+        <v>15128.05</v>
+      </c>
+      <c r="D74" t="n">
+        <v>12038.65</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B75" t="n">
+        <v>4847.99</v>
+      </c>
+      <c r="C75" t="n">
+        <v>10265.19</v>
+      </c>
+      <c r="D75" t="n">
+        <v>11388.88</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B76" t="n">
+        <v>4860.73</v>
+      </c>
+      <c r="C76" t="n">
+        <v>10483.34</v>
+      </c>
+      <c r="D76" t="n">
+        <v>10453.8</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B77" t="n">
+        <v>5558.36</v>
+      </c>
+      <c r="C77" t="n">
+        <v>13970.38</v>
+      </c>
+      <c r="D77" t="n">
+        <v>13665.48</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B78" t="n">
+        <v>6141.66</v>
+      </c>
+      <c r="C78" t="n">
+        <v>11483.58</v>
+      </c>
+      <c r="D78" t="n">
+        <v>11252.32</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B79" t="n">
+        <v>12782.6</v>
+      </c>
+      <c r="C79" t="n">
+        <v>13011.37</v>
+      </c>
+      <c r="D79" t="n">
+        <v>12161.29</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B80" t="n">
+        <v>12749.34</v>
+      </c>
+      <c r="C80" t="n">
+        <v>12562.2</v>
+      </c>
+      <c r="D80" t="n">
+        <v>12549.41</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B81" t="n">
+        <v>9860.48</v>
+      </c>
+      <c r="C81" t="n">
+        <v>12357.27</v>
+      </c>
+      <c r="D81" t="n">
+        <v>12518.28</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B82" t="n">
+        <v>8153.6</v>
+      </c>
+      <c r="C82" t="n">
+        <v>14182.21</v>
+      </c>
+      <c r="D82" t="n">
+        <v>12174.27</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B83" t="n">
+        <v>6599.24</v>
+      </c>
+      <c r="C83" t="n">
+        <v>11947.62</v>
+      </c>
+      <c r="D83" t="n">
+        <v>11247.4</v>
       </c>
     </row>
   </sheetData>
@@ -3078,7 +3855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T92"/>
+  <dimension ref="A1:T116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8822,6 +9599,1494 @@
         <v>341685.1</v>
       </c>
       <c r="T92" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B93" t="n">
+        <v>9671.799999999999</v>
+      </c>
+      <c r="C93" t="n">
+        <v>10900.4</v>
+      </c>
+      <c r="D93" t="n">
+        <v>232122</v>
+      </c>
+      <c r="E93" t="n">
+        <v>239075.4</v>
+      </c>
+      <c r="F93" t="n">
+        <v>3296.4</v>
+      </c>
+      <c r="G93" t="n">
+        <v>1892.4</v>
+      </c>
+      <c r="H93" t="n">
+        <v>2306.9</v>
+      </c>
+      <c r="I93" t="n">
+        <v>45418.5</v>
+      </c>
+      <c r="J93" t="n">
+        <v>51020.2</v>
+      </c>
+      <c r="K93" t="n">
+        <v>1210.1</v>
+      </c>
+      <c r="L93" t="n">
+        <v>1911</v>
+      </c>
+      <c r="M93" t="n">
+        <v>2291.5</v>
+      </c>
+      <c r="N93" t="n">
+        <v>45863.8</v>
+      </c>
+      <c r="O93" t="n">
+        <v>44737.6</v>
+      </c>
+      <c r="P93" t="n">
+        <v>444.6</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>13475.7</v>
+      </c>
+      <c r="R93" t="n">
+        <v>15447.8</v>
+      </c>
+      <c r="S93" t="n">
+        <v>323417</v>
+      </c>
+      <c r="T93" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B94" t="n">
+        <v>10702.3</v>
+      </c>
+      <c r="C94" t="n">
+        <v>12777.2</v>
+      </c>
+      <c r="D94" t="n">
+        <v>256854.9</v>
+      </c>
+      <c r="E94" t="n">
+        <v>261753.7</v>
+      </c>
+      <c r="F94" t="n">
+        <v>4510.2</v>
+      </c>
+      <c r="G94" t="n">
+        <v>2079.3</v>
+      </c>
+      <c r="H94" t="n">
+        <v>2500.9</v>
+      </c>
+      <c r="I94" t="n">
+        <v>49904.1</v>
+      </c>
+      <c r="J94" t="n">
+        <v>56900</v>
+      </c>
+      <c r="K94" t="n">
+        <v>1231.8</v>
+      </c>
+      <c r="L94" t="n">
+        <v>2101.8</v>
+      </c>
+      <c r="M94" t="n">
+        <v>2525.9</v>
+      </c>
+      <c r="N94" t="n">
+        <v>50443.1</v>
+      </c>
+      <c r="O94" t="n">
+        <v>46203.6</v>
+      </c>
+      <c r="P94" t="n">
+        <v>486.7</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>14887.5</v>
+      </c>
+      <c r="R94" t="n">
+        <v>17631.6</v>
+      </c>
+      <c r="S94" t="n">
+        <v>357299</v>
+      </c>
+      <c r="T94" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B95" t="n">
+        <v>10675.1</v>
+      </c>
+      <c r="C95" t="n">
+        <v>12679.5</v>
+      </c>
+      <c r="D95" t="n">
+        <v>256202.9</v>
+      </c>
+      <c r="E95" t="n">
+        <v>262203.6</v>
+      </c>
+      <c r="F95" t="n">
+        <v>4585.4</v>
+      </c>
+      <c r="G95" t="n">
+        <v>2070.1</v>
+      </c>
+      <c r="H95" t="n">
+        <v>2432.8</v>
+      </c>
+      <c r="I95" t="n">
+        <v>49683.5</v>
+      </c>
+      <c r="J95" t="n">
+        <v>58827</v>
+      </c>
+      <c r="K95" t="n">
+        <v>1343.6</v>
+      </c>
+      <c r="L95" t="n">
+        <v>2100</v>
+      </c>
+      <c r="M95" t="n">
+        <v>2423.6</v>
+      </c>
+      <c r="N95" t="n">
+        <v>50399.2</v>
+      </c>
+      <c r="O95" t="n">
+        <v>46034</v>
+      </c>
+      <c r="P95" t="n">
+        <v>558</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>14849.5</v>
+      </c>
+      <c r="R95" t="n">
+        <v>17432.8</v>
+      </c>
+      <c r="S95" t="n">
+        <v>356389</v>
+      </c>
+      <c r="T95" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B96" t="n">
+        <v>10714</v>
+      </c>
+      <c r="C96" t="n">
+        <v>12311.9</v>
+      </c>
+      <c r="D96" t="n">
+        <v>257135.7</v>
+      </c>
+      <c r="E96" t="n">
+        <v>262556.6</v>
+      </c>
+      <c r="F96" t="n">
+        <v>4861.7</v>
+      </c>
+      <c r="G96" t="n">
+        <v>2059.4</v>
+      </c>
+      <c r="H96" t="n">
+        <v>2412.7</v>
+      </c>
+      <c r="I96" t="n">
+        <v>49424.6</v>
+      </c>
+      <c r="J96" t="n">
+        <v>59301.9</v>
+      </c>
+      <c r="K96" t="n">
+        <v>1387.9</v>
+      </c>
+      <c r="L96" t="n">
+        <v>2094.9</v>
+      </c>
+      <c r="M96" t="n">
+        <v>2421.3</v>
+      </c>
+      <c r="N96" t="n">
+        <v>50277.6</v>
+      </c>
+      <c r="O96" t="n">
+        <v>46140.2</v>
+      </c>
+      <c r="P96" t="n">
+        <v>564.1</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>14872</v>
+      </c>
+      <c r="R96" t="n">
+        <v>17101.3</v>
+      </c>
+      <c r="S96" t="n">
+        <v>356928.5</v>
+      </c>
+      <c r="T96" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B97" t="n">
+        <v>10427.1</v>
+      </c>
+      <c r="C97" t="n">
+        <v>11814.9</v>
+      </c>
+      <c r="D97" t="n">
+        <v>250249.6</v>
+      </c>
+      <c r="E97" t="n">
+        <v>255982.3</v>
+      </c>
+      <c r="F97" t="n">
+        <v>4572.4</v>
+      </c>
+      <c r="G97" t="n">
+        <v>2069.1</v>
+      </c>
+      <c r="H97" t="n">
+        <v>2460.5</v>
+      </c>
+      <c r="I97" t="n">
+        <v>49657.5</v>
+      </c>
+      <c r="J97" t="n">
+        <v>59557.3</v>
+      </c>
+      <c r="K97" t="n">
+        <v>1376.5</v>
+      </c>
+      <c r="L97" t="n">
+        <v>2108.5</v>
+      </c>
+      <c r="M97" t="n">
+        <v>2442.1</v>
+      </c>
+      <c r="N97" t="n">
+        <v>50602.8</v>
+      </c>
+      <c r="O97" t="n">
+        <v>46660.1</v>
+      </c>
+      <c r="P97" t="n">
+        <v>568</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>14609.3</v>
+      </c>
+      <c r="R97" t="n">
+        <v>16695.6</v>
+      </c>
+      <c r="S97" t="n">
+        <v>350624.1</v>
+      </c>
+      <c r="T97" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B98" t="n">
+        <v>10434.7</v>
+      </c>
+      <c r="C98" t="n">
+        <v>12015.5</v>
+      </c>
+      <c r="D98" t="n">
+        <v>250433.9</v>
+      </c>
+      <c r="E98" t="n">
+        <v>254645.6</v>
+      </c>
+      <c r="F98" t="n">
+        <v>4435.1</v>
+      </c>
+      <c r="G98" t="n">
+        <v>2062.6</v>
+      </c>
+      <c r="H98" t="n">
+        <v>2416.9</v>
+      </c>
+      <c r="I98" t="n">
+        <v>49501.5</v>
+      </c>
+      <c r="J98" t="n">
+        <v>59508.2</v>
+      </c>
+      <c r="K98" t="n">
+        <v>1374.2</v>
+      </c>
+      <c r="L98" t="n">
+        <v>2049.6</v>
+      </c>
+      <c r="M98" t="n">
+        <v>2357.5</v>
+      </c>
+      <c r="N98" t="n">
+        <v>49190.3</v>
+      </c>
+      <c r="O98" t="n">
+        <v>44708.3</v>
+      </c>
+      <c r="P98" t="n">
+        <v>495.5</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>14550.1</v>
+      </c>
+      <c r="R98" t="n">
+        <v>16660</v>
+      </c>
+      <c r="S98" t="n">
+        <v>349203.5</v>
+      </c>
+      <c r="T98" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B99" t="n">
+        <v>10084.6</v>
+      </c>
+      <c r="C99" t="n">
+        <v>11316.6</v>
+      </c>
+      <c r="D99" t="n">
+        <v>242030.1</v>
+      </c>
+      <c r="E99" t="n">
+        <v>246459</v>
+      </c>
+      <c r="F99" t="n">
+        <v>4217.9</v>
+      </c>
+      <c r="G99" t="n">
+        <v>1961.6</v>
+      </c>
+      <c r="H99" t="n">
+        <v>2343.5</v>
+      </c>
+      <c r="I99" t="n">
+        <v>47078</v>
+      </c>
+      <c r="J99" t="n">
+        <v>57463.8</v>
+      </c>
+      <c r="K99" t="n">
+        <v>1399.7</v>
+      </c>
+      <c r="L99" t="n">
+        <v>1996.7</v>
+      </c>
+      <c r="M99" t="n">
+        <v>2339.8</v>
+      </c>
+      <c r="N99" t="n">
+        <v>47920.4</v>
+      </c>
+      <c r="O99" t="n">
+        <v>42727.6</v>
+      </c>
+      <c r="P99" t="n">
+        <v>474.1</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>14045.3</v>
+      </c>
+      <c r="R99" t="n">
+        <v>15915.7</v>
+      </c>
+      <c r="S99" t="n">
+        <v>337086.2</v>
+      </c>
+      <c r="T99" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B100" t="n">
+        <v>9209</v>
+      </c>
+      <c r="C100" t="n">
+        <v>10419.7</v>
+      </c>
+      <c r="D100" t="n">
+        <v>221015.4</v>
+      </c>
+      <c r="E100" t="n">
+        <v>227862</v>
+      </c>
+      <c r="F100" t="n">
+        <v>3891.7</v>
+      </c>
+      <c r="G100" t="n">
+        <v>1891</v>
+      </c>
+      <c r="H100" t="n">
+        <v>2318.6</v>
+      </c>
+      <c r="I100" t="n">
+        <v>45384.9</v>
+      </c>
+      <c r="J100" t="n">
+        <v>53864.3</v>
+      </c>
+      <c r="K100" t="n">
+        <v>1348.6</v>
+      </c>
+      <c r="L100" t="n">
+        <v>1909.8</v>
+      </c>
+      <c r="M100" t="n">
+        <v>2300.6</v>
+      </c>
+      <c r="N100" t="n">
+        <v>45834.7</v>
+      </c>
+      <c r="O100" t="n">
+        <v>39925.3</v>
+      </c>
+      <c r="P100" t="n">
+        <v>457.2</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>13011.6</v>
+      </c>
+      <c r="R100" t="n">
+        <v>14935.5</v>
+      </c>
+      <c r="S100" t="n">
+        <v>312278</v>
+      </c>
+      <c r="T100" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B101" t="n">
+        <v>10120.5</v>
+      </c>
+      <c r="C101" t="n">
+        <v>11767.9</v>
+      </c>
+      <c r="D101" t="n">
+        <v>242891.5</v>
+      </c>
+      <c r="E101" t="n">
+        <v>249722.1</v>
+      </c>
+      <c r="F101" t="n">
+        <v>4357.1</v>
+      </c>
+      <c r="G101" t="n">
+        <v>2103.9</v>
+      </c>
+      <c r="H101" t="n">
+        <v>2547.8</v>
+      </c>
+      <c r="I101" t="n">
+        <v>50493.6</v>
+      </c>
+      <c r="J101" t="n">
+        <v>60198.2</v>
+      </c>
+      <c r="K101" t="n">
+        <v>1338.2</v>
+      </c>
+      <c r="L101" t="n">
+        <v>2108.3</v>
+      </c>
+      <c r="M101" t="n">
+        <v>2503.5</v>
+      </c>
+      <c r="N101" t="n">
+        <v>50599.5</v>
+      </c>
+      <c r="O101" t="n">
+        <v>43716.8</v>
+      </c>
+      <c r="P101" t="n">
+        <v>515.1</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>14336</v>
+      </c>
+      <c r="R101" t="n">
+        <v>16758</v>
+      </c>
+      <c r="S101" t="n">
+        <v>344064.3</v>
+      </c>
+      <c r="T101" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B102" t="n">
+        <v>10452.6</v>
+      </c>
+      <c r="C102" t="n">
+        <v>11949.9</v>
+      </c>
+      <c r="D102" t="n">
+        <v>250862.6</v>
+      </c>
+      <c r="E102" t="n">
+        <v>256740.4</v>
+      </c>
+      <c r="F102" t="n">
+        <v>4318.4</v>
+      </c>
+      <c r="G102" t="n">
+        <v>2128.6</v>
+      </c>
+      <c r="H102" t="n">
+        <v>2527.6</v>
+      </c>
+      <c r="I102" t="n">
+        <v>51087.3</v>
+      </c>
+      <c r="J102" t="n">
+        <v>61612.7</v>
+      </c>
+      <c r="K102" t="n">
+        <v>1404.6</v>
+      </c>
+      <c r="L102" t="n">
+        <v>2116.3</v>
+      </c>
+      <c r="M102" t="n">
+        <v>2492.7</v>
+      </c>
+      <c r="N102" t="n">
+        <v>50790.5</v>
+      </c>
+      <c r="O102" t="n">
+        <v>44704.1</v>
+      </c>
+      <c r="P102" t="n">
+        <v>484.9</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>14701.8</v>
+      </c>
+      <c r="R102" t="n">
+        <v>16837.9</v>
+      </c>
+      <c r="S102" t="n">
+        <v>352843.3</v>
+      </c>
+      <c r="T102" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B103" t="n">
+        <v>10496.9</v>
+      </c>
+      <c r="C103" t="n">
+        <v>11983.7</v>
+      </c>
+      <c r="D103" t="n">
+        <v>251925.6</v>
+      </c>
+      <c r="E103" t="n">
+        <v>257372</v>
+      </c>
+      <c r="F103" t="n">
+        <v>4410</v>
+      </c>
+      <c r="G103" t="n">
+        <v>2108.1</v>
+      </c>
+      <c r="H103" t="n">
+        <v>2494.3</v>
+      </c>
+      <c r="I103" t="n">
+        <v>50594</v>
+      </c>
+      <c r="J103" t="n">
+        <v>58522.1</v>
+      </c>
+      <c r="K103" t="n">
+        <v>1322.3</v>
+      </c>
+      <c r="L103" t="n">
+        <v>2087.8</v>
+      </c>
+      <c r="M103" t="n">
+        <v>2435.9</v>
+      </c>
+      <c r="N103" t="n">
+        <v>50107.3</v>
+      </c>
+      <c r="O103" t="n">
+        <v>45968.6</v>
+      </c>
+      <c r="P103" t="n">
+        <v>495.2</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>14696.8</v>
+      </c>
+      <c r="R103" t="n">
+        <v>16732.2</v>
+      </c>
+      <c r="S103" t="n">
+        <v>352722.3</v>
+      </c>
+      <c r="T103" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B104" t="n">
+        <v>10547.8</v>
+      </c>
+      <c r="C104" t="n">
+        <v>12107.5</v>
+      </c>
+      <c r="D104" t="n">
+        <v>253147.2</v>
+      </c>
+      <c r="E104" t="n">
+        <v>259334.3</v>
+      </c>
+      <c r="F104" t="n">
+        <v>4269.4</v>
+      </c>
+      <c r="G104" t="n">
+        <v>2108.1</v>
+      </c>
+      <c r="H104" t="n">
+        <v>2476.2</v>
+      </c>
+      <c r="I104" t="n">
+        <v>50594.3</v>
+      </c>
+      <c r="J104" t="n">
+        <v>56978.6</v>
+      </c>
+      <c r="K104" t="n">
+        <v>1230.2</v>
+      </c>
+      <c r="L104" t="n">
+        <v>2101.7</v>
+      </c>
+      <c r="M104" t="n">
+        <v>2499.2</v>
+      </c>
+      <c r="N104" t="n">
+        <v>50441.5</v>
+      </c>
+      <c r="O104" t="n">
+        <v>46946.5</v>
+      </c>
+      <c r="P104" t="n">
+        <v>472.2</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>14761.7</v>
+      </c>
+      <c r="R104" t="n">
+        <v>17021.6</v>
+      </c>
+      <c r="S104" t="n">
+        <v>354280.3</v>
+      </c>
+      <c r="T104" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B105" t="n">
+        <v>10560.8</v>
+      </c>
+      <c r="C105" t="n">
+        <v>11934.5</v>
+      </c>
+      <c r="D105" t="n">
+        <v>253459.8</v>
+      </c>
+      <c r="E105" t="n">
+        <v>259007.6</v>
+      </c>
+      <c r="F105" t="n">
+        <v>4262.5</v>
+      </c>
+      <c r="G105" t="n">
+        <v>2072.9</v>
+      </c>
+      <c r="H105" t="n">
+        <v>2444.1</v>
+      </c>
+      <c r="I105" t="n">
+        <v>49749.5</v>
+      </c>
+      <c r="J105" t="n">
+        <v>56608.4</v>
+      </c>
+      <c r="K105" t="n">
+        <v>1219.3</v>
+      </c>
+      <c r="L105" t="n">
+        <v>2093.8</v>
+      </c>
+      <c r="M105" t="n">
+        <v>2445.1</v>
+      </c>
+      <c r="N105" t="n">
+        <v>50250.7</v>
+      </c>
+      <c r="O105" t="n">
+        <v>46948.5</v>
+      </c>
+      <c r="P105" t="n">
+        <v>454.6</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>14730.5</v>
+      </c>
+      <c r="R105" t="n">
+        <v>16738.1</v>
+      </c>
+      <c r="S105" t="n">
+        <v>353531.8</v>
+      </c>
+      <c r="T105" t="n">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B106" t="n">
+        <v>10216.1</v>
+      </c>
+      <c r="C106" t="n">
+        <v>11331.3</v>
+      </c>
+      <c r="D106" t="n">
+        <v>245185.6</v>
+      </c>
+      <c r="E106" t="n">
+        <v>252272.5</v>
+      </c>
+      <c r="F106" t="n">
+        <v>4089.4</v>
+      </c>
+      <c r="G106" t="n">
+        <v>2014.6</v>
+      </c>
+      <c r="H106" t="n">
+        <v>2351.2</v>
+      </c>
+      <c r="I106" t="n">
+        <v>48349.8</v>
+      </c>
+      <c r="J106" t="n">
+        <v>54117.3</v>
+      </c>
+      <c r="K106" t="n">
+        <v>1248.6</v>
+      </c>
+      <c r="L106" t="n">
+        <v>2026.7</v>
+      </c>
+      <c r="M106" t="n">
+        <v>2394.8</v>
+      </c>
+      <c r="N106" t="n">
+        <v>48640</v>
+      </c>
+      <c r="O106" t="n">
+        <v>45659.2</v>
+      </c>
+      <c r="P106" t="n">
+        <v>432.8</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>14259.4</v>
+      </c>
+      <c r="R106" t="n">
+        <v>16074.8</v>
+      </c>
+      <c r="S106" t="n">
+        <v>342224.6</v>
+      </c>
+      <c r="T106" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B107" t="n">
+        <v>9561.200000000001</v>
+      </c>
+      <c r="C107" t="n">
+        <v>10779.2</v>
+      </c>
+      <c r="D107" t="n">
+        <v>229469</v>
+      </c>
+      <c r="E107" t="n">
+        <v>238209</v>
+      </c>
+      <c r="F107" t="n">
+        <v>3674.1</v>
+      </c>
+      <c r="G107" t="n">
+        <v>1951</v>
+      </c>
+      <c r="H107" t="n">
+        <v>2341.9</v>
+      </c>
+      <c r="I107" t="n">
+        <v>46823.3</v>
+      </c>
+      <c r="J107" t="n">
+        <v>51819.7</v>
+      </c>
+      <c r="K107" t="n">
+        <v>1166.3</v>
+      </c>
+      <c r="L107" t="n">
+        <v>1938.9</v>
+      </c>
+      <c r="M107" t="n">
+        <v>2311.1</v>
+      </c>
+      <c r="N107" t="n">
+        <v>46534.1</v>
+      </c>
+      <c r="O107" t="n">
+        <v>43631.3</v>
+      </c>
+      <c r="P107" t="n">
+        <v>404.3</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>13451.9</v>
+      </c>
+      <c r="R107" t="n">
+        <v>15403.8</v>
+      </c>
+      <c r="S107" t="n">
+        <v>322844.9</v>
+      </c>
+      <c r="T107" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B108" t="n">
+        <v>10627.1</v>
+      </c>
+      <c r="C108" t="n">
+        <v>12200.5</v>
+      </c>
+      <c r="D108" t="n">
+        <v>255051.4</v>
+      </c>
+      <c r="E108" t="n">
+        <v>261775</v>
+      </c>
+      <c r="F108" t="n">
+        <v>4370.5</v>
+      </c>
+      <c r="G108" t="n">
+        <v>2187.8</v>
+      </c>
+      <c r="H108" t="n">
+        <v>2614.6</v>
+      </c>
+      <c r="I108" t="n">
+        <v>52506.7</v>
+      </c>
+      <c r="J108" t="n">
+        <v>58822.6</v>
+      </c>
+      <c r="K108" t="n">
+        <v>1426.4</v>
+      </c>
+      <c r="L108" t="n">
+        <v>2142.2</v>
+      </c>
+      <c r="M108" t="n">
+        <v>2544.4</v>
+      </c>
+      <c r="N108" t="n">
+        <v>51412</v>
+      </c>
+      <c r="O108" t="n">
+        <v>47005.6</v>
+      </c>
+      <c r="P108" t="n">
+        <v>522.8</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>14960.2</v>
+      </c>
+      <c r="R108" t="n">
+        <v>17343.8</v>
+      </c>
+      <c r="S108" t="n">
+        <v>359045.4</v>
+      </c>
+      <c r="T108" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B109" t="n">
+        <v>10994.1</v>
+      </c>
+      <c r="C109" t="n">
+        <v>12785.6</v>
+      </c>
+      <c r="D109" t="n">
+        <v>263858.8</v>
+      </c>
+      <c r="E109" t="n">
+        <v>270184.7</v>
+      </c>
+      <c r="F109" t="n">
+        <v>4559.7</v>
+      </c>
+      <c r="G109" t="n">
+        <v>2201.8</v>
+      </c>
+      <c r="H109" t="n">
+        <v>2605.3</v>
+      </c>
+      <c r="I109" t="n">
+        <v>52842.6</v>
+      </c>
+      <c r="J109" t="n">
+        <v>60549.7</v>
+      </c>
+      <c r="K109" t="n">
+        <v>1426.5</v>
+      </c>
+      <c r="L109" t="n">
+        <v>2188.6</v>
+      </c>
+      <c r="M109" t="n">
+        <v>2566.9</v>
+      </c>
+      <c r="N109" t="n">
+        <v>52525.4</v>
+      </c>
+      <c r="O109" t="n">
+        <v>47843.6</v>
+      </c>
+      <c r="P109" t="n">
+        <v>554.6</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>15387.5</v>
+      </c>
+      <c r="R109" t="n">
+        <v>17924.4</v>
+      </c>
+      <c r="S109" t="n">
+        <v>369300.2</v>
+      </c>
+      <c r="T109" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B110" t="n">
+        <v>11268</v>
+      </c>
+      <c r="C110" t="n">
+        <v>12989.7</v>
+      </c>
+      <c r="D110" t="n">
+        <v>270433.1</v>
+      </c>
+      <c r="E110" t="n">
+        <v>278893</v>
+      </c>
+      <c r="F110" t="n">
+        <v>5070.2</v>
+      </c>
+      <c r="G110" t="n">
+        <v>2213.3</v>
+      </c>
+      <c r="H110" t="n">
+        <v>2632.2</v>
+      </c>
+      <c r="I110" t="n">
+        <v>53118.8</v>
+      </c>
+      <c r="J110" t="n">
+        <v>58909</v>
+      </c>
+      <c r="K110" t="n">
+        <v>1404.2</v>
+      </c>
+      <c r="L110" t="n">
+        <v>2214.6</v>
+      </c>
+      <c r="M110" t="n">
+        <v>2592.8</v>
+      </c>
+      <c r="N110" t="n">
+        <v>53149.7</v>
+      </c>
+      <c r="O110" t="n">
+        <v>48779.8</v>
+      </c>
+      <c r="P110" t="n">
+        <v>548.9</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>15699.2</v>
+      </c>
+      <c r="R110" t="n">
+        <v>18097.8</v>
+      </c>
+      <c r="S110" t="n">
+        <v>376780.3</v>
+      </c>
+      <c r="T110" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B111" t="n">
+        <v>11170</v>
+      </c>
+      <c r="C111" t="n">
+        <v>12828</v>
+      </c>
+      <c r="D111" t="n">
+        <v>268080.5</v>
+      </c>
+      <c r="E111" t="n">
+        <v>275507.6</v>
+      </c>
+      <c r="F111" t="n">
+        <v>4804.3</v>
+      </c>
+      <c r="G111" t="n">
+        <v>2229.3</v>
+      </c>
+      <c r="H111" t="n">
+        <v>2605.9</v>
+      </c>
+      <c r="I111" t="n">
+        <v>53502.3</v>
+      </c>
+      <c r="J111" t="n">
+        <v>59128.7</v>
+      </c>
+      <c r="K111" t="n">
+        <v>1485.8</v>
+      </c>
+      <c r="L111" t="n">
+        <v>2199.5</v>
+      </c>
+      <c r="M111" t="n">
+        <v>2618.8</v>
+      </c>
+      <c r="N111" t="n">
+        <v>52788.6</v>
+      </c>
+      <c r="O111" t="n">
+        <v>49551.1</v>
+      </c>
+      <c r="P111" t="n">
+        <v>464.1</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>15602.5</v>
+      </c>
+      <c r="R111" t="n">
+        <v>17871</v>
+      </c>
+      <c r="S111" t="n">
+        <v>374460.3</v>
+      </c>
+      <c r="T111" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B112" t="n">
+        <v>10798</v>
+      </c>
+      <c r="C112" t="n">
+        <v>12042.5</v>
+      </c>
+      <c r="D112" t="n">
+        <v>259152.1</v>
+      </c>
+      <c r="E112" t="n">
+        <v>267283.6</v>
+      </c>
+      <c r="F112" t="n">
+        <v>4514.4</v>
+      </c>
+      <c r="G112" t="n">
+        <v>2203.5</v>
+      </c>
+      <c r="H112" t="n">
+        <v>2570.8</v>
+      </c>
+      <c r="I112" t="n">
+        <v>52884.5</v>
+      </c>
+      <c r="J112" t="n">
+        <v>58529.3</v>
+      </c>
+      <c r="K112" t="n">
+        <v>1443.4</v>
+      </c>
+      <c r="L112" t="n">
+        <v>2093.3</v>
+      </c>
+      <c r="M112" t="n">
+        <v>2412</v>
+      </c>
+      <c r="N112" t="n">
+        <v>50239.9</v>
+      </c>
+      <c r="O112" t="n">
+        <v>46227.5</v>
+      </c>
+      <c r="P112" t="n">
+        <v>467.3</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>15099</v>
+      </c>
+      <c r="R112" t="n">
+        <v>16880.6</v>
+      </c>
+      <c r="S112" t="n">
+        <v>362375.8</v>
+      </c>
+      <c r="T112" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B113" t="n">
+        <v>10232.6</v>
+      </c>
+      <c r="C113" t="n">
+        <v>11356.8</v>
+      </c>
+      <c r="D113" t="n">
+        <v>245581.7</v>
+      </c>
+      <c r="E113" t="n">
+        <v>255189.6</v>
+      </c>
+      <c r="F113" t="n">
+        <v>4100.2</v>
+      </c>
+      <c r="G113" t="n">
+        <v>2079.1</v>
+      </c>
+      <c r="H113" t="n">
+        <v>2386.7</v>
+      </c>
+      <c r="I113" t="n">
+        <v>49898.1</v>
+      </c>
+      <c r="J113" t="n">
+        <v>56184</v>
+      </c>
+      <c r="K113" t="n">
+        <v>1320.5</v>
+      </c>
+      <c r="L113" t="n">
+        <v>1947.8</v>
+      </c>
+      <c r="M113" t="n">
+        <v>2308.1</v>
+      </c>
+      <c r="N113" t="n">
+        <v>46747.5</v>
+      </c>
+      <c r="O113" t="n">
+        <v>41785.7</v>
+      </c>
+      <c r="P113" t="n">
+        <v>445.5</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>14262.1</v>
+      </c>
+      <c r="R113" t="n">
+        <v>15982.5</v>
+      </c>
+      <c r="S113" t="n">
+        <v>342289.7</v>
+      </c>
+      <c r="T113" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="4" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B114" t="n">
+        <v>9614.700000000001</v>
+      </c>
+      <c r="C114" t="n">
+        <v>10822.1</v>
+      </c>
+      <c r="D114" t="n">
+        <v>230751.8</v>
+      </c>
+      <c r="E114" t="n">
+        <v>240908.9</v>
+      </c>
+      <c r="F114" t="n">
+        <v>3791.3</v>
+      </c>
+      <c r="G114" t="n">
+        <v>1937.7</v>
+      </c>
+      <c r="H114" t="n">
+        <v>2384.4</v>
+      </c>
+      <c r="I114" t="n">
+        <v>46504</v>
+      </c>
+      <c r="J114" t="n">
+        <v>52094</v>
+      </c>
+      <c r="K114" t="n">
+        <v>1262.1</v>
+      </c>
+      <c r="L114" t="n">
+        <v>1840.8</v>
+      </c>
+      <c r="M114" t="n">
+        <v>2238</v>
+      </c>
+      <c r="N114" t="n">
+        <v>44179.8</v>
+      </c>
+      <c r="O114" t="n">
+        <v>40877.6</v>
+      </c>
+      <c r="P114" t="n">
+        <v>459.3</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>13394</v>
+      </c>
+      <c r="R114" t="n">
+        <v>15261.8</v>
+      </c>
+      <c r="S114" t="n">
+        <v>321456.1</v>
+      </c>
+      <c r="T114" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B115" t="n">
+        <v>10728.9</v>
+      </c>
+      <c r="C115" t="n">
+        <v>12584.2</v>
+      </c>
+      <c r="D115" t="n">
+        <v>257494</v>
+      </c>
+      <c r="E115" t="n">
+        <v>265674.8</v>
+      </c>
+      <c r="F115" t="n">
+        <v>4747.2</v>
+      </c>
+      <c r="G115" t="n">
+        <v>2143.1</v>
+      </c>
+      <c r="H115" t="n">
+        <v>2565.9</v>
+      </c>
+      <c r="I115" t="n">
+        <v>51433.3</v>
+      </c>
+      <c r="J115" t="n">
+        <v>58179</v>
+      </c>
+      <c r="K115" t="n">
+        <v>1319.3</v>
+      </c>
+      <c r="L115" t="n">
+        <v>2098.6</v>
+      </c>
+      <c r="M115" t="n">
+        <v>2520</v>
+      </c>
+      <c r="N115" t="n">
+        <v>50366.3</v>
+      </c>
+      <c r="O115" t="n">
+        <v>44714.7</v>
+      </c>
+      <c r="P115" t="n">
+        <v>449.9</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>14973.7</v>
+      </c>
+      <c r="R115" t="n">
+        <v>17621.2</v>
+      </c>
+      <c r="S115" t="n">
+        <v>359369</v>
+      </c>
+      <c r="T115" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="4" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B116" t="n">
+        <v>10936</v>
+      </c>
+      <c r="C116" t="n">
+        <v>12744.8</v>
+      </c>
+      <c r="D116" t="n">
+        <v>262463.4</v>
+      </c>
+      <c r="E116" t="n">
+        <v>272659.2</v>
+      </c>
+      <c r="F116" t="n">
+        <v>5137.6</v>
+      </c>
+      <c r="G116" t="n">
+        <v>2188.3</v>
+      </c>
+      <c r="H116" t="n">
+        <v>2575.7</v>
+      </c>
+      <c r="I116" t="n">
+        <v>52519.5</v>
+      </c>
+      <c r="J116" t="n">
+        <v>60572.5</v>
+      </c>
+      <c r="K116" t="n">
+        <v>1314.2</v>
+      </c>
+      <c r="L116" t="n">
+        <v>2142.9</v>
+      </c>
+      <c r="M116" t="n">
+        <v>2548.6</v>
+      </c>
+      <c r="N116" t="n">
+        <v>51430.5</v>
+      </c>
+      <c r="O116" t="n">
+        <v>44207.8</v>
+      </c>
+      <c r="P116" t="n">
+        <v>483.5</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>15270.5</v>
+      </c>
+      <c r="R116" t="n">
+        <v>17836.1</v>
+      </c>
+      <c r="S116" t="n">
+        <v>366492.3</v>
+      </c>
+      <c r="T116" t="n">
         <v>287</v>
       </c>
     </row>
@@ -8836,7 +11101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q92"/>
+  <dimension ref="A1:Q116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10694,54 +12959,33 @@
         <v>46260</v>
       </c>
       <c r="B54" t="n">
-        <v>6078.76</v>
+        <v>6873.25</v>
       </c>
       <c r="C54" t="n">
-        <v>5886.5</v>
+        <v>6702.28</v>
       </c>
       <c r="D54" t="n">
-        <v>13872.03</v>
+        <v>9322.67</v>
       </c>
       <c r="E54" t="n">
-        <v>14586.59</v>
+        <v>9317.450000000001</v>
       </c>
       <c r="F54" t="n">
-        <v>30081.21</v>
+        <v>10481.38</v>
       </c>
       <c r="G54" t="n">
-        <v>20268.74</v>
+        <v>10056.54</v>
       </c>
       <c r="H54" t="n">
-        <v>9044.91</v>
+        <v>7536.69</v>
       </c>
       <c r="I54" t="n">
         <v>288</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="K54" t="n">
-        <v>6078.76</v>
-      </c>
-      <c r="L54" t="n">
-        <v>5886.5</v>
-      </c>
-      <c r="M54" t="n">
-        <v>30081.21</v>
-      </c>
-      <c r="N54" t="n">
-        <v>20268.74</v>
-      </c>
-      <c r="O54" t="n">
-        <v>13872.03</v>
-      </c>
-      <c r="P54" t="n">
-        <v>14586.59</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>9044.91</v>
+          <t>final</t>
+        </is>
       </c>
     </row>
     <row r="55">
@@ -10749,45 +12993,33 @@
         <v>46261</v>
       </c>
       <c r="B55" t="n">
-        <v>6870.55</v>
+        <v>7656.06</v>
       </c>
       <c r="C55" t="n">
-        <v>6816.7</v>
+        <v>7585.02</v>
+      </c>
+      <c r="D55" t="n">
+        <v>13905.53</v>
+      </c>
+      <c r="E55" t="n">
+        <v>14158.31</v>
       </c>
       <c r="F55" t="n">
-        <v>29186.79</v>
+        <v>12623.77</v>
       </c>
       <c r="G55" t="n">
-        <v>31061.65</v>
+        <v>12170.71</v>
+      </c>
+      <c r="H55" t="n">
+        <v>9223.889999999999</v>
       </c>
       <c r="I55" t="n">
         <v>288</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="K55" t="n">
-        <v>6870.55</v>
-      </c>
-      <c r="L55" t="n">
-        <v>6816.7</v>
-      </c>
-      <c r="M55" t="n">
-        <v>29186.79</v>
-      </c>
-      <c r="N55" t="n">
-        <v>31061.65</v>
-      </c>
-      <c r="O55" t="n">
-        <v>48368.45</v>
-      </c>
-      <c r="P55" t="n">
-        <v>50413.37</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>16980.07</v>
+          <t>final</t>
+        </is>
       </c>
     </row>
     <row r="56">
@@ -10795,54 +13027,33 @@
         <v>46262</v>
       </c>
       <c r="B56" t="n">
-        <v>5577.55</v>
+        <v>5605.03</v>
       </c>
       <c r="C56" t="n">
-        <v>5525.42</v>
+        <v>5538.04</v>
       </c>
       <c r="D56" t="n">
-        <v>27408.76</v>
+        <v>15304.79</v>
       </c>
       <c r="E56" t="n">
-        <v>28393.79</v>
+        <v>15813.16</v>
       </c>
       <c r="F56" t="n">
-        <v>29490.31</v>
+        <v>15444.54</v>
       </c>
       <c r="G56" t="n">
-        <v>30487.38</v>
+        <v>14838.73</v>
       </c>
       <c r="H56" t="n">
-        <v>12589.5</v>
+        <v>8484.27</v>
       </c>
       <c r="I56" t="n">
         <v>288</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="K56" t="n">
-        <v>5577.55</v>
-      </c>
-      <c r="L56" t="n">
-        <v>5525.42</v>
-      </c>
-      <c r="M56" t="n">
-        <v>29490.31</v>
-      </c>
-      <c r="N56" t="n">
-        <v>30487.38</v>
-      </c>
-      <c r="O56" t="n">
-        <v>27408.76</v>
-      </c>
-      <c r="P56" t="n">
-        <v>28393.79</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>12589.5</v>
+          <t>final</t>
+        </is>
       </c>
     </row>
     <row r="57">
@@ -10850,54 +13061,33 @@
         <v>46263</v>
       </c>
       <c r="B57" t="n">
-        <v>4168.24</v>
+        <v>3736.58</v>
       </c>
       <c r="C57" t="n">
-        <v>3639.11</v>
+        <v>3639.19</v>
       </c>
       <c r="D57" t="n">
-        <v>22339.12</v>
+        <v>9341.290000000001</v>
       </c>
       <c r="E57" t="n">
-        <v>24022.46</v>
+        <v>9272.389999999999</v>
       </c>
       <c r="F57" t="n">
-        <v>17797.34</v>
+        <v>10651.32</v>
       </c>
       <c r="G57" t="n">
-        <v>16328.46</v>
+        <v>10637.36</v>
       </c>
       <c r="H57" t="n">
-        <v>9117.01</v>
+        <v>5585.61</v>
       </c>
       <c r="I57" t="n">
         <v>288</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="K57" t="n">
-        <v>4168.24</v>
-      </c>
-      <c r="L57" t="n">
-        <v>3639.11</v>
-      </c>
-      <c r="M57" t="n">
-        <v>17797.34</v>
-      </c>
-      <c r="N57" t="n">
-        <v>16328.46</v>
-      </c>
-      <c r="O57" t="n">
-        <v>22339.12</v>
-      </c>
-      <c r="P57" t="n">
-        <v>24022.46</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>9117.01</v>
+          <t>final</t>
+        </is>
       </c>
     </row>
     <row r="58">
@@ -10905,45 +13095,33 @@
         <v>46264</v>
       </c>
       <c r="B58" t="n">
-        <v>136.17</v>
+        <v>-176.35</v>
       </c>
       <c r="C58" t="n">
         <v>24.3</v>
       </c>
+      <c r="D58" t="n">
+        <v>13992.86</v>
+      </c>
+      <c r="E58" t="n">
+        <v>14139.71</v>
+      </c>
       <c r="F58" t="n">
-        <v>26602.37</v>
+        <v>12130.43</v>
       </c>
       <c r="G58" t="n">
-        <v>27178.76</v>
+        <v>12472.2</v>
+      </c>
+      <c r="H58" t="n">
+        <v>4301.11</v>
       </c>
       <c r="I58" t="n">
         <v>288</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="K58" t="n">
-        <v>136.17</v>
-      </c>
-      <c r="L58" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="M58" t="n">
-        <v>26602.37</v>
-      </c>
-      <c r="N58" t="n">
-        <v>27178.76</v>
-      </c>
-      <c r="O58" t="n">
-        <v>74656.96000000001</v>
-      </c>
-      <c r="P58" t="n">
-        <v>77904.85000000001</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>17921.41</v>
+          <t>final</t>
+        </is>
       </c>
     </row>
     <row r="59">
@@ -10951,45 +13129,33 @@
         <v>46265</v>
       </c>
       <c r="B59" t="n">
-        <v>917.6799999999999</v>
+        <v>564.6799999999999</v>
       </c>
       <c r="C59" t="n">
-        <v>802.91</v>
+        <v>768.39</v>
+      </c>
+      <c r="D59" t="n">
+        <v>15438.84</v>
+      </c>
+      <c r="E59" t="n">
+        <v>15901.22</v>
       </c>
       <c r="F59" t="n">
-        <v>26283.51</v>
+        <v>13786.92</v>
       </c>
       <c r="G59" t="n">
-        <v>26864.61</v>
+        <v>14721.37</v>
+      </c>
+      <c r="H59" t="n">
+        <v>5234.9</v>
       </c>
       <c r="I59" t="n">
         <v>288</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="K59" t="n">
-        <v>917.6799999999999</v>
-      </c>
-      <c r="L59" t="n">
-        <v>802.91</v>
-      </c>
-      <c r="M59" t="n">
-        <v>26283.51</v>
-      </c>
-      <c r="N59" t="n">
-        <v>26864.61</v>
-      </c>
-      <c r="O59" t="n">
-        <v>47646.67</v>
-      </c>
-      <c r="P59" t="n">
-        <v>49886.35</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>12743.32</v>
+          <t>final</t>
+        </is>
       </c>
     </row>
     <row r="60">
@@ -10997,54 +13163,33 @@
         <v>46266</v>
       </c>
       <c r="B60" t="n">
-        <v>4999.71</v>
+        <v>4639.04</v>
       </c>
       <c r="C60" t="n">
-        <v>4568.92</v>
+        <v>4595.4</v>
       </c>
       <c r="D60" t="n">
-        <v>26389.21</v>
+        <v>9344.139999999999</v>
       </c>
       <c r="E60" t="n">
-        <v>27383.53</v>
+        <v>9171.129999999999</v>
       </c>
       <c r="F60" t="n">
-        <v>17592.81</v>
+        <v>11853.13</v>
       </c>
       <c r="G60" t="n">
-        <v>12321.93</v>
+        <v>11397.13</v>
       </c>
       <c r="H60" t="n">
-        <v>9307</v>
+        <v>6238.08</v>
       </c>
       <c r="I60" t="n">
         <v>288</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="K60" t="n">
-        <v>4999.71</v>
-      </c>
-      <c r="L60" t="n">
-        <v>4568.92</v>
-      </c>
-      <c r="M60" t="n">
-        <v>17592.81</v>
-      </c>
-      <c r="N60" t="n">
-        <v>12321.93</v>
-      </c>
-      <c r="O60" t="n">
-        <v>26389.21</v>
-      </c>
-      <c r="P60" t="n">
-        <v>27383.53</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>9307</v>
+          <t>final</t>
+        </is>
       </c>
     </row>
     <row r="61">
@@ -11052,45 +13197,33 @@
         <v>46267</v>
       </c>
       <c r="B61" t="n">
-        <v>4922.72</v>
+        <v>4679.14</v>
       </c>
       <c r="C61" t="n">
-        <v>4483.62</v>
+        <v>4552.29</v>
+      </c>
+      <c r="D61" t="n">
+        <v>13814.28</v>
+      </c>
+      <c r="E61" t="n">
+        <v>13940.88</v>
       </c>
       <c r="F61" t="n">
-        <v>21025.3</v>
+        <v>12020.06</v>
       </c>
       <c r="G61" t="n">
-        <v>14115.39</v>
+        <v>11820.95</v>
+      </c>
+      <c r="H61" t="n">
+        <v>6988.15</v>
       </c>
       <c r="I61" t="n">
         <v>288</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="K61" t="n">
-        <v>4922.72</v>
-      </c>
-      <c r="L61" t="n">
-        <v>4483.62</v>
-      </c>
-      <c r="M61" t="n">
-        <v>21025.3</v>
-      </c>
-      <c r="N61" t="n">
-        <v>14115.39</v>
-      </c>
-      <c r="O61" t="n">
-        <v>78467.69</v>
-      </c>
-      <c r="P61" t="n">
-        <v>78776.75</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>17407.5</v>
+          <t>final</t>
+        </is>
       </c>
     </row>
     <row r="62">
@@ -11098,45 +13231,33 @@
         <v>46268</v>
       </c>
       <c r="B62" t="n">
-        <v>3924.77</v>
+        <v>3498.94</v>
       </c>
       <c r="C62" t="n">
-        <v>3338.37</v>
+        <v>3335.85</v>
+      </c>
+      <c r="D62" t="n">
+        <v>15731.22</v>
+      </c>
+      <c r="E62" t="n">
+        <v>15517.87</v>
       </c>
       <c r="F62" t="n">
-        <v>22076.4</v>
+        <v>13171.76</v>
       </c>
       <c r="G62" t="n">
-        <v>15702.86</v>
+        <v>13328.78</v>
+      </c>
+      <c r="H62" t="n">
+        <v>6611.77</v>
       </c>
       <c r="I62" t="n">
         <v>288</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="K62" t="n">
-        <v>3924.77</v>
-      </c>
-      <c r="L62" t="n">
-        <v>3338.37</v>
-      </c>
-      <c r="M62" t="n">
-        <v>22076.4</v>
-      </c>
-      <c r="N62" t="n">
-        <v>15702.86</v>
-      </c>
-      <c r="O62" t="n">
-        <v>49958.57</v>
-      </c>
-      <c r="P62" t="n">
-        <v>47342.5</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>12023.45</v>
+          <t>final</t>
+        </is>
       </c>
     </row>
     <row r="63">
@@ -11144,54 +13265,33 @@
         <v>46269</v>
       </c>
       <c r="B63" t="n">
-        <v>3740.97</v>
+        <v>3426.25</v>
       </c>
       <c r="C63" t="n">
-        <v>3380.32</v>
+        <v>3393.02</v>
       </c>
       <c r="D63" t="n">
-        <v>29379.65</v>
+        <v>9342.450000000001</v>
       </c>
       <c r="E63" t="n">
-        <v>29911.47</v>
+        <v>9133.02</v>
       </c>
       <c r="F63" t="n">
-        <v>21027.66</v>
+        <v>11971.85</v>
       </c>
       <c r="G63" t="n">
-        <v>12975.71</v>
+        <v>11606.07</v>
       </c>
       <c r="H63" t="n">
-        <v>9132.57</v>
+        <v>5479.14</v>
       </c>
       <c r="I63" t="n">
         <v>288</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="K63" t="n">
-        <v>3740.97</v>
-      </c>
-      <c r="L63" t="n">
-        <v>3380.32</v>
-      </c>
-      <c r="M63" t="n">
-        <v>21027.66</v>
-      </c>
-      <c r="N63" t="n">
-        <v>12975.71</v>
-      </c>
-      <c r="O63" t="n">
-        <v>29379.65</v>
-      </c>
-      <c r="P63" t="n">
-        <v>29911.47</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>9132.57</v>
+          <t>final</t>
+        </is>
       </c>
     </row>
     <row r="64">
@@ -11199,42 +13299,33 @@
         <v>46270</v>
       </c>
       <c r="B64" t="n">
-        <v>3124.51</v>
+        <v>2584.47</v>
       </c>
       <c r="C64" t="n">
-        <v>2499.57</v>
+        <v>2476.94</v>
+      </c>
+      <c r="D64" t="n">
+        <v>13642.77</v>
+      </c>
+      <c r="E64" t="n">
+        <v>14073.11</v>
       </c>
       <c r="F64" t="n">
-        <v>30660.64</v>
+        <v>11671.23</v>
+      </c>
+      <c r="G64" t="n">
+        <v>11489.16</v>
+      </c>
+      <c r="H64" t="n">
+        <v>5708.11</v>
       </c>
       <c r="I64" t="n">
         <v>288</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="K64" t="n">
-        <v>3124.51</v>
-      </c>
-      <c r="L64" t="n">
-        <v>2499.57</v>
-      </c>
-      <c r="M64" t="n">
-        <v>30660.64</v>
-      </c>
-      <c r="N64" t="n">
-        <v>32326.65</v>
-      </c>
-      <c r="O64" t="n">
-        <v>43308.92</v>
-      </c>
-      <c r="P64" t="n">
-        <v>46940.7</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>14214.4</v>
+          <t>final</t>
+        </is>
       </c>
     </row>
     <row r="65">
@@ -11242,54 +13333,33 @@
         <v>46271</v>
       </c>
       <c r="B65" t="n">
-        <v>-217.13</v>
+        <v>-322.62</v>
       </c>
       <c r="C65" t="n">
-        <v>-89.97</v>
+        <v>-198.34</v>
       </c>
       <c r="D65" t="n">
-        <v>28406.9</v>
+        <v>12809.84</v>
       </c>
       <c r="E65" t="n">
-        <v>31257.98</v>
+        <v>13607.29</v>
       </c>
       <c r="F65" t="n">
-        <v>27312.42</v>
+        <v>12473.17</v>
       </c>
       <c r="G65" t="n">
-        <v>28945.34</v>
+        <v>12783.13</v>
       </c>
       <c r="H65" t="n">
-        <v>9369.870000000001</v>
+        <v>3995.15</v>
       </c>
       <c r="I65" t="n">
         <v>288</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="K65" t="n">
-        <v>-217.13</v>
-      </c>
-      <c r="L65" t="n">
-        <v>-89.97</v>
-      </c>
-      <c r="M65" t="n">
-        <v>27312.42</v>
-      </c>
-      <c r="N65" t="n">
-        <v>28945.34</v>
-      </c>
-      <c r="O65" t="n">
-        <v>28406.9</v>
-      </c>
-      <c r="P65" t="n">
-        <v>31257.98</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>9369.870000000001</v>
+          <t>final</t>
+        </is>
       </c>
     </row>
     <row r="66">
@@ -11297,45 +13367,33 @@
         <v>46272</v>
       </c>
       <c r="B66" t="n">
-        <v>3905.22</v>
+        <v>3901.67</v>
       </c>
       <c r="C66" t="n">
-        <v>3934.67</v>
+        <v>3941.86</v>
+      </c>
+      <c r="D66" t="n">
+        <v>12225.79</v>
+      </c>
+      <c r="E66" t="n">
+        <v>12215.4</v>
       </c>
       <c r="F66" t="n">
-        <v>28252.86</v>
+        <v>13740.55</v>
       </c>
       <c r="G66" t="n">
-        <v>26511.99</v>
+        <v>14582.73</v>
+      </c>
+      <c r="H66" t="n">
+        <v>6864.5</v>
       </c>
       <c r="I66" t="n">
         <v>288</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="K66" t="n">
-        <v>3905.22</v>
-      </c>
-      <c r="L66" t="n">
-        <v>3934.67</v>
-      </c>
-      <c r="M66" t="n">
-        <v>28252.86</v>
-      </c>
-      <c r="N66" t="n">
-        <v>26511.99</v>
-      </c>
-      <c r="O66" t="n">
-        <v>54685.62</v>
-      </c>
-      <c r="P66" t="n">
-        <v>56975.6</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>16337.96</v>
+          <t>final</t>
+        </is>
       </c>
     </row>
     <row r="67">
@@ -11343,45 +13401,33 @@
         <v>46273</v>
       </c>
       <c r="B67" t="n">
-        <v>5819.31</v>
+        <v>5622.6</v>
       </c>
       <c r="C67" t="n">
-        <v>5479.98</v>
+        <v>5606.52</v>
+      </c>
+      <c r="D67" t="n">
+        <v>13678.62</v>
+      </c>
+      <c r="E67" t="n">
+        <v>13697.91</v>
       </c>
       <c r="F67" t="n">
-        <v>17557.2</v>
+        <v>11265.71</v>
       </c>
       <c r="G67" t="n">
-        <v>14412.46</v>
+        <v>11413.28</v>
+      </c>
+      <c r="H67" t="n">
+        <v>7828.62</v>
       </c>
       <c r="I67" t="n">
         <v>288</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="K67" t="n">
-        <v>5819.31</v>
-      </c>
-      <c r="L67" t="n">
-        <v>5479.98</v>
-      </c>
-      <c r="M67" t="n">
-        <v>17557.2</v>
-      </c>
-      <c r="N67" t="n">
-        <v>14412.46</v>
-      </c>
-      <c r="O67" t="n">
-        <v>47612.04</v>
-      </c>
-      <c r="P67" t="n">
-        <v>48776.77</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>14178.51</v>
+          <t>final</t>
+        </is>
       </c>
     </row>
     <row r="68">
@@ -11389,54 +13435,33 @@
         <v>46274</v>
       </c>
       <c r="B68" t="n">
-        <v>5750.53</v>
+        <v>5448.04</v>
       </c>
       <c r="C68" t="n">
-        <v>5283.45</v>
+        <v>5365.81</v>
       </c>
       <c r="D68" t="n">
-        <v>19976.6</v>
+        <v>12656.22</v>
       </c>
       <c r="E68" t="n">
-        <v>20976.41</v>
+        <v>12514.98</v>
       </c>
       <c r="F68" t="n">
-        <v>16668.17</v>
+        <v>11433.48</v>
       </c>
       <c r="G68" t="n">
-        <v>10669.6</v>
+        <v>11127.42</v>
       </c>
       <c r="H68" t="n">
-        <v>8730.049999999999</v>
+        <v>7379.25</v>
       </c>
       <c r="I68" t="n">
         <v>288</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="K68" t="n">
-        <v>5750.53</v>
-      </c>
-      <c r="L68" t="n">
-        <v>5283.45</v>
-      </c>
-      <c r="M68" t="n">
-        <v>16668.17</v>
-      </c>
-      <c r="N68" t="n">
-        <v>10669.6</v>
-      </c>
-      <c r="O68" t="n">
-        <v>19976.6</v>
-      </c>
-      <c r="P68" t="n">
-        <v>20976.41</v>
-      </c>
-      <c r="Q68" t="n">
-        <v>8730.049999999999</v>
+          <t>final</t>
+        </is>
       </c>
     </row>
     <row r="69">
@@ -11444,39 +13469,33 @@
         <v>46275</v>
       </c>
       <c r="B69" t="n">
-        <v>5028.17</v>
+        <v>4831.19</v>
       </c>
       <c r="C69" t="n">
-        <v>4606.51</v>
+        <v>4695.11</v>
+      </c>
+      <c r="D69" t="n">
+        <v>11987.1</v>
+      </c>
+      <c r="E69" t="n">
+        <v>11829.64</v>
+      </c>
+      <c r="F69" t="n">
+        <v>14860.35</v>
+      </c>
+      <c r="G69" t="n">
+        <v>15196.02</v>
+      </c>
+      <c r="H69" t="n">
+        <v>7306.96</v>
       </c>
       <c r="I69" t="n">
         <v>288</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="K69" t="n">
-        <v>5028.17</v>
-      </c>
-      <c r="L69" t="n">
-        <v>4606.51</v>
-      </c>
-      <c r="M69" t="n">
-        <v>37921.34</v>
-      </c>
-      <c r="N69" t="n">
-        <v>36240.03</v>
-      </c>
-      <c r="O69" t="n">
-        <v>45174.82</v>
-      </c>
-      <c r="P69" t="n">
-        <v>47834.7</v>
-      </c>
-      <c r="Q69" t="n">
-        <v>16254.06</v>
+          <t>final</t>
+        </is>
       </c>
     </row>
     <row r="70">
@@ -11484,45 +13503,33 @@
         <v>46276</v>
       </c>
       <c r="B70" t="n">
-        <v>5000.77</v>
+        <v>4744.52</v>
       </c>
       <c r="C70" t="n">
-        <v>4613.94</v>
+        <v>4626.75</v>
+      </c>
+      <c r="D70" t="n">
+        <v>13574.06</v>
+      </c>
+      <c r="E70" t="n">
+        <v>13749.56</v>
       </c>
       <c r="F70" t="n">
-        <v>22225.63</v>
+        <v>11374.15</v>
       </c>
       <c r="G70" t="n">
-        <v>16679.15</v>
+        <v>11217.81</v>
+      </c>
+      <c r="H70" t="n">
+        <v>7027.91</v>
       </c>
       <c r="I70" t="n">
         <v>288</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="K70" t="n">
-        <v>5000.77</v>
-      </c>
-      <c r="L70" t="n">
-        <v>4613.94</v>
-      </c>
-      <c r="M70" t="n">
-        <v>22225.63</v>
-      </c>
-      <c r="N70" t="n">
-        <v>16679.15</v>
-      </c>
-      <c r="O70" t="n">
-        <v>46971.34</v>
-      </c>
-      <c r="P70" t="n">
-        <v>49612.85</v>
-      </c>
-      <c r="Q70" t="n">
-        <v>13859.61</v>
+          <t>final</t>
+        </is>
       </c>
     </row>
     <row r="71">
@@ -11530,54 +13537,33 @@
         <v>46277</v>
       </c>
       <c r="B71" t="n">
-        <v>4778.7</v>
+        <v>4775.23</v>
       </c>
       <c r="C71" t="n">
-        <v>4528.16</v>
+        <v>4675.46</v>
       </c>
       <c r="D71" t="n">
-        <v>20506.52</v>
+        <v>12606.14</v>
       </c>
       <c r="E71" t="n">
-        <v>21821.57</v>
+        <v>12752.16</v>
       </c>
       <c r="F71" t="n">
-        <v>23501.87</v>
+        <v>11588.55</v>
       </c>
       <c r="G71" t="n">
-        <v>16785.23</v>
+        <v>11310.07</v>
       </c>
       <c r="H71" t="n">
-        <v>8989.379999999999</v>
+        <v>6872.72</v>
       </c>
       <c r="I71" t="n">
         <v>288</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="K71" t="n">
-        <v>4778.7</v>
-      </c>
-      <c r="L71" t="n">
-        <v>4528.16</v>
-      </c>
-      <c r="M71" t="n">
-        <v>23501.87</v>
-      </c>
-      <c r="N71" t="n">
-        <v>16785.23</v>
-      </c>
-      <c r="O71" t="n">
-        <v>20506.52</v>
-      </c>
-      <c r="P71" t="n">
-        <v>21821.57</v>
-      </c>
-      <c r="Q71" t="n">
-        <v>8989.379999999999</v>
+          <t>final</t>
+        </is>
       </c>
     </row>
     <row r="72">
@@ -11585,39 +13571,33 @@
         <v>46278</v>
       </c>
       <c r="B72" t="n">
-        <v>1333.23</v>
+        <v>1319.7</v>
       </c>
       <c r="C72" t="n">
-        <v>1322.1</v>
+        <v>1329.67</v>
+      </c>
+      <c r="D72" t="n">
+        <v>10642.35</v>
+      </c>
+      <c r="E72" t="n">
+        <v>11190.81</v>
+      </c>
+      <c r="F72" t="n">
+        <v>13180.25</v>
+      </c>
+      <c r="G72" t="n">
+        <v>13598.49</v>
+      </c>
+      <c r="H72" t="n">
+        <v>4434.43</v>
       </c>
       <c r="I72" t="n">
         <v>288</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="K72" t="n">
-        <v>1333.23</v>
-      </c>
-      <c r="L72" t="n">
-        <v>1322.1</v>
-      </c>
-      <c r="M72" t="n">
-        <v>36780</v>
-      </c>
-      <c r="N72" t="n">
-        <v>40352.72</v>
-      </c>
-      <c r="O72" t="n">
-        <v>36724.33</v>
-      </c>
-      <c r="P72" t="n">
-        <v>41353.34</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>12649.6</v>
+          <t>final</t>
+        </is>
       </c>
     </row>
     <row r="73">
@@ -11625,45 +13605,33 @@
         <v>46279</v>
       </c>
       <c r="B73" t="n">
-        <v>5117.86</v>
+        <v>5067.07</v>
       </c>
       <c r="C73" t="n">
-        <v>5131.41</v>
+        <v>5074.3</v>
+      </c>
+      <c r="D73" t="n">
+        <v>14970.03</v>
+      </c>
+      <c r="E73" t="n">
+        <v>15383.64</v>
       </c>
       <c r="F73" t="n">
-        <v>20064</v>
+        <v>12706.07</v>
       </c>
       <c r="G73" t="n">
-        <v>22556.16</v>
+        <v>13242.28</v>
+      </c>
+      <c r="H73" t="n">
+        <v>7702.75</v>
       </c>
       <c r="I73" t="n">
         <v>288</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="K73" t="n">
-        <v>5117.86</v>
-      </c>
-      <c r="L73" t="n">
-        <v>5131.41</v>
-      </c>
-      <c r="M73" t="n">
-        <v>20064</v>
-      </c>
-      <c r="N73" t="n">
-        <v>22556.16</v>
-      </c>
-      <c r="O73" t="n">
-        <v>45924.54</v>
-      </c>
-      <c r="P73" t="n">
-        <v>48837.97</v>
-      </c>
-      <c r="Q73" t="n">
-        <v>14333.57</v>
+          <t>final</t>
+        </is>
       </c>
     </row>
     <row r="74">
@@ -11671,45 +13639,33 @@
         <v>46280</v>
       </c>
       <c r="B74" t="n">
-        <v>5304.31</v>
+        <v>5344.56</v>
       </c>
       <c r="C74" t="n">
-        <v>5138.45</v>
+        <v>5162.44</v>
+      </c>
+      <c r="D74" t="n">
+        <v>11339.33</v>
+      </c>
+      <c r="E74" t="n">
+        <v>11296.95</v>
       </c>
       <c r="F74" t="n">
-        <v>21294.75</v>
+        <v>10740.2</v>
       </c>
       <c r="G74" t="n">
-        <v>22435.8</v>
+        <v>10901.16</v>
+      </c>
+      <c r="H74" t="n">
+        <v>6843.49</v>
       </c>
       <c r="I74" t="n">
         <v>288</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="K74" t="n">
-        <v>5304.31</v>
-      </c>
-      <c r="L74" t="n">
-        <v>5138.45</v>
-      </c>
-      <c r="M74" t="n">
-        <v>21294.75</v>
-      </c>
-      <c r="N74" t="n">
-        <v>22435.8</v>
-      </c>
-      <c r="O74" t="n">
-        <v>32053.39</v>
-      </c>
-      <c r="P74" t="n">
-        <v>32612.81</v>
-      </c>
-      <c r="Q74" t="n">
-        <v>11658.22</v>
+          <t>final</t>
+        </is>
       </c>
     </row>
     <row r="75">
@@ -11717,39 +13673,33 @@
         <v>46281</v>
       </c>
       <c r="B75" t="n">
-        <v>5146.68</v>
+        <v>5066.79</v>
       </c>
       <c r="C75" t="n">
-        <v>4811.89</v>
+        <v>4909.89</v>
+      </c>
+      <c r="D75" t="n">
+        <v>12038.65</v>
+      </c>
+      <c r="E75" t="n">
+        <v>12568.72</v>
+      </c>
+      <c r="F75" t="n">
+        <v>15128.05</v>
+      </c>
+      <c r="G75" t="n">
+        <v>15640.59</v>
+      </c>
+      <c r="H75" t="n">
+        <v>7438.83</v>
       </c>
       <c r="I75" t="n">
         <v>288</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="K75" t="n">
-        <v>5146.68</v>
-      </c>
-      <c r="L75" t="n">
-        <v>4811.89</v>
-      </c>
-      <c r="M75" t="n">
-        <v>33351.55</v>
-      </c>
-      <c r="N75" t="n">
-        <v>35528.14</v>
-      </c>
-      <c r="O75" t="n">
-        <v>33342.56</v>
-      </c>
-      <c r="P75" t="n">
-        <v>36649.44</v>
-      </c>
-      <c r="Q75" t="n">
-        <v>13594.16</v>
+          <t>final</t>
+        </is>
       </c>
     </row>
     <row r="76">
@@ -11757,54 +13707,33 @@
         <v>46282</v>
       </c>
       <c r="B76" t="n">
-        <v>5008.53</v>
+        <v>4847.99</v>
       </c>
       <c r="C76" t="n">
-        <v>4726.3</v>
+        <v>4731.89</v>
       </c>
       <c r="D76" t="n">
-        <v>16760.48</v>
+        <v>11388.88</v>
       </c>
       <c r="E76" t="n">
-        <v>19092.79</v>
+        <v>12160.33</v>
       </c>
       <c r="F76" t="n">
-        <v>17011.73</v>
+        <v>10265.19</v>
       </c>
       <c r="G76" t="n">
-        <v>18546.02</v>
+        <v>10600.02</v>
       </c>
       <c r="H76" t="n">
-        <v>8698.24</v>
+        <v>6629.09</v>
       </c>
       <c r="I76" t="n">
         <v>288</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="K76" t="n">
-        <v>5008.53</v>
-      </c>
-      <c r="L76" t="n">
-        <v>4726.3</v>
-      </c>
-      <c r="M76" t="n">
-        <v>17011.73</v>
-      </c>
-      <c r="N76" t="n">
-        <v>18546.02</v>
-      </c>
-      <c r="O76" t="n">
-        <v>16760.48</v>
-      </c>
-      <c r="P76" t="n">
-        <v>19092.79</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>8698.24</v>
+          <t>final</t>
+        </is>
       </c>
     </row>
     <row r="77">
@@ -11812,54 +13741,33 @@
         <v>46283</v>
       </c>
       <c r="B77" t="n">
-        <v>4748.07</v>
+        <v>4860.73</v>
       </c>
       <c r="C77" t="n">
-        <v>4635.16</v>
+        <v>4781.74</v>
       </c>
       <c r="D77" t="n">
-        <v>11565.77</v>
+        <v>10453.8</v>
       </c>
       <c r="E77" t="n">
-        <v>12750.16</v>
+        <v>11455.65</v>
       </c>
       <c r="F77" t="n">
-        <v>11584.08</v>
+        <v>10483.34</v>
       </c>
       <c r="G77" t="n">
-        <v>12239.54</v>
+        <v>11039.41</v>
       </c>
       <c r="H77" t="n">
-        <v>6919.44</v>
+        <v>6660.83</v>
       </c>
       <c r="I77" t="n">
         <v>288</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="K77" t="n">
-        <v>4748.07</v>
-      </c>
-      <c r="L77" t="n">
-        <v>4635.16</v>
-      </c>
-      <c r="M77" t="n">
-        <v>11584.08</v>
-      </c>
-      <c r="N77" t="n">
-        <v>12239.54</v>
-      </c>
-      <c r="O77" t="n">
-        <v>11565.77</v>
-      </c>
-      <c r="P77" t="n">
-        <v>12750.16</v>
-      </c>
-      <c r="Q77" t="n">
-        <v>6919.44</v>
+          <t>final</t>
+        </is>
       </c>
     </row>
     <row r="78">
@@ -11867,54 +13775,33 @@
         <v>46284</v>
       </c>
       <c r="B78" t="n">
-        <v>5548.56</v>
+        <v>5558.36</v>
       </c>
       <c r="C78" t="n">
-        <v>5593.83</v>
+        <v>5579.48</v>
       </c>
       <c r="D78" t="n">
-        <v>19244.37</v>
+        <v>13665.48</v>
       </c>
       <c r="E78" t="n">
-        <v>21062.71</v>
+        <v>14772.65</v>
       </c>
       <c r="F78" t="n">
-        <v>19003.61</v>
+        <v>13970.38</v>
       </c>
       <c r="G78" t="n">
-        <v>18999.56</v>
+        <v>13888.06</v>
       </c>
       <c r="H78" t="n">
-        <v>9949.85</v>
+        <v>8214.629999999999</v>
       </c>
       <c r="I78" t="n">
         <v>288</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="K78" t="n">
-        <v>5548.56</v>
-      </c>
-      <c r="L78" t="n">
-        <v>5593.83</v>
-      </c>
-      <c r="M78" t="n">
-        <v>19003.61</v>
-      </c>
-      <c r="N78" t="n">
-        <v>18999.56</v>
-      </c>
-      <c r="O78" t="n">
-        <v>19244.37</v>
-      </c>
-      <c r="P78" t="n">
-        <v>21062.71</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>9949.85</v>
+          <t>final</t>
+        </is>
       </c>
     </row>
     <row r="79">
@@ -11922,54 +13809,33 @@
         <v>46285</v>
       </c>
       <c r="B79" t="n">
-        <v>6138.06</v>
+        <v>6141.66</v>
       </c>
       <c r="C79" t="n">
         <v>6209.01</v>
       </c>
       <c r="D79" t="n">
-        <v>12777.26</v>
+        <v>11252.32</v>
       </c>
       <c r="E79" t="n">
-        <v>14353.45</v>
+        <v>12531.28</v>
       </c>
       <c r="F79" t="n">
-        <v>12859.13</v>
+        <v>11483.58</v>
       </c>
       <c r="G79" t="n">
-        <v>12940.55</v>
+        <v>11505.88</v>
       </c>
       <c r="H79" t="n">
-        <v>8406.51</v>
+        <v>7923.99</v>
       </c>
       <c r="I79" t="n">
         <v>288</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="K79" t="n">
-        <v>6138.06</v>
-      </c>
-      <c r="L79" t="n">
-        <v>6209.01</v>
-      </c>
-      <c r="M79" t="n">
-        <v>12859.13</v>
-      </c>
-      <c r="N79" t="n">
-        <v>12940.55</v>
-      </c>
-      <c r="O79" t="n">
-        <v>12777.26</v>
-      </c>
-      <c r="P79" t="n">
-        <v>14353.45</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>8406.51</v>
+          <t>final</t>
+        </is>
       </c>
     </row>
     <row r="80">
@@ -11977,45 +13843,33 @@
         <v>46286</v>
       </c>
       <c r="B80" t="n">
-        <v>13059.41</v>
+        <v>12782.6</v>
       </c>
       <c r="C80" t="n">
-        <v>13702.61</v>
+        <v>13324.4</v>
+      </c>
+      <c r="D80" t="n">
+        <v>12161.29</v>
+      </c>
+      <c r="E80" t="n">
+        <v>12988.7</v>
       </c>
       <c r="F80" t="n">
-        <v>26991.73</v>
+        <v>13011.37</v>
       </c>
       <c r="G80" t="n">
-        <v>28161.95</v>
+        <v>12442.22</v>
+      </c>
+      <c r="H80" t="n">
+        <v>13159.12</v>
       </c>
       <c r="I80" t="n">
         <v>288</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="K80" t="n">
-        <v>13059.41</v>
-      </c>
-      <c r="L80" t="n">
-        <v>13702.61</v>
-      </c>
-      <c r="M80" t="n">
-        <v>26991.73</v>
-      </c>
-      <c r="N80" t="n">
-        <v>28161.95</v>
-      </c>
-      <c r="O80" t="n">
-        <v>43126</v>
-      </c>
-      <c r="P80" t="n">
-        <v>48110.7</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>21325.63</v>
+          <t>final</t>
+        </is>
       </c>
     </row>
     <row r="81">
@@ -12023,54 +13877,33 @@
         <v>46287</v>
       </c>
       <c r="B81" t="n">
-        <v>8437.129999999999</v>
+        <v>12749.34</v>
       </c>
       <c r="C81" t="n">
-        <v>8353.049999999999</v>
+        <v>12658</v>
       </c>
       <c r="D81" t="n">
-        <v>10233.09</v>
+        <v>12549.41</v>
       </c>
       <c r="E81" t="n">
-        <v>10177.68</v>
+        <v>12950.56</v>
       </c>
       <c r="F81" t="n">
-        <v>11812.5</v>
+        <v>12562.2</v>
       </c>
       <c r="G81" t="n">
-        <v>11543.64</v>
+        <v>12195.14</v>
       </c>
       <c r="H81" t="n">
-        <v>9036.719999999999</v>
+        <v>12654.12</v>
       </c>
       <c r="I81" t="n">
         <v>288</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="K81" t="n">
-        <v>8437.129999999999</v>
-      </c>
-      <c r="L81" t="n">
-        <v>8353.049999999999</v>
-      </c>
-      <c r="M81" t="n">
-        <v>11812.5</v>
-      </c>
-      <c r="N81" t="n">
-        <v>11543.64</v>
-      </c>
-      <c r="O81" t="n">
-        <v>10233.09</v>
-      </c>
-      <c r="P81" t="n">
-        <v>10177.68</v>
-      </c>
-      <c r="Q81" t="n">
-        <v>9036.719999999999</v>
+          <t>final</t>
+        </is>
       </c>
     </row>
     <row r="82">
@@ -12078,54 +13911,33 @@
         <v>46288</v>
       </c>
       <c r="B82" t="n">
-        <v>7752.03</v>
+        <v>9860.48</v>
       </c>
       <c r="C82" t="n">
-        <v>7399.98</v>
+        <v>9602.190000000001</v>
       </c>
       <c r="D82" t="n">
-        <v>9844.49</v>
+        <v>12518.28</v>
       </c>
       <c r="E82" t="n">
-        <v>9859.1</v>
+        <v>12977.45</v>
       </c>
       <c r="F82" t="n">
-        <v>15571.52</v>
+        <v>12357.27</v>
       </c>
       <c r="G82" t="n">
-        <v>10690.2</v>
+        <v>11199.41</v>
       </c>
       <c r="H82" t="n">
-        <v>8201.57</v>
+        <v>10364.58</v>
       </c>
       <c r="I82" t="n">
         <v>288</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="K82" t="n">
-        <v>7752.03</v>
-      </c>
-      <c r="L82" t="n">
-        <v>7399.98</v>
-      </c>
-      <c r="M82" t="n">
-        <v>15571.52</v>
-      </c>
-      <c r="N82" t="n">
-        <v>10690.2</v>
-      </c>
-      <c r="O82" t="n">
-        <v>9844.49</v>
-      </c>
-      <c r="P82" t="n">
-        <v>9859.1</v>
-      </c>
-      <c r="Q82" t="n">
-        <v>8201.57</v>
+          <t>final</t>
+        </is>
       </c>
     </row>
     <row r="83">
@@ -12133,54 +13945,33 @@
         <v>46289</v>
       </c>
       <c r="B83" t="n">
-        <v>8149.42</v>
+        <v>8153.6</v>
       </c>
       <c r="C83" t="n">
-        <v>8088.92</v>
+        <v>8091.63</v>
       </c>
       <c r="D83" t="n">
-        <v>19539.77</v>
+        <v>12174.27</v>
       </c>
       <c r="E83" t="n">
-        <v>21286.87</v>
+        <v>12959.45</v>
       </c>
       <c r="F83" t="n">
-        <v>22933.85</v>
+        <v>14182.21</v>
       </c>
       <c r="G83" t="n">
-        <v>23195.61</v>
+        <v>13965.56</v>
       </c>
       <c r="H83" t="n">
-        <v>12071.94</v>
+        <v>9595.43</v>
       </c>
       <c r="I83" t="n">
         <v>288</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="K83" t="n">
-        <v>8149.42</v>
-      </c>
-      <c r="L83" t="n">
-        <v>8088.92</v>
-      </c>
-      <c r="M83" t="n">
-        <v>22933.85</v>
-      </c>
-      <c r="N83" t="n">
-        <v>23195.61</v>
-      </c>
-      <c r="O83" t="n">
-        <v>19539.77</v>
-      </c>
-      <c r="P83" t="n">
-        <v>21286.87</v>
-      </c>
-      <c r="Q83" t="n">
-        <v>12071.94</v>
+          <t>final</t>
+        </is>
       </c>
     </row>
     <row r="84">
@@ -12188,48 +13979,33 @@
         <v>46290</v>
       </c>
       <c r="B84" t="n">
-        <v>6607.58</v>
+        <v>6599.24</v>
       </c>
       <c r="C84" t="n">
-        <v>6536.35</v>
+        <v>6527.56</v>
       </c>
       <c r="D84" t="n">
-        <v>15116.29</v>
+        <v>11247.4</v>
       </c>
       <c r="E84" t="n">
-        <v>16720.52</v>
+        <v>12212.49</v>
       </c>
       <c r="F84" t="n">
-        <v>31629.85</v>
+        <v>11947.62</v>
+      </c>
+      <c r="G84" t="n">
+        <v>11987.94</v>
+      </c>
+      <c r="H84" t="n">
+        <v>8111.79</v>
       </c>
       <c r="I84" t="n">
         <v>288</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="K84" t="n">
-        <v>6607.58</v>
-      </c>
-      <c r="L84" t="n">
-        <v>6536.35</v>
-      </c>
-      <c r="M84" t="n">
-        <v>31629.85</v>
-      </c>
-      <c r="N84" t="n">
-        <v>33322.01</v>
-      </c>
-      <c r="O84" t="n">
-        <v>15116.29</v>
-      </c>
-      <c r="P84" t="n">
-        <v>16720.52</v>
-      </c>
-      <c r="Q84" t="n">
-        <v>11302.01</v>
+          <t>final</t>
+        </is>
       </c>
     </row>
     <row r="85">
@@ -12670,6 +14446,1326 @@
       </c>
       <c r="Q92" t="n">
         <v>8587.59</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B93" t="n">
+        <v>2957.24</v>
+      </c>
+      <c r="C93" t="n">
+        <v>3047.73</v>
+      </c>
+      <c r="D93" t="n">
+        <v>5021.77</v>
+      </c>
+      <c r="E93" t="n">
+        <v>5911.11</v>
+      </c>
+      <c r="F93" t="n">
+        <v>5316.22</v>
+      </c>
+      <c r="G93" t="n">
+        <v>5138.83</v>
+      </c>
+      <c r="H93" t="n">
+        <v>3763.91</v>
+      </c>
+      <c r="I93" t="n">
+        <v>288</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K93" t="n">
+        <v>2957.24</v>
+      </c>
+      <c r="L93" t="n">
+        <v>3047.73</v>
+      </c>
+      <c r="M93" t="n">
+        <v>5316.22</v>
+      </c>
+      <c r="N93" t="n">
+        <v>5138.83</v>
+      </c>
+      <c r="O93" t="n">
+        <v>5021.77</v>
+      </c>
+      <c r="P93" t="n">
+        <v>5911.11</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>3763.91</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B94" t="n">
+        <v>7446.82</v>
+      </c>
+      <c r="C94" t="n">
+        <v>7651.63</v>
+      </c>
+      <c r="D94" t="n">
+        <v>19254.9</v>
+      </c>
+      <c r="E94" t="n">
+        <v>21816.02</v>
+      </c>
+      <c r="F94" t="n">
+        <v>19907.93</v>
+      </c>
+      <c r="G94" t="n">
+        <v>21037.68</v>
+      </c>
+      <c r="H94" t="n">
+        <v>11557.22</v>
+      </c>
+      <c r="I94" t="n">
+        <v>288</v>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K94" t="n">
+        <v>7446.82</v>
+      </c>
+      <c r="L94" t="n">
+        <v>7651.63</v>
+      </c>
+      <c r="M94" t="n">
+        <v>19907.93</v>
+      </c>
+      <c r="N94" t="n">
+        <v>21037.68</v>
+      </c>
+      <c r="O94" t="n">
+        <v>19254.9</v>
+      </c>
+      <c r="P94" t="n">
+        <v>21816.02</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>11557.22</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B95" t="n">
+        <v>9807.290000000001</v>
+      </c>
+      <c r="C95" t="n">
+        <v>9675.66</v>
+      </c>
+      <c r="D95" t="n">
+        <v>11960.1</v>
+      </c>
+      <c r="E95" t="n">
+        <v>12819.8</v>
+      </c>
+      <c r="F95" t="n">
+        <v>13165.53</v>
+      </c>
+      <c r="G95" t="n">
+        <v>13211.03</v>
+      </c>
+      <c r="H95" t="n">
+        <v>10623.39</v>
+      </c>
+      <c r="I95" t="n">
+        <v>288</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K95" t="n">
+        <v>9807.290000000001</v>
+      </c>
+      <c r="L95" t="n">
+        <v>9675.66</v>
+      </c>
+      <c r="M95" t="n">
+        <v>13165.53</v>
+      </c>
+      <c r="N95" t="n">
+        <v>13211.03</v>
+      </c>
+      <c r="O95" t="n">
+        <v>11960.1</v>
+      </c>
+      <c r="P95" t="n">
+        <v>12819.8</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>10623.39</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B96" t="n">
+        <v>10967.45</v>
+      </c>
+      <c r="C96" t="n">
+        <v>10898.51</v>
+      </c>
+      <c r="D96" t="n">
+        <v>7862.05</v>
+      </c>
+      <c r="E96" t="n">
+        <v>8360.68</v>
+      </c>
+      <c r="F96" t="n">
+        <v>9902.15</v>
+      </c>
+      <c r="G96" t="n">
+        <v>9809.82</v>
+      </c>
+      <c r="H96" t="n">
+        <v>10353.01</v>
+      </c>
+      <c r="I96" t="n">
+        <v>288</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K96" t="n">
+        <v>10967.45</v>
+      </c>
+      <c r="L96" t="n">
+        <v>10898.51</v>
+      </c>
+      <c r="M96" t="n">
+        <v>9902.15</v>
+      </c>
+      <c r="N96" t="n">
+        <v>9809.82</v>
+      </c>
+      <c r="O96" t="n">
+        <v>7862.05</v>
+      </c>
+      <c r="P96" t="n">
+        <v>8360.68</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>10353.01</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B97" t="n">
+        <v>8099.24</v>
+      </c>
+      <c r="C97" t="n">
+        <v>7922.44</v>
+      </c>
+      <c r="D97" t="n">
+        <v>7659.76</v>
+      </c>
+      <c r="E97" t="n">
+        <v>8243.24</v>
+      </c>
+      <c r="F97" t="n">
+        <v>8991.219999999999</v>
+      </c>
+      <c r="G97" t="n">
+        <v>8925.469999999999</v>
+      </c>
+      <c r="H97" t="n">
+        <v>8104.64</v>
+      </c>
+      <c r="I97" t="n">
+        <v>288</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K97" t="n">
+        <v>8099.24</v>
+      </c>
+      <c r="L97" t="n">
+        <v>7922.44</v>
+      </c>
+      <c r="M97" t="n">
+        <v>8991.219999999999</v>
+      </c>
+      <c r="N97" t="n">
+        <v>8925.469999999999</v>
+      </c>
+      <c r="O97" t="n">
+        <v>7659.76</v>
+      </c>
+      <c r="P97" t="n">
+        <v>8243.24</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>8104.64</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B98" t="n">
+        <v>10003.5</v>
+      </c>
+      <c r="C98" t="n">
+        <v>9998.5</v>
+      </c>
+      <c r="D98" t="n">
+        <v>7766.59</v>
+      </c>
+      <c r="E98" t="n">
+        <v>8269.879999999999</v>
+      </c>
+      <c r="F98" t="n">
+        <v>9973.709999999999</v>
+      </c>
+      <c r="G98" t="n">
+        <v>9857.889999999999</v>
+      </c>
+      <c r="H98" t="n">
+        <v>9694.389999999999</v>
+      </c>
+      <c r="I98" t="n">
+        <v>288</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K98" t="n">
+        <v>10003.5</v>
+      </c>
+      <c r="L98" t="n">
+        <v>9998.5</v>
+      </c>
+      <c r="M98" t="n">
+        <v>9973.709999999999</v>
+      </c>
+      <c r="N98" t="n">
+        <v>9857.889999999999</v>
+      </c>
+      <c r="O98" t="n">
+        <v>7766.59</v>
+      </c>
+      <c r="P98" t="n">
+        <v>8269.879999999999</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>9694.389999999999</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B99" t="n">
+        <v>9208.32</v>
+      </c>
+      <c r="C99" t="n">
+        <v>9065.34</v>
+      </c>
+      <c r="D99" t="n">
+        <v>5159.64</v>
+      </c>
+      <c r="E99" t="n">
+        <v>5663.72</v>
+      </c>
+      <c r="F99" t="n">
+        <v>8084.36</v>
+      </c>
+      <c r="G99" t="n">
+        <v>7737.93</v>
+      </c>
+      <c r="H99" t="n">
+        <v>8337.77</v>
+      </c>
+      <c r="I99" t="n">
+        <v>288</v>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K99" t="n">
+        <v>9208.32</v>
+      </c>
+      <c r="L99" t="n">
+        <v>9065.34</v>
+      </c>
+      <c r="M99" t="n">
+        <v>8084.36</v>
+      </c>
+      <c r="N99" t="n">
+        <v>7737.93</v>
+      </c>
+      <c r="O99" t="n">
+        <v>5159.64</v>
+      </c>
+      <c r="P99" t="n">
+        <v>5663.72</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>8337.77</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B100" t="n">
+        <v>4927.04</v>
+      </c>
+      <c r="C100" t="n">
+        <v>4882.91</v>
+      </c>
+      <c r="D100" t="n">
+        <v>2285.45</v>
+      </c>
+      <c r="E100" t="n">
+        <v>2962.68</v>
+      </c>
+      <c r="F100" t="n">
+        <v>2620.9</v>
+      </c>
+      <c r="G100" t="n">
+        <v>2641.86</v>
+      </c>
+      <c r="H100" t="n">
+        <v>4282.57</v>
+      </c>
+      <c r="I100" t="n">
+        <v>288</v>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K100" t="n">
+        <v>4927.04</v>
+      </c>
+      <c r="L100" t="n">
+        <v>4882.91</v>
+      </c>
+      <c r="M100" t="n">
+        <v>2620.9</v>
+      </c>
+      <c r="N100" t="n">
+        <v>2641.86</v>
+      </c>
+      <c r="O100" t="n">
+        <v>2285.45</v>
+      </c>
+      <c r="P100" t="n">
+        <v>2962.68</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>4282.57</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B101" t="n">
+        <v>7561.89</v>
+      </c>
+      <c r="C101" t="n">
+        <v>7885.97</v>
+      </c>
+      <c r="D101" t="n">
+        <v>11217.91</v>
+      </c>
+      <c r="E101" t="n">
+        <v>12556.96</v>
+      </c>
+      <c r="F101" t="n">
+        <v>12584.9</v>
+      </c>
+      <c r="G101" t="n">
+        <v>12755.81</v>
+      </c>
+      <c r="H101" t="n">
+        <v>9283.66</v>
+      </c>
+      <c r="I101" t="n">
+        <v>288</v>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K101" t="n">
+        <v>7561.89</v>
+      </c>
+      <c r="L101" t="n">
+        <v>7885.97</v>
+      </c>
+      <c r="M101" t="n">
+        <v>12584.9</v>
+      </c>
+      <c r="N101" t="n">
+        <v>12755.81</v>
+      </c>
+      <c r="O101" t="n">
+        <v>11217.91</v>
+      </c>
+      <c r="P101" t="n">
+        <v>12556.96</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>9283.66</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B102" t="n">
+        <v>13367.27</v>
+      </c>
+      <c r="C102" t="n">
+        <v>13351.76</v>
+      </c>
+      <c r="D102" t="n">
+        <v>14184.15</v>
+      </c>
+      <c r="E102" t="n">
+        <v>15356.34</v>
+      </c>
+      <c r="F102" t="n">
+        <v>16906.33</v>
+      </c>
+      <c r="G102" t="n">
+        <v>16897.08</v>
+      </c>
+      <c r="H102" t="n">
+        <v>14128.93</v>
+      </c>
+      <c r="I102" t="n">
+        <v>288</v>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K102" t="n">
+        <v>13367.27</v>
+      </c>
+      <c r="L102" t="n">
+        <v>13351.76</v>
+      </c>
+      <c r="M102" t="n">
+        <v>16906.33</v>
+      </c>
+      <c r="N102" t="n">
+        <v>16897.08</v>
+      </c>
+      <c r="O102" t="n">
+        <v>14184.15</v>
+      </c>
+      <c r="P102" t="n">
+        <v>15356.34</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>14128.93</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B103" t="n">
+        <v>7987.37</v>
+      </c>
+      <c r="C103" t="n">
+        <v>7871.65</v>
+      </c>
+      <c r="D103" t="n">
+        <v>11995.94</v>
+      </c>
+      <c r="E103" t="n">
+        <v>12731.52</v>
+      </c>
+      <c r="F103" t="n">
+        <v>12890.6</v>
+      </c>
+      <c r="G103" t="n">
+        <v>12898.47</v>
+      </c>
+      <c r="H103" t="n">
+        <v>9297.620000000001</v>
+      </c>
+      <c r="I103" t="n">
+        <v>288</v>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K103" t="n">
+        <v>7987.37</v>
+      </c>
+      <c r="L103" t="n">
+        <v>7871.65</v>
+      </c>
+      <c r="M103" t="n">
+        <v>12890.6</v>
+      </c>
+      <c r="N103" t="n">
+        <v>12898.47</v>
+      </c>
+      <c r="O103" t="n">
+        <v>11995.94</v>
+      </c>
+      <c r="P103" t="n">
+        <v>12731.52</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>9297.620000000001</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B104" t="n">
+        <v>8007.67</v>
+      </c>
+      <c r="C104" t="n">
+        <v>7991.32</v>
+      </c>
+      <c r="D104" t="n">
+        <v>15724.77</v>
+      </c>
+      <c r="E104" t="n">
+        <v>16708.57</v>
+      </c>
+      <c r="F104" t="n">
+        <v>16127.57</v>
+      </c>
+      <c r="G104" t="n">
+        <v>16499.65</v>
+      </c>
+      <c r="H104" t="n">
+        <v>10459.3</v>
+      </c>
+      <c r="I104" t="n">
+        <v>288</v>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K104" t="n">
+        <v>8007.67</v>
+      </c>
+      <c r="L104" t="n">
+        <v>7991.32</v>
+      </c>
+      <c r="M104" t="n">
+        <v>16127.57</v>
+      </c>
+      <c r="N104" t="n">
+        <v>16499.65</v>
+      </c>
+      <c r="O104" t="n">
+        <v>15724.77</v>
+      </c>
+      <c r="P104" t="n">
+        <v>16708.57</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>10459.3</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B105" t="n">
+        <v>7170.93</v>
+      </c>
+      <c r="C105" t="n">
+        <v>7076.38</v>
+      </c>
+      <c r="D105" t="n">
+        <v>14569.85</v>
+      </c>
+      <c r="E105" t="n">
+        <v>15364.43</v>
+      </c>
+      <c r="F105" t="n">
+        <v>15340.37</v>
+      </c>
+      <c r="G105" t="n">
+        <v>15450.82</v>
+      </c>
+      <c r="H105" t="n">
+        <v>9456.07</v>
+      </c>
+      <c r="I105" t="n">
+        <v>288</v>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K105" t="n">
+        <v>7170.93</v>
+      </c>
+      <c r="L105" t="n">
+        <v>7076.38</v>
+      </c>
+      <c r="M105" t="n">
+        <v>15340.37</v>
+      </c>
+      <c r="N105" t="n">
+        <v>15450.82</v>
+      </c>
+      <c r="O105" t="n">
+        <v>14569.85</v>
+      </c>
+      <c r="P105" t="n">
+        <v>15364.43</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>9456.07</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B106" t="n">
+        <v>8172.25</v>
+      </c>
+      <c r="C106" t="n">
+        <v>8127.75</v>
+      </c>
+      <c r="D106" t="n">
+        <v>10796.25</v>
+      </c>
+      <c r="E106" t="n">
+        <v>11814.32</v>
+      </c>
+      <c r="F106" t="n">
+        <v>13394.58</v>
+      </c>
+      <c r="G106" t="n">
+        <v>13450.89</v>
+      </c>
+      <c r="H106" t="n">
+        <v>9385.299999999999</v>
+      </c>
+      <c r="I106" t="n">
+        <v>288</v>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K106" t="n">
+        <v>8172.25</v>
+      </c>
+      <c r="L106" t="n">
+        <v>8127.75</v>
+      </c>
+      <c r="M106" t="n">
+        <v>13394.58</v>
+      </c>
+      <c r="N106" t="n">
+        <v>13450.89</v>
+      </c>
+      <c r="O106" t="n">
+        <v>10796.25</v>
+      </c>
+      <c r="P106" t="n">
+        <v>11814.32</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>9385.299999999999</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B107" t="n">
+        <v>5189.35</v>
+      </c>
+      <c r="C107" t="n">
+        <v>5244.08</v>
+      </c>
+      <c r="D107" t="n">
+        <v>6413.68</v>
+      </c>
+      <c r="E107" t="n">
+        <v>7265.82</v>
+      </c>
+      <c r="F107" t="n">
+        <v>8085.41</v>
+      </c>
+      <c r="G107" t="n">
+        <v>7917.95</v>
+      </c>
+      <c r="H107" t="n">
+        <v>5907.8</v>
+      </c>
+      <c r="I107" t="n">
+        <v>288</v>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K107" t="n">
+        <v>5189.35</v>
+      </c>
+      <c r="L107" t="n">
+        <v>5244.08</v>
+      </c>
+      <c r="M107" t="n">
+        <v>8085.41</v>
+      </c>
+      <c r="N107" t="n">
+        <v>7917.95</v>
+      </c>
+      <c r="O107" t="n">
+        <v>6413.68</v>
+      </c>
+      <c r="P107" t="n">
+        <v>7265.82</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>5907.8</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B108" t="n">
+        <v>7983.65</v>
+      </c>
+      <c r="C108" t="n">
+        <v>8066.71</v>
+      </c>
+      <c r="D108" t="n">
+        <v>14048.53</v>
+      </c>
+      <c r="E108" t="n">
+        <v>15639.88</v>
+      </c>
+      <c r="F108" t="n">
+        <v>16519.02</v>
+      </c>
+      <c r="G108" t="n">
+        <v>17038.01</v>
+      </c>
+      <c r="H108" t="n">
+        <v>10425.47</v>
+      </c>
+      <c r="I108" t="n">
+        <v>288</v>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K108" t="n">
+        <v>7983.65</v>
+      </c>
+      <c r="L108" t="n">
+        <v>8066.71</v>
+      </c>
+      <c r="M108" t="n">
+        <v>16519.02</v>
+      </c>
+      <c r="N108" t="n">
+        <v>17038.01</v>
+      </c>
+      <c r="O108" t="n">
+        <v>14048.53</v>
+      </c>
+      <c r="P108" t="n">
+        <v>15639.88</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>10425.47</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B109" t="n">
+        <v>10035.59</v>
+      </c>
+      <c r="C109" t="n">
+        <v>9452.02</v>
+      </c>
+      <c r="D109" t="n">
+        <v>15228.37</v>
+      </c>
+      <c r="E109" t="n">
+        <v>16364.44</v>
+      </c>
+      <c r="F109" t="n">
+        <v>17874.69</v>
+      </c>
+      <c r="G109" t="n">
+        <v>17889.01</v>
+      </c>
+      <c r="H109" t="n">
+        <v>11626.26</v>
+      </c>
+      <c r="I109" t="n">
+        <v>288</v>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K109" t="n">
+        <v>10035.59</v>
+      </c>
+      <c r="L109" t="n">
+        <v>9452.02</v>
+      </c>
+      <c r="M109" t="n">
+        <v>17874.69</v>
+      </c>
+      <c r="N109" t="n">
+        <v>17889.01</v>
+      </c>
+      <c r="O109" t="n">
+        <v>15228.37</v>
+      </c>
+      <c r="P109" t="n">
+        <v>16364.44</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>11626.26</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B110" t="n">
+        <v>9348.25</v>
+      </c>
+      <c r="C110" t="n">
+        <v>9226.889999999999</v>
+      </c>
+      <c r="D110" t="n">
+        <v>15526.59</v>
+      </c>
+      <c r="E110" t="n">
+        <v>17504.08</v>
+      </c>
+      <c r="F110" t="n">
+        <v>17920.06</v>
+      </c>
+      <c r="G110" t="n">
+        <v>18002.1</v>
+      </c>
+      <c r="H110" t="n">
+        <v>11595.87</v>
+      </c>
+      <c r="I110" t="n">
+        <v>288</v>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K110" t="n">
+        <v>9348.25</v>
+      </c>
+      <c r="L110" t="n">
+        <v>9226.889999999999</v>
+      </c>
+      <c r="M110" t="n">
+        <v>17920.06</v>
+      </c>
+      <c r="N110" t="n">
+        <v>18002.1</v>
+      </c>
+      <c r="O110" t="n">
+        <v>15526.59</v>
+      </c>
+      <c r="P110" t="n">
+        <v>17504.08</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>11595.87</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B111" t="n">
+        <v>10039.08</v>
+      </c>
+      <c r="C111" t="n">
+        <v>10052.07</v>
+      </c>
+      <c r="D111" t="n">
+        <v>19850.7</v>
+      </c>
+      <c r="E111" t="n">
+        <v>21228.73</v>
+      </c>
+      <c r="F111" t="n">
+        <v>19233.1</v>
+      </c>
+      <c r="G111" t="n">
+        <v>19749.69</v>
+      </c>
+      <c r="H111" t="n">
+        <v>13022.69</v>
+      </c>
+      <c r="I111" t="n">
+        <v>288</v>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K111" t="n">
+        <v>10039.08</v>
+      </c>
+      <c r="L111" t="n">
+        <v>10052.07</v>
+      </c>
+      <c r="M111" t="n">
+        <v>19233.1</v>
+      </c>
+      <c r="N111" t="n">
+        <v>19749.69</v>
+      </c>
+      <c r="O111" t="n">
+        <v>19850.7</v>
+      </c>
+      <c r="P111" t="n">
+        <v>21228.73</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>13022.69</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B112" t="n">
+        <v>7762.82</v>
+      </c>
+      <c r="C112" t="n">
+        <v>7654.5</v>
+      </c>
+      <c r="D112" t="n">
+        <v>18102.77</v>
+      </c>
+      <c r="E112" t="n">
+        <v>19333.04</v>
+      </c>
+      <c r="F112" t="n">
+        <v>18091.15</v>
+      </c>
+      <c r="G112" t="n">
+        <v>17838.41</v>
+      </c>
+      <c r="H112" t="n">
+        <v>10757.78</v>
+      </c>
+      <c r="I112" t="n">
+        <v>288</v>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K112" t="n">
+        <v>7762.82</v>
+      </c>
+      <c r="L112" t="n">
+        <v>7654.5</v>
+      </c>
+      <c r="M112" t="n">
+        <v>18091.15</v>
+      </c>
+      <c r="N112" t="n">
+        <v>17838.41</v>
+      </c>
+      <c r="O112" t="n">
+        <v>18102.77</v>
+      </c>
+      <c r="P112" t="n">
+        <v>19333.04</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>10757.78</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B113" t="n">
+        <v>6319.89</v>
+      </c>
+      <c r="C113" t="n">
+        <v>6328.35</v>
+      </c>
+      <c r="D113" t="n">
+        <v>12094.8</v>
+      </c>
+      <c r="E113" t="n">
+        <v>13090.57</v>
+      </c>
+      <c r="F113" t="n">
+        <v>11922.13</v>
+      </c>
+      <c r="G113" t="n">
+        <v>11902.51</v>
+      </c>
+      <c r="H113" t="n">
+        <v>8063.53</v>
+      </c>
+      <c r="I113" t="n">
+        <v>288</v>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K113" t="n">
+        <v>6319.89</v>
+      </c>
+      <c r="L113" t="n">
+        <v>6328.35</v>
+      </c>
+      <c r="M113" t="n">
+        <v>11922.13</v>
+      </c>
+      <c r="N113" t="n">
+        <v>11902.51</v>
+      </c>
+      <c r="O113" t="n">
+        <v>12094.8</v>
+      </c>
+      <c r="P113" t="n">
+        <v>13090.57</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>8063.53</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="4" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B114" t="n">
+        <v>2295.77</v>
+      </c>
+      <c r="C114" t="n">
+        <v>2365.61</v>
+      </c>
+      <c r="D114" t="n">
+        <v>6977.87</v>
+      </c>
+      <c r="E114" t="n">
+        <v>7897.79</v>
+      </c>
+      <c r="F114" t="n">
+        <v>7128.95</v>
+      </c>
+      <c r="G114" t="n">
+        <v>7177.41</v>
+      </c>
+      <c r="H114" t="n">
+        <v>3817.99</v>
+      </c>
+      <c r="I114" t="n">
+        <v>288</v>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K114" t="n">
+        <v>2295.77</v>
+      </c>
+      <c r="L114" t="n">
+        <v>2365.61</v>
+      </c>
+      <c r="M114" t="n">
+        <v>7128.95</v>
+      </c>
+      <c r="N114" t="n">
+        <v>7177.41</v>
+      </c>
+      <c r="O114" t="n">
+        <v>6977.87</v>
+      </c>
+      <c r="P114" t="n">
+        <v>7897.79</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>3817.99</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B115" t="n">
+        <v>5921.4</v>
+      </c>
+      <c r="C115" t="n">
+        <v>6064.51</v>
+      </c>
+      <c r="D115" t="n">
+        <v>14483</v>
+      </c>
+      <c r="E115" t="n">
+        <v>16343.65</v>
+      </c>
+      <c r="F115" t="n">
+        <v>11942.41</v>
+      </c>
+      <c r="G115" t="n">
+        <v>12326.07</v>
+      </c>
+      <c r="H115" t="n">
+        <v>8446.9</v>
+      </c>
+      <c r="I115" t="n">
+        <v>288</v>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K115" t="n">
+        <v>5921.4</v>
+      </c>
+      <c r="L115" t="n">
+        <v>6064.51</v>
+      </c>
+      <c r="M115" t="n">
+        <v>11942.41</v>
+      </c>
+      <c r="N115" t="n">
+        <v>12326.07</v>
+      </c>
+      <c r="O115" t="n">
+        <v>14483</v>
+      </c>
+      <c r="P115" t="n">
+        <v>16343.65</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>8446.9</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="4" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B116" t="n">
+        <v>6123.87</v>
+      </c>
+      <c r="C116" t="n">
+        <v>6209.5</v>
+      </c>
+      <c r="D116" t="n">
+        <v>21063.75</v>
+      </c>
+      <c r="E116" t="n">
+        <v>22590.5</v>
+      </c>
+      <c r="F116" t="n">
+        <v>19142.86</v>
+      </c>
+      <c r="G116" t="n">
+        <v>20286.26</v>
+      </c>
+      <c r="H116" t="n">
+        <v>10485.94</v>
+      </c>
+      <c r="I116" t="n">
+        <v>288</v>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="K116" t="n">
+        <v>6123.87</v>
+      </c>
+      <c r="L116" t="n">
+        <v>6209.5</v>
+      </c>
+      <c r="M116" t="n">
+        <v>19142.86</v>
+      </c>
+      <c r="N116" t="n">
+        <v>20286.26</v>
+      </c>
+      <c r="O116" t="n">
+        <v>21063.75</v>
+      </c>
+      <c r="P116" t="n">
+        <v>22590.5</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>10485.94</v>
       </c>
     </row>
   </sheetData>
